--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -12136,172 +12136,172 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>12680885-2</t>
+          <t>19636993-7</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Paola</t>
+          <t>Javiera</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>978578934</t>
+          <t>986460190</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>paolarias2026@gmsil.com</t>
+          <t>javiera.fica@bx.cl</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>0885</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F298" s="2">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Chillan</t>
+          <t>La florida</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>105318464</t>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Paola</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>976216745</t>
+          <t>978578934</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>csrolina.soto.inojoda@hmail.com</t>
+          <t>paolarias2026@gmsil.com</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>0885</t>
         </is>
       </c>
       <c r="F299" s="2">
         <v>46135</v>
       </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>12680885-2</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Ivette</t>
+          <t>105318464</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>929382154</t>
+          <t>976216745</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>ivette.gonzalez5@gmail.com</t>
+          <t>csrolina.soto.inojoda@hmail.com</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>0885</t>
+          <t>864</t>
         </is>
       </c>
       <c r="F300" s="2">
         <v>46135</v>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>Chillan</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>19636993-7</t>
+          <t>12680885-2</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Macarena</t>
+          <t>Ivette</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>953333723</t>
+          <t>929382154</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Maca.arevalo.neculhueque@gmail.com</t>
+          <t>ivette.gonzalez5@gmail.com</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>0885</t>
         </is>
       </c>
       <c r="F301" s="2">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Chillan</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>13377893-4</t>
+          <t>19636993-7</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>sergio</t>
+          <t>Macarena</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>937613580</t>
+          <t>953333723</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>slagos@gmail.com</t>
+          <t>Maca.arevalo.neculhueque@gmail.com</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F302" s="2">
@@ -12309,39 +12309,39 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>chillan</t>
+          <t>Quilicura</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>184302497</t>
+          <t>13377893-4</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Maria jose esparza</t>
+          <t>sergio</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>954172922</t>
+          <t>937613580</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>mariaesparza@liceomartabrunet.cl</t>
+          <t>slagos@gmail.com</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="F303" s="2">
@@ -12354,34 +12354,34 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Chillan</t>
+          <t>chillan</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>13377893-4</t>
+          <t>184302497</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>camila</t>
+          <t>Maria jose esparza</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>948632874</t>
+          <t>954172922</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>kamifelice.2@gmsil.com</t>
+          <t>mariaesparza@liceomartabrunet.cl</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="F304" s="2">
@@ -12394,34 +12394,34 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>CHILLAN</t>
+          <t>Chillan</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8.464.650-4</t>
+          <t>13377893-4</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>María jose</t>
+          <t>camila</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>987944995</t>
+          <t>948632874</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>anam@hotmail.com</t>
+          <t>kamifelice.2@gmsil.com</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="F305" s="2">
@@ -12441,27 +12441,27 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>135654590</t>
+          <t>8.464.650-4</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>angelina</t>
+          <t>María jose</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>962746104</t>
+          <t>987944995</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>angelinavilla_@hotmail.com</t>
+          <t>anam@hotmail.com</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="F306" s="2">
@@ -12474,34 +12474,34 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>chillan</t>
+          <t>CHILLAN</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>13377893-4</t>
+          <t>135654590</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>angelina</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>964071656</t>
+          <t>962746104</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>marangel1973@gmail.com</t>
+          <t>angelinavilla_@hotmail.com</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F307" s="2">
@@ -12521,27 +12521,27 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>12680885-2</t>
+          <t>13377893-4</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Johana ravanal</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>979469759</t>
+          <t>964071656</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Johanaravanal.etc@gmail.com</t>
+          <t>marangel1973@gmail.com</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>0885</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="F308" s="2">
@@ -12554,34 +12554,34 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Chillan</t>
+          <t>chillan</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>175458975</t>
+          <t>12680885-2</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Johana ravanal</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>945620506</t>
+          <t>979469759</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>alejandromonardez12@gmail.com</t>
+          <t>Johanaravanal.etc@gmail.com</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>0885</t>
         </is>
       </c>
       <c r="F309" s="2">
@@ -12589,39 +12589,39 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>Chillan</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>8.464.650-4</t>
+          <t>175458975</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>995255569</t>
+          <t>945620506</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>rechaza@gmail.com</t>
+          <t>alejandromonardez12@gmail.com</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F310" s="2">
@@ -12629,104 +12629,104 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>CHILLAN</t>
+          <t>Puente alto</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>184302497</t>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>947329839</t>
+          <t>995255569</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>gerardogutierrezcarrasco89@gmail.com</t>
+          <t>rechaza@gmail.com</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="F311" s="2">
         <v>46136</v>
       </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>13377893-4</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>daniela</t>
+          <t>184302497</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>951968972</t>
+          <t>947329839</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>daniejara1309@gmail.com</t>
+          <t>gerardogutierrezcarrasco89@gmail.com</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="F312" s="2">
         <v>46136</v>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>chillan</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>184302497</t>
+          <t>13377893-4</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Gerardo</t>
+          <t>daniela</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>947329839</t>
+          <t>951968972</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>gerardogutierrezcarrasco89@gmail.com</t>
+          <t>daniejara1309@gmail.com</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="F313" s="2">
@@ -12739,34 +12739,34 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Chillan</t>
+          <t>chillan</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>135654590</t>
+          <t>184302497</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>carlos</t>
+          <t>Gerardo</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>966528490</t>
+          <t>947329839</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>carloscastillo1@gmail.com</t>
+          <t>gerardogutierrezcarrasco89@gmail.com</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="F314" s="2">
@@ -12779,34 +12779,34 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>chillan</t>
+          <t>Chillan</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>8.464.650-4</t>
+          <t>135654590</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>carlos</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>988681015</t>
+          <t>966528490</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>rechaza@gmail.com</t>
+          <t>carloscastillo1@gmail.com</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F315" s="2">
@@ -12819,34 +12819,34 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>CHILLAN</t>
+          <t>chillan</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>184302497</t>
+          <t>8.464.650-4</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Emperatriz</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>997992712</t>
+          <t>988681015</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>emperatrizmata@gmail.com</t>
+          <t>rechaza@gmail.com</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="F316" s="2">
@@ -12859,34 +12859,34 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Chillan</t>
+          <t>CHILLAN</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>160334290</t>
+          <t>184302497</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Isabel</t>
+          <t>Emperatriz</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>944435361</t>
+          <t>997992712</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>isabelclaveria11@gmail.com</t>
+          <t>emperatrizmata@gmail.com</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="F317" s="2">
@@ -12894,38 +12894,4768 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Viña del mar</t>
+          <t>Chillan</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>13377893-4</t>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Isabel</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>939613934</t>
+          <t>944435361</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>leslyleal221181@gmail.com</t>
+          <t>isabelclaveria11@gmail.com</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>13377893-4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F318" s="2">
         <v>46136</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Lesly leal</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>939613934</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>leslyleal221181@gmail.com</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+      <c r="F319" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>20398235-6</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Yeri Lopez</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>+569 82111199</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>yeri.lopez@yahoo.cl</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="F320" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>118755634</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>922014272</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="F321" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Antonia Josefina</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>927651378</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>carterasyzapatosaj@gmail.com</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F322" s="2">
+        <v>46135</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>118755634</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Alicia</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>959319424</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="F323" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>13565459-0</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>angela</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>+56 9 7205 2991</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>angelajofre42@gmail.com</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F324" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Leticia</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>944082039</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>leticia.cires1985@gmail.com</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F325" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Alicia</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>979825832</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Alicia.gonzalez123@gmail.com</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="F326" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>118755634</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>940807201</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="F327" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Romina</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>975685170</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>ariasarmijoromina@gmail.com</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F328" s="2">
+        <v>46135</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>141550888</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Pia</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>989887795</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>piahelengalaz@gmail.com</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="F329" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>949021231</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>sandritasmu@gmail.com</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F330" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>191756237</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>bfernandez@datodinamico.cl</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F331" s="2">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>118755634</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>983517045</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="F332" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Agustina</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>961353528</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>agustina.miranda.a97@gmail.com</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F333" s="2">
+        <v>46135</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>PUENTE ALTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Camilo Custodio Rojas Roman</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>978723028</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>camilo.rojasroman@gmail.com</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F334" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Ingrid</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>989063801</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ingriddelpilarv9@gmail.com</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F335" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>13565459-0</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>paola</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>9 5729 2737</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>pao.paola2@gmail.com</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F336" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>959523294</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>santana.ignacio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F337" s="2">
+        <v>46135</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>19636993-7</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Jesus</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>951326099</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>jesu.bombal@gmail.com</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="F338" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>203982356</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Carlos Martin</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>+569 86436020</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>carlistosmartinortiz@gmail.com</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="F339" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>135654590</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>belen</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>940478340</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>belenbelencita7@gmail.com</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F340" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Ckaudio</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>976543217</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>claudiobonjovi1990@gmail.com</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F341" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Nayadet</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>982012489</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>nayadetgdiaz@gmail.com</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F342" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>180505091</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>56951370404</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>valeriacerda.a@gmail.com</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="F343" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>La Granja</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>juan carlos ayala vasquez</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Alejandro Salazar</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>965747704</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>alej.salazar.89@gmail.com</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F344" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>140556351</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>923791457</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>kespinoza092005@gmail.com</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F345" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>207071420</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>957458106</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>fefacossio13@gmail.com</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>96.891.370-0</t>
+        </is>
+      </c>
+      <c r="F346" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>16288310-0</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>959463460</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>angelseraphan45@gmail.com</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="F347" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>19037691-5</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Ciro Cortes Manriquez</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>991650192</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>ciroa.cortesm@gmail.com</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>COSAM municipal de pudahuel</t>
+        </is>
+      </c>
+      <c r="F348" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Libertador General Bernardo O’Higgins</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Alberto</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>987274449</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="F349" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>172867529</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>951069210</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>betzabefernandez.r@gmail.com</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="F350" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>19636993-7</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>950974874</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>camilasorianosilva@gmail.com</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="F351" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>16288310-0</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>988290556</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>claudiaiturrietam@gmaol.com</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="F352" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>118755634</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>974066438</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="F353" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>979825832</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>alicia.gonzalez123@gmail.com</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="F354" s="2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>180505091</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>569990908165</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>claudia.sanh@gmail.com</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="F355" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>203982356</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>+569 22430392</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>ramire19371@gmail.com</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="F356" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Rocío</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>940507267</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>rociokas87@gmail.com</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>7893</t>
+        </is>
+      </c>
+      <c r="F357" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>12680885-3</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Alicia</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>979825832</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Alicia.gonzalez123@gmail.com</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="F358" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>190376915</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Genesis</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>56964977475</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>genesis.avilaesp@gmail.com</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Cosam municipal pudahuel</t>
+        </is>
+      </c>
+      <c r="F359" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Jasthin</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>973872873</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F360" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>16288310-0</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Consulo</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>953036385</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>consuelolopezjeres@gmail.com</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="F361" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Matías</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>942282834</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F362" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>16288310-0</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>937110024</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Isabelashantiuwu@gmail.com</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="F363" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>962970874</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>rosita.vas.m@gmail.com</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F364" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Veronica</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>978596219</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Veronica.landaeta1974@gmail.com</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="F365" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Ángel</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>975823756</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F366" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>12345677</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Fgjkk</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>9345678889</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>carmencastro613@gmail.com</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="F367" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Ghjklljbv</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>96021062</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>María José Osorio</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>997052240</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>mosorioavalos@gmsil.com</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="F368" s="2">
+        <v>46135</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>9602106-2</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>983118140</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>medaliabrago@gmail.com</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="F369" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>9.602.106-2</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>987492760</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>panchox88@gmail.com</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="F370" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>19037691-5</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Francesca</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>953744041</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>f.salvoh@gmail.com</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Cliodinamica</t>
+        </is>
+      </c>
+      <c r="F371" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>La reina</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>9.602.106-2</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>944192379</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>simon.perez.b@usach.cl</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="F372" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>98494393</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>valeriaantunez@gmail.com</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F373" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>135654590</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>jimena</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>95450796</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>jime_natal@gmail.com</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F374" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>997000364</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F375" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>203982356</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Cristobal</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>+569 75285980</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>cristobal.picarte@gmail.com</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="F376" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Quinta Noral</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>9795983-8</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>964271820</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>karla.lodi77@gmail.com</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F377" s="2">
+        <v>46324</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Quilpué</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Gino</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>999946471</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="F378" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>141550888</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Gerardo</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>988831220</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>gebsoak@gmail.com</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="F379" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Erika</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>56993307870</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>larucadeunihue@gmail.com</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="F380" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>965172558</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F381" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>135654590</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>juan Francisco</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>958911485</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>juanfrancisco-22@gmail.com</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F382" s="2">
+        <v>46130</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>118755634</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>998973794</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="F383" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Jimena</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>938288247</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F384" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Risalba</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>993650086</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="F385" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Jaqueline</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>976681549</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>jlanderos80@gmail.com</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F386" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>56998876497</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>rvargas@casasdelmaule.cl</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="F387" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>946355991</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>katherinelavabdero033@gmail.com</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F388" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>180505091</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Lía</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>56961839663</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>li.conejeros.b@gmail.com</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="F389" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>135654590</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>miguel</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>941554730</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>miguelarias26@gmail.com</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F390" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>11875563-4</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>956039549</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>5563</t>
+        </is>
+      </c>
+      <c r="F391" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>16288310-0</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>967026787</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>isabelgonzalezmunos86@gmail.com</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="F392" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>13565459-0</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>soledad</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>945123685</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>soledadcontreras.preunic@gmail.com</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F393" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>172867529</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>56977469590</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>karenespindolaulloa@gmail.com</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="F394" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>203982356</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Viviana Mera Muñoz</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>+569 66081656</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>vivianameram@gmail.com</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="F395" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>13.3053689</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Francisca Valdes</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>989552770</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>franciscavaldesj@gmail.com</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F396" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>14155088-8</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Mery araya</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>998903830</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>meriviolett1257@gmail.com</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="F397" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>96021062</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>María jose</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>992492232</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>marisjosearancibia@gmail.com</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="F398" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>16288310-0</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Margarita</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>975660343</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>margaritarubio624@gmail.com</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="F399" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>14155088-8</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>982100980</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>luiscamposa@gmail.com</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="F400" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Jorge Sotomayor Núñez</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>990785800</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>jsotomayor.n@gmail.com</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F401" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>16288310-0</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Carmen Gloria Ossandón</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>994829430</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>ossandoncarmengloria@gmail.com</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="F402" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>14155088-8</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Viviana</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>998059128</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>vivicerpalara@gmail.com</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="F403" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>16288310-0</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Leticia</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>991211159</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>leticiapineda1997@gmail.com</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="F404" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>180505091</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Roxana</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>56989151791</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>rurzuabustamante@gmail.com</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="F405" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Paula Sepulveda Orrego</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>965016347</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>paula.sepulveda.o@gmsil.com</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F406" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>203982356</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>+569 35955986</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>robertoandres958@gmail.com</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="F407" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>San bernardo</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Benilde</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>963031919</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F408" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>14155088-8</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>933949129</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>moragacamposcamila@gmail.com</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="F409" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Curico</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>978699548</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>benja.munoz2010@gmail.com</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F410" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Ibania</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>967689034</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>ibaniasammartinzamm@gmail.com</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="F411" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>957037428</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F412" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>19.037.691-5</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Stella Delgado</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>948668795</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>stelladelgadosalamanca@gmail.com</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Cliodinamica</t>
+        </is>
+      </c>
+      <c r="F413" s="2">
+        <v>45678</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Ximena</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>979080894</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>xconchacontreras@gmail.com</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>7893</t>
+        </is>
+      </c>
+      <c r="F414" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>chillan viejo</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>180505091</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>56942694227</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>garrido.matias1991@gmail.com</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="F415" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Padre Hurtado</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Maria pereira</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>992845646</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>kristypereiram@gmail.com</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F416" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>956893538</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>janny.23h@gmail.com</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="F417" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>13377893-4</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>javiera</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>982139338</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>7893</t>
+        </is>
+      </c>
+      <c r="F418" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Chillan viejo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Irles</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>952628197</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>irlesgajardo@gmail.com</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F419" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>96021062</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>931199643</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>jorgejavieviergonzalezv@gmail.com</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="F420" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>932175210</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>milii.villalobos.0312@gmail.com</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="F421" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>19.037.691-5</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>935366889</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>deysay.20@gmail.com</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Cliodinamica</t>
+        </is>
+      </c>
+      <c r="F422" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>98784724</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Roger</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>961182376</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>roger.villoslado@gmail.com</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F423" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>96021062</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Angelica</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>950055432</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>angelicamariarm@gmail.com</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="F424" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>994511641</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F425" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>95538033</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>gustavo.basulto@tumejoraliado.cl</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F426" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>966108781</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F427" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>951665773</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>isacaceres1@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="F428" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Anabella</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>958073001</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F429" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Marjorie</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>991219903</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>marjorie.contreras@live.cl</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F430" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>998664675</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F431" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>19.037.691-5</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Franchesca Michele Paz Paz</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>56987422680</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>franchescap.paz@gmail.com</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Cliodinamica</t>
+        </is>
+      </c>
+      <c r="F432" s="2">
+        <v>43983</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>19.037.691-5</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Tania Angulo</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>995895027</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>taynycha17@gmail.com</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Cliodinamica</t>
+        </is>
+      </c>
+      <c r="F433" s="2">
+        <v>46117</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Juan Carlos nueñez</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>962956628</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>jcnunez@spacenet.cl</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="F434" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Lilian</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>995290215</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F435" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>983983707</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>valeriazurita.gonzalez@gmail.com</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F436" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Ángel</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>98380183</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F437" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H486"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -17658,6 +17658,1951 @@
         </is>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Yeldo Valdés acevedo</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>990747826</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>yeldo.valdes.a@gmail.com</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F438" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Alexis</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>972242438</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F439" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Marcela</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>971775745</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>marcela.ancamil.94@gmail.com</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F440" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>97447632</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Viviana</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>953247225</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>vturchan@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F441" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>973480118</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F442" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>953969129</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>hermes.ferrada@gmail.com</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F443" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>944773380</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>nino7027@gmail.com</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F444" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>946757876</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F445" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>180505091</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Maricel</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>56949071227</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>prevmaricel1987@gmail.com</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="F446" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>19.037.691-5</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Genesis leal</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>56950114151</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>leal.genesis1993@gmail.com</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Cliodinamica</t>
+        </is>
+      </c>
+      <c r="F447" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>San joaquin</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>967678324</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>martinezleonarrdo@gmail.com</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="F448" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>989942739</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F449" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>9852862581</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>ec9852150@gmail.com</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="F450" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>961983024</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>contrerasjarafrancisca@gmail.com</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F451" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Erica</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>javierolivaresready@gmail.com</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="F452" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Roxana</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>6565826829</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>danielmonica24@gmial.com</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="F453" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Carolina Valdés Caceres</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>984496164</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>carovaldesca@gmail.com</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F454" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Pilar</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>carlosibarria34@gmail.com</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="F455" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Magali</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>9996763225</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>notengo@gmial.vom</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="F456" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>97273828</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F457" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>928292920</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F458" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>997140749</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="F459" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Jorge Diaz</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>950447051</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>jorge.diaz@vctchile.com</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F460" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Marisol</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>9725146389</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>tomaseherrreraz@gmail.com</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="F461" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>978709456</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>ventasgermany@gmail.com</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="F462" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Karina</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>979610532</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>k.leonmunoz@gmsil.com</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F463" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>14155088-8</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Karla</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>947483171</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>karlarojasmatamala@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="F464" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>22219144-0</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>975432545</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F465" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>965451422</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>josepth7zamora@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F466" s="2">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Josepth</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>965451422</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>josepth7zamora@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="F467" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>14155088-8</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Karin</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>947483171</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>karin.miranda98@gmail.com</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="F468" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>180505091</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Denise</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>56957344313</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>denisbahamondes1@gmail.com</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="F469" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>11875563</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>000000000</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>notiene@gmaill.com</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F470" s="2">
+        <v>46137</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>19.037.691-5</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Juan Hernández</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>+569 7660 4081</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>jhernandez.cicsa@gmail.com</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>cliodinamica</t>
+        </is>
+      </c>
+      <c r="F471" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>María Carolina Stark Campos</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>948642874</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>carolinastark@gmail.com</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F472" s="2">
+        <v>411380</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Doralisa Fuentes</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>999640448</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>dorysfuentes07@gmail.com</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F473" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Juani</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>991874908</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>moralesjuani88@gmail.com</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F474" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Carlos manriquez</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>933392976</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>manriquez.ius92@gmail.com</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="F475" s="2">
+        <v>46138</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Valeska Hernández Rayo</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>993586365</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>valeskahrayo@gmail.com</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F476" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>102693531</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Marcela Gutierrez</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>995167424</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>marcelavergara35@gmail.com</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F477" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>97447632</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>961685344</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>npardod@gmail.com</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F478" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>108566507</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Ximena</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>949232488</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>maritete2203@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F479" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>San miguel</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Lisete</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>966054538</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>douglaslucena_72@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F480" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>97447632</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>961685344</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>npardod@gmail.com</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F481" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>102693531</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>934139053</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>claudiariasojega@gmail.com</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F482" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Lo prado</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>16933558-3</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Costanza</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>942664225</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>oscar.mcastro93@gmail.com</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F483" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>97447632</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>961685344</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>npardod@gmail.com</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F484" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>20.486.959-6</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Benj</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>922147247</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>ojogatoverde@gmail.com</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F485" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>10269353-1</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Leslie</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>930629162</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>coaquira.zarate.leslie@gmail.com</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F486" s="2">
+        <v>46139</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R570"/>
+  <dimension ref="A1:R617"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="15" max="15" width="20.7109375" style="2" customWidth="1"/>
@@ -34913,32 +34913,32 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>17250376-4</t>
+          <t>21668032-4</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Ignacio</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Leslie</t>
+          <t>Daniela</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>56966543446</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>ignaciotorrestt@gmail.com</t>
+          <t>dc_pozas@hotmail.com</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
@@ -34948,81 +34948,76 @@
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="M554" t="inlineStr">
         <is>
-          <t>0376-4</t>
+          <t>encuestador datodinamico</t>
         </is>
       </c>
       <c r="N554" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O554" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="P554" s="3">
-        <v>46141.01381944444</v>
+        <v>46140.97743055555</v>
       </c>
       <c r="Q554" s="3">
-        <v>46141.03280092592</v>
+        <v>46141.96667824074</v>
       </c>
       <c r="R554" s="3">
-        <v>46141.03277777778</v>
+        <v>46141.96667824074</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>184302497</t>
+          <t>17250376-4</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Ignacio</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Pareja</t>
+          <t>Leslie</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>Hija de mi pareja</t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr">
-        <is>
-          <t>Hijo</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>949486563</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>osoriomardonescd@gmail.com</t>
+          <t>ignaciotorrestt@gmail.com</t>
         </is>
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>Chillan</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0376-4</t>
         </is>
       </c>
       <c r="N555" t="inlineStr">
@@ -35034,13 +35029,13 @@
         <v>46140</v>
       </c>
       <c r="P555" s="3">
-        <v>46141.01655092592</v>
+        <v>46141.01381944444</v>
       </c>
       <c r="Q555" s="3">
-        <v>46141.04357638889</v>
+        <v>46141.03280092592</v>
       </c>
       <c r="R555" s="3">
-        <v>46141.04354166667</v>
+        <v>46141.03277777778</v>
       </c>
     </row>
     <row r="556">
@@ -35051,27 +35046,32 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Leticia</t>
+          <t>Cristian</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Esposo</t>
+          <t>Pareja</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Hija de mi pareja</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Hijo</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>965426023</t>
+          <t>949486563</t>
         </is>
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>leticiasotomora88@gmail.com</t>
+          <t>osoriomardonescd@gmail.com</t>
         </is>
       </c>
       <c r="K556" t="inlineStr">
@@ -35098,189 +35098,194 @@
         <v>46140</v>
       </c>
       <c r="P556" s="3">
-        <v>46141.05482638889</v>
+        <v>46141.01655092592</v>
       </c>
       <c r="Q556" s="3">
-        <v>46141.08783564815</v>
+        <v>46141.04357638889</v>
       </c>
       <c r="R556" s="3">
-        <v>46141.0878125</v>
+        <v>46141.04354166667</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>105033206</t>
+          <t>184302497</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Leticia</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Marcia</t>
+          <t>Esposo</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Hija</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t>Hijo</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>42842865</t>
+          <t>965426023</t>
         </is>
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>nelsoncordero482@gmail.com</t>
+          <t>leticiasotomora88@gmail.com</t>
         </is>
       </c>
       <c r="K557" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Chillan</t>
         </is>
       </c>
       <c r="M557" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="N557" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O557" s="2">
         <v>46140</v>
       </c>
       <c r="P557" s="3">
-        <v>46141.0672800926</v>
+        <v>46141.05482638889</v>
+      </c>
+      <c r="Q557" s="3">
+        <v>46141.08783564815</v>
       </c>
       <c r="R557" s="3">
-        <v>46141.15247685185</v>
+        <v>46141.0878125</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>184302497</t>
+          <t>105033206</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>Hija</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Hijo</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>976648332</t>
+          <t>42842865</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>alejandra.n24@gmail.com</t>
+          <t>nelsoncordero482@gmail.com</t>
         </is>
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>Chillan</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>33</t>
         </is>
       </c>
       <c r="N558" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O558" s="2">
         <v>46140</v>
       </c>
       <c r="P558" s="3">
-        <v>46141.10434027778</v>
-      </c>
-      <c r="Q558" s="3">
-        <v>46141.12237268519</v>
+        <v>46141.0672800926</v>
       </c>
       <c r="R558" s="3">
-        <v>46141.12236111111</v>
+        <v>46141.15247685185</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>194219067</t>
+          <t>184302497</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Carlos urrea</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Patricia soto</t>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>944476648</t>
+          <t>976648332</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>c.urreatorres@gmail.com</t>
+          <t>alejandra.n24@gmail.com</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>San miguel</t>
+          <t>Chillan</t>
         </is>
       </c>
       <c r="M559" t="inlineStr">
         <is>
-          <t>Camila Urrea</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="N559" t="inlineStr">
@@ -35292,134 +35297,129 @@
         <v>46140</v>
       </c>
       <c r="P559" s="3">
-        <v>46141.13788194444</v>
+        <v>46141.10434027778</v>
       </c>
       <c r="Q559" s="3">
-        <v>46141.18722222222</v>
+        <v>46141.12237268519</v>
       </c>
       <c r="R559" s="3">
-        <v>46141.18721064815</v>
+        <v>46141.12236111111</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>16274824-6</t>
+          <t>194219067</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Carlos urrea</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Patricia soto</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>56972267309</t>
+          <t>944476648</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>J.yanezmontecinos@gmail.com</t>
+          <t>c.urreatorres@gmail.com</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>San miguel</t>
         </is>
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t>Conac</t>
+          <t>Camila Urrea</t>
         </is>
       </c>
       <c r="N560" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O560" s="2">
         <v>46140</v>
       </c>
       <c r="P560" s="3">
-        <v>46141.14972222222</v>
+        <v>46141.13788194444</v>
+      </c>
+      <c r="Q560" s="3">
+        <v>46141.18722222222</v>
       </c>
       <c r="R560" s="3">
-        <v>46141.76561342593</v>
+        <v>46141.18721064815</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>17250376-4</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>Brenda</t>
+          <t>16274824-6</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>948544198</t>
+          <t>56972267309</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>brenda.cast88@gmail.com</t>
-        </is>
-      </c>
-      <c r="K561" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="L561" t="inlineStr">
-        <is>
-          <t>Independencia</t>
+          <t>J.yanezmontecinos@gmail.com</t>
         </is>
       </c>
       <c r="M561" t="inlineStr">
         <is>
-          <t>0376-5</t>
+          <t>Conac</t>
         </is>
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O561" s="2">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="P561" s="3">
-        <v>46141.67172453704</v>
-      </c>
-      <c r="Q561" s="3">
-        <v>46141.70496527778</v>
+        <v>46141.14972222222</v>
       </c>
       <c r="R561" s="3">
-        <v>46141.70496527778</v>
+        <v>46141.76561342593</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>19313240-5</t>
+          <t>17250376-4</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Carla</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>Diana</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>965349941</t>
+          <t>948544198</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>carla.segura.osses@gmail.com</t>
+          <t>brenda.cast88@gmail.com</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
@@ -35429,12 +35429,12 @@
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="M562" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0376-5</t>
         </is>
       </c>
       <c r="N562" t="inlineStr">
@@ -35446,44 +35446,44 @@
         <v>46141</v>
       </c>
       <c r="P562" s="3">
-        <v>46141.688125</v>
+        <v>46141.67172453704</v>
       </c>
       <c r="Q562" s="3">
-        <v>46141.71259259259</v>
+        <v>46141.70496527778</v>
       </c>
       <c r="R562" s="3">
-        <v>46141.71259259259</v>
+        <v>46141.70496527778</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>19313205</t>
+          <t>19313240-5</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Eliana</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Diana</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>965349941</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>elianamunozcelis@gmail.com</t>
+          <t>carla.segura.osses@gmail.com</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
@@ -35493,7 +35493,7 @@
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="M563" t="inlineStr">
@@ -35510,59 +35510,59 @@
         <v>46141</v>
       </c>
       <c r="P563" s="3">
-        <v>46141.69107638889</v>
+        <v>46141.688125</v>
       </c>
       <c r="Q563" s="3">
-        <v>46141.71989583333</v>
+        <v>46141.71259259259</v>
       </c>
       <c r="R563" s="3">
-        <v>46141.71989583333</v>
+        <v>46141.71259259259</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>19313205</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Andrea Ferretti Abarca</t>
+          <t>Eliana</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Gabriela Jara Ferretti</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Esteban Jara Ferretti</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>998431958</t>
+          <t>999999</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>andreaferretticory@gmail.com</t>
+          <t>elianamunozcelis@gmail.com</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="M564" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N564" t="inlineStr">
@@ -35574,49 +35574,59 @@
         <v>46141</v>
       </c>
       <c r="P564" s="3">
-        <v>46141.70777777777</v>
+        <v>46141.69107638889</v>
       </c>
       <c r="Q564" s="3">
-        <v>46141.73083333333</v>
+        <v>46141.71989583333</v>
       </c>
       <c r="R564" s="3">
-        <v>46141.73083333333</v>
+        <v>46141.71989583333</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>184302497</t>
+          <t>13305368-9</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Andrea Ferretti Abarca</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Gabriela Jara Ferretti</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Esteban Jara Ferretti</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>958898163</t>
+          <t>998431958</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>luisgonzalezcaro@gmail.com</t>
+          <t>andreaferretticory@gmail.com</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>Chillan</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="M565" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N565" t="inlineStr">
@@ -35628,54 +35638,49 @@
         <v>46141</v>
       </c>
       <c r="P565" s="3">
-        <v>46141.70820601852</v>
+        <v>46141.70777777777</v>
       </c>
       <c r="Q565" s="3">
-        <v>46141.74273148148</v>
+        <v>46141.73083333333</v>
       </c>
       <c r="R565" s="3">
-        <v>46141.74273148148</v>
+        <v>46141.73083333333</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>19313240-5</t>
+          <t>184302497</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Angel</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>Jesa</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>939460277</t>
+          <t>958898163</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>jesa.antonia@gmail.com</t>
+          <t>luisgonzalezcaro@gmail.com</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>Estacion central</t>
+          <t>Chillan</t>
         </is>
       </c>
       <c r="M566" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="N566" t="inlineStr">
@@ -35687,39 +35692,39 @@
         <v>46141</v>
       </c>
       <c r="P566" s="3">
-        <v>46141.71496527777</v>
+        <v>46141.70820601852</v>
       </c>
       <c r="Q566" s="3">
-        <v>46141.7325</v>
+        <v>46141.74273148148</v>
       </c>
       <c r="R566" s="3">
-        <v>46141.7325</v>
+        <v>46141.74273148148</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>17250376-4</t>
+          <t>19313240-5</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Valeria</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Antonia</t>
+          <t>Jesa</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>939460277</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>nane.guaiquil@gmail.com</t>
+          <t>jesa.antonia@gmail.com</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
@@ -35729,135 +35734,130 @@
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>San miguel</t>
+          <t>Estacion central</t>
         </is>
       </c>
       <c r="M567" t="inlineStr">
         <is>
-          <t>0376-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N567" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O567" s="2">
         <v>46141</v>
       </c>
       <c r="P567" s="3">
-        <v>46141.73247685185</v>
+        <v>46141.71496527777</v>
       </c>
       <c r="Q567" s="3">
-        <v>46141.76467592592</v>
+        <v>46141.7325</v>
       </c>
       <c r="R567" s="3">
-        <v>46141.76467592592</v>
+        <v>46141.7325</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>8.464.650-4</t>
+          <t>17250376-4</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>leonor</t>
+          <t>Valeria</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Antonia</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>990186049</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>rechaza@gmail.com</t>
+          <t>nane.guaiquil@gmail.com</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>CHILLAN</t>
+          <t>San miguel</t>
         </is>
       </c>
       <c r="M568" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>0376-6</t>
         </is>
       </c>
       <c r="N568" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O568" s="2">
         <v>46141</v>
       </c>
       <c r="P568" s="3">
-        <v>46141.74442129629</v>
+        <v>46141.73247685185</v>
       </c>
       <c r="Q568" s="3">
-        <v>46141.76310185185</v>
+        <v>46141.76467592592</v>
       </c>
       <c r="R568" s="3">
-        <v>46141.76310185185</v>
+        <v>46141.76467592592</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>19313240-5</t>
+          <t>8.464.650-4</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>leonor</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Maitr</t>
-        </is>
-      </c>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>Coni</t>
+          <t>David</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>952370460</t>
+          <t>990186049</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>anasepulveda6@gmail.com</t>
+          <t>rechaza@gmail.com</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>Lo prado</t>
+          <t>CHILLAN</t>
         </is>
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="N569" t="inlineStr">
@@ -35869,13 +35869,13 @@
         <v>46141</v>
       </c>
       <c r="P569" s="3">
-        <v>46141.74678240741</v>
+        <v>46141.74442129629</v>
       </c>
       <c r="Q569" s="3">
-        <v>46141.76068287037</v>
+        <v>46141.76310185185</v>
       </c>
       <c r="R569" s="3">
-        <v>46141.76068287037</v>
+        <v>46141.76310185185</v>
       </c>
     </row>
     <row r="570">
@@ -35886,27 +35886,27 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Alejanda</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Maitr</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Francisca</t>
+          <t>Coni</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>989197601</t>
+          <t>952370460</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>bernaalehandravargas@ggmail.com</t>
+          <t>anasepulveda6@gmail.com</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
@@ -35916,12 +35916,12 @@
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>Cerro navia</t>
+          <t>Lo prado</t>
         </is>
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N570" t="inlineStr">
@@ -35933,10 +35933,2959 @@
         <v>46141</v>
       </c>
       <c r="P570" s="3">
+        <v>46141.74678240741</v>
+      </c>
+      <c r="Q570" s="3">
+        <v>46141.76068287037</v>
+      </c>
+      <c r="R570" s="3">
+        <v>46141.76068287037</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Alejanda</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>989197601</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>bernaalehandravargas@ggmail.com</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>Cerro navia</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O571" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P571" s="3">
         <v>46141.77056712963</v>
       </c>
-      <c r="R570" s="3">
-        <v>46141.77401620371</v>
+      <c r="Q571" s="3">
+        <v>46141.78674768518</v>
+      </c>
+      <c r="R571" s="3">
+        <v>46141.78674768518</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Mirta</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>962351653</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O572" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P572" s="3">
+        <v>46141.77474537037</v>
+      </c>
+      <c r="Q572" s="3">
+        <v>46141.80137731481</v>
+      </c>
+      <c r="R572" s="3">
+        <v>46141.80137731481</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Yasna</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Alen</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Romina</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>941386941</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>yasna.pinela@gmail.com</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O573" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P573" s="3">
+        <v>46141.79465277778</v>
+      </c>
+      <c r="Q573" s="3">
+        <v>46141.81171296297</v>
+      </c>
+      <c r="R573" s="3">
+        <v>46141.81170138888</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Marcelo</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Tania</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Patricio antonio</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>981243211</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>patriciocayun1960@gmail.com</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O574" s="2">
+        <v>45382</v>
+      </c>
+      <c r="P574" s="3">
+        <v>46141.79858796296</v>
+      </c>
+      <c r="Q574" s="3">
+        <v>46141.83960648148</v>
+      </c>
+      <c r="R574" s="3">
+        <v>46141.83960648148</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>19313205</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Maximiliano</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>937628622</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>camilawork41@gmail.con</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O575" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P575" s="3">
+        <v>46141.80354166667</v>
+      </c>
+      <c r="Q575" s="3">
+        <v>46141.82684027778</v>
+      </c>
+      <c r="R575" s="3">
+        <v>46141.82684027778</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Valeska</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Antonia</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>942703307</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>quintana.carcamo@gmail.com</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>San joaquin</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>0376-7</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O576" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P576" s="3">
+        <v>46141.81939814815</v>
+      </c>
+      <c r="Q576" s="3">
+        <v>46141.85115740741</v>
+      </c>
+      <c r="R576" s="3">
+        <v>46141.85115740741</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>16250303-0</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Adrián Luengo González</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Adrián Luengo Infantes</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Nicolás Luengo Infantes</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>940951842</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>nancyinfanteh@gmail.com</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>76016305-8</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O577" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P577" s="3">
+        <v>46141.83357638889</v>
+      </c>
+      <c r="Q577" s="3">
+        <v>46141.86357638889</v>
+      </c>
+      <c r="R577" s="3">
+        <v>46141.86357638889</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Isaías</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>942130983</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O578" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P578" s="3">
+        <v>46141.86013888889</v>
+      </c>
+      <c r="Q578" s="3">
+        <v>46141.88569444444</v>
+      </c>
+      <c r="R578" s="3">
+        <v>46141.88569444444</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Nicolle</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>974449247</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O579" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P579" s="3">
+        <v>46141.89697916667</v>
+      </c>
+      <c r="Q579" s="3">
+        <v>46141.91947916667</v>
+      </c>
+      <c r="R579" s="3">
+        <v>46141.91947916667</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Claudio</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Alondra</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>944343105</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>claudiogonzalezalarcon@gmail.com</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>0376-8</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O580" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P580" s="3">
+        <v>46141.9177199074</v>
+      </c>
+      <c r="Q580" s="3">
+        <v>46141.9421412037</v>
+      </c>
+      <c r="R580" s="3">
+        <v>46141.9421412037</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Carla</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Damian</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Alondra</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>942846179</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>carlasolisvaldes@gmail.com</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O581" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P581" s="3">
+        <v>46141.92127314815</v>
+      </c>
+      <c r="Q581" s="3">
+        <v>46141.93805555555</v>
+      </c>
+      <c r="R581" s="3">
+        <v>46141.93805555555</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Josefa</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Dominique</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>981498294</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O582" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P582" s="3">
+        <v>46141.92925925926</v>
+      </c>
+      <c r="Q582" s="3">
+        <v>46141.95179398148</v>
+      </c>
+      <c r="R582" s="3">
+        <v>46141.95179398148</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>991557949</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>claudiobonjovi1990@gmail.com</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O583" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P583" s="3">
+        <v>46141.93803240741</v>
+      </c>
+      <c r="R583" s="3">
+        <v>46141.94197916667</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Nahuel</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>9999999</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>javierapdt@gmail.com</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O584" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P584" s="3">
+        <v>46141.94166666667</v>
+      </c>
+      <c r="Q584" s="3">
+        <v>46141.95818287037</v>
+      </c>
+      <c r="R584" s="3">
+        <v>46141.95818287037</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Sandea</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>964801415</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O585" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P585" s="3">
+        <v>46141.95914351851</v>
+      </c>
+      <c r="Q585" s="3">
+        <v>46141.98612268519</v>
+      </c>
+      <c r="R585" s="3">
+        <v>46141.98612268519</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Cristobal</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>954674516</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>cristobalblu@gmail.com</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O586" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P586" s="3">
+        <v>46141.96186342592</v>
+      </c>
+      <c r="Q586" s="3">
+        <v>46141.97425925926</v>
+      </c>
+      <c r="R586" s="3">
+        <v>46141.97425925926</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Estela</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Rosemary</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>967971809</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>estelaromero.ak@gmail.com</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>9270-2</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O587" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P587" s="3">
+        <v>46141.96890046296</v>
+      </c>
+      <c r="Q587" s="3">
+        <v>46141.99258101852</v>
+      </c>
+      <c r="R587" s="3">
+        <v>46141.99258101852</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>216680324</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>luis</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Eliza</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>56942663568</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>eliza.vidal.infante@live.cl</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>encuestador datodinamico</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O588" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P588" s="3">
+        <v>46141.97024305556</v>
+      </c>
+      <c r="Q588" s="3">
+        <v>46142.00402777777</v>
+      </c>
+      <c r="R588" s="3">
+        <v>46142.00402777777</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>991557949</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>claudiobonjovi1990@gmsil.com</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O589" s="2">
+        <v>46171</v>
+      </c>
+      <c r="P589" s="3">
+        <v>46141.98082175926</v>
+      </c>
+      <c r="R589" s="3">
+        <v>46141.98266203704</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Nelson</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Miriam</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Liss</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>942842865</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>nelsoncordero482@gmail.com</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O590" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P590" s="3">
+        <v>46141.98521990741</v>
+      </c>
+      <c r="Q590" s="3">
+        <v>46142.02505787037</v>
+      </c>
+      <c r="R590" s="3">
+        <v>46142.02503472222</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Ernesto</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>940776832</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>hernestoalnado@gmail.com</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>Cerillos</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O591" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P591" s="3">
+        <v>46141.99025462963</v>
+      </c>
+      <c r="Q591" s="3">
+        <v>46142.01643518519</v>
+      </c>
+      <c r="R591" s="3">
+        <v>46142.01640046296</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>19313240-5</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>95727627</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>praticiamoraless67@gmail.com</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O592" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P592" s="3">
+        <v>46141.99133101852</v>
+      </c>
+      <c r="Q592" s="3">
+        <v>46142.00856481482</v>
+      </c>
+      <c r="R592" s="3">
+        <v>46142.00856481482</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Ximena</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Belén</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>931931415</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O593" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P593" s="3">
+        <v>46141.99547453703</v>
+      </c>
+      <c r="Q593" s="3">
+        <v>46142.0192824074</v>
+      </c>
+      <c r="R593" s="3">
+        <v>46142.01925925926</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>gftj@gyjj.com</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O594" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P594" s="3">
+        <v>46142.00335648148</v>
+      </c>
+      <c r="R594" s="3">
+        <v>46142.00869212963</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Ximena</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Matilda</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>991557949</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>claudiobomjovi1990@gmail.com</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O595" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P595" s="3">
+        <v>46142.01018518519</v>
+      </c>
+      <c r="R595" s="3">
+        <v>46142.01559027778</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Moises</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Pareja</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>972778435</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>moisessmith31@gmail.com</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O596" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P596" s="3">
+        <v>46142.02925925926</v>
+      </c>
+      <c r="Q596" s="3">
+        <v>46142.04768518519</v>
+      </c>
+      <c r="R596" s="3">
+        <v>46142.04766203703</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>8.464.650-4</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Eugenia</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>995827639</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>rechaza@gmail.com</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>CHILLAN</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O597" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P597" s="3">
+        <v>46142.0366550926</v>
+      </c>
+      <c r="Q597" s="3">
+        <v>46142.07069444444</v>
+      </c>
+      <c r="R597" s="3">
+        <v>46142.0706712963</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>alex_29.5@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>0376-4</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O598" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P598" s="3">
+        <v>46142.04672453704</v>
+      </c>
+      <c r="Q598" s="3">
+        <v>46142.07829861112</v>
+      </c>
+      <c r="R598" s="3">
+        <v>46142.07829861112</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>15221550-9</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Griselda Del Carmen Zapata Días</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Alejandro Alberto Salinas Zapata</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>953281591</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>grisellezapata@gmail.com</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>76016305-8</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O599" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P599" s="3">
+        <v>46142.05434027778</v>
+      </c>
+      <c r="Q599" s="3">
+        <v>46142.08575231482</v>
+      </c>
+      <c r="R599" s="3">
+        <v>46142.08575231482</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Lisset</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Florencia</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>973270705</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>roalissetsandoval2@gmail.com</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O600" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P600" s="3">
+        <v>46142.05736111111</v>
+      </c>
+      <c r="Q600" s="3">
+        <v>46142.08401620371</v>
+      </c>
+      <c r="R600" s="3">
+        <v>46142.08401620371</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Paulina Pizarro</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Ágata</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>942209329</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>pizarropaulina57@gmail.com</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O601" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P601" s="3">
+        <v>46142.06248842593</v>
+      </c>
+      <c r="Q601" s="3">
+        <v>46142.10137731482</v>
+      </c>
+      <c r="R601" s="3">
+        <v>46142.10137731482</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Hector</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Aida</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>962561346</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>hector.sanmartin1984@gmail.com</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>9270-2</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O602" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P602" s="3">
+        <v>46142.06280092592</v>
+      </c>
+      <c r="Q602" s="3">
+        <v>46142.09310185185</v>
+      </c>
+      <c r="R602" s="3">
+        <v>46142.09310185185</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>216680324</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Joaquin</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>56981738051</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>gracelagos.duran@gmail.com</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>encuestador datodinamico</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O603" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P603" s="3">
+        <v>46142.07861111111</v>
+      </c>
+      <c r="Q603" s="3">
+        <v>46142.11672453704</v>
+      </c>
+      <c r="R603" s="3">
+        <v>46142.11672453704</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Amalia</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>971676485</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>Clau.room200@gmail.com</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>Santiago centro</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>9270-2</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O604" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P604" s="3">
+        <v>46142.10045138889</v>
+      </c>
+      <c r="Q604" s="3">
+        <v>46142.12478009259</v>
+      </c>
+      <c r="R604" s="3">
+        <v>46142.12476851852</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Alonso</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>esteban</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>andres</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>904553956</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>alonsocuzzi@gmail.com</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>maipu</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O605" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P605" s="3">
+        <v>46142.14655092593</v>
+      </c>
+      <c r="Q605" s="3">
+        <v>46142.16890046296</v>
+      </c>
+      <c r="R605" s="3">
+        <v>46142.16890046296</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Susana</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Ramón</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>992240441</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>romanodr1986@gmail.com</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>9270-3</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O606" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P606" s="3">
+        <v>46142.57710648148</v>
+      </c>
+      <c r="Q606" s="3">
+        <v>46142.62108796297</v>
+      </c>
+      <c r="R606" s="3">
+        <v>46142.62108796297</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Aida</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Hector</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Agustin</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>971008539</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>aidasanmartinvallejos1@gmail.com</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>0376-9</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O607" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P607" s="3">
+        <v>46142.593125</v>
+      </c>
+      <c r="Q607" s="3">
+        <v>46142.6303125</v>
+      </c>
+      <c r="R607" s="3">
+        <v>46142.6303125</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>16274824-6</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Jaime Yáñez</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Viviana piraud</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Isidora Yáñez piraud</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>56972267309</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>J.yanezmontecinos@gmail.com</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>Conac</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O608" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P608" s="3">
+        <v>46142.61384259259</v>
+      </c>
+      <c r="R608" s="3">
+        <v>46142.62085648148</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Ariadne</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Eduards</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Yessenia</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>941821708</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>yesenia.ariadne1993@gmail.com</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>9270-3</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O609" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P609" s="3">
+        <v>46142.63422453703</v>
+      </c>
+      <c r="Q609" s="3">
+        <v>46142.67168981482</v>
+      </c>
+      <c r="R609" s="3">
+        <v>46142.67168981482</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>993578356</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>pailahualcristian@gmail.com</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>0376-10</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O610" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P610" s="3">
+        <v>46142.64590277777</v>
+      </c>
+      <c r="R610" s="3">
+        <v>46142.66032407407</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>184302497</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>973552239</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>sirena.diaz.a@gmail.com</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O611" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P611" s="3">
+        <v>46142.64709490741</v>
+      </c>
+      <c r="Q611" s="3">
+        <v>46142.66631944444</v>
+      </c>
+      <c r="R611" s="3">
+        <v>46142.66631944444</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Erika sagredo</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Martina Sagredo</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>945216601</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>erikayr3@gmail.com</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O612" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P612" s="3">
+        <v>46142.65035879629</v>
+      </c>
+      <c r="R612" s="3">
+        <v>46142.66211805555</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>956414467</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>caricerpa@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O613" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P613" s="3">
+        <v>46142.65700231482</v>
+      </c>
+      <c r="R613" s="3">
+        <v>46142.69306712963</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>993578356</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>pailahualcristian@gmail.com</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>0376-10</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O614" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P614" s="3">
+        <v>46142.66049768518</v>
+      </c>
+      <c r="Q614" s="3">
+        <v>46142.68484953704</v>
+      </c>
+      <c r="R614" s="3">
+        <v>46142.68484953704</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Erika Sagredo</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Martina Sagredo</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>945216601</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>erikayr3@gmail.com</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O615" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P615" s="3">
+        <v>46142.66297453704</v>
+      </c>
+      <c r="Q615" s="3">
+        <v>46142.67984953704</v>
+      </c>
+      <c r="R615" s="3">
+        <v>46142.67984953704</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Facundo</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>987006605</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>fran.jorquera.valdivia@gmail.com</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O616" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P616" s="3">
+        <v>46142.67943287037</v>
+      </c>
+      <c r="Q616" s="3">
+        <v>46142.70636574074</v>
+      </c>
+      <c r="R616" s="3">
+        <v>46142.70636574074</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>999641492</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>ivarro112370@gmail.com</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>Qulicura</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O617" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P617" s="3">
+        <v>46142.69354166667</v>
+      </c>
+      <c r="R617" s="3">
+        <v>46142.70815972222</v>
       </c>
     </row>
   </sheetData>

--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R617"/>
+  <dimension ref="A1:R647"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="15" max="15" width="20.7109375" style="2" customWidth="1"/>
@@ -30764,6 +30764,11 @@
           <t>Waldo</t>
         </is>
       </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Ninoska</t>
+        </is>
+      </c>
       <c r="I489" t="inlineStr">
         <is>
           <t>965022493</t>
@@ -38636,8 +38641,11 @@
       <c r="P613" s="3">
         <v>46142.65700231482</v>
       </c>
+      <c r="Q613" s="3">
+        <v>46142.73483796296</v>
+      </c>
       <c r="R613" s="3">
-        <v>46142.69306712963</v>
+        <v>46142.73483796296</v>
       </c>
     </row>
     <row r="614">
@@ -38884,8 +38892,1974 @@
       <c r="P617" s="3">
         <v>46142.69354166667</v>
       </c>
+      <c r="Q617" s="3">
+        <v>46142.70998842592</v>
+      </c>
       <c r="R617" s="3">
-        <v>46142.70815972222</v>
+        <v>46142.70998842592</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>17244539k</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Byron</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>958278791</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>momentosprint.correo@gmail.com</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O618" s="2">
+        <v>46141</v>
+      </c>
+      <c r="P618" s="3">
+        <v>46142.70800925926</v>
+      </c>
+      <c r="Q618" s="3">
+        <v>46142.73719907408</v>
+      </c>
+      <c r="R618" s="3">
+        <v>46142.73719907408</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>982696981</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>veritolopez1966@gmail.com</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O619" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P619" s="3">
+        <v>46142.71646990741</v>
+      </c>
+      <c r="R619" s="3">
+        <v>46142.72030092592</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>213099035</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Renato</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>977477072</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>isicaceresmartinez@gmail.com</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O620" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P620" s="3">
+        <v>46142.71984953704</v>
+      </c>
+      <c r="R620" s="3">
+        <v>46142.79954861111</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Cristian Ortiz Toro</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>9-79735207</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>ortiz.cristian.toro@gmail.com</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O621" s="2">
+        <v>46143</v>
+      </c>
+      <c r="P621" s="3">
+        <v>46142.72434027778</v>
+      </c>
+      <c r="R621" s="3">
+        <v>46143.77266203704</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>13081719-K</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Camila Aguilera</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Sonia del Carmen</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Daniel Enrique</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Gabriel Alonso</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>979521340</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>c.camila.aguilera@gmail.com</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O622" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P622" s="3">
+        <v>46142.73483796296</v>
+      </c>
+      <c r="Q622" s="3">
+        <v>46142.75884259259</v>
+      </c>
+      <c r="R622" s="3">
+        <v>46142.75884259259</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Estrella</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Agustin</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>966712998</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>maathii.lol@gmail.com</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O623" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P623" s="3">
+        <v>46142.73495370371</v>
+      </c>
+      <c r="Q623" s="3">
+        <v>46142.75990740741</v>
+      </c>
+      <c r="R623" s="3">
+        <v>46142.75990740741</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>13081718k</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Catherine gonzalez</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Rayen</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>69897495</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>cathypg13@gmail.com</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O624" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P624" s="3">
+        <v>46142.73496527778</v>
+      </c>
+      <c r="Q624" s="3">
+        <v>46142.77568287037</v>
+      </c>
+      <c r="R624" s="3">
+        <v>46142.77568287037</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Yerelin</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Bastian</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>974015077</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O625" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P625" s="3">
+        <v>46142.74815972222</v>
+      </c>
+      <c r="Q625" s="3">
+        <v>46142.77163194444</v>
+      </c>
+      <c r="R625" s="3">
+        <v>46142.77162037037</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>106598088</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Leticia</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>944018826</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>carloszuiga851@yahoo.com</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O626" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P626" s="3">
+        <v>46142.75349537037</v>
+      </c>
+      <c r="Q626" s="3">
+        <v>46142.77050925926</v>
+      </c>
+      <c r="R626" s="3">
+        <v>46142.77050925926</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Rafaella</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>amanda.guerra.barria@gmail.com</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>0376-11</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O627" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P627" s="3">
+        <v>46142.7536574074</v>
+      </c>
+      <c r="Q627" s="3">
+        <v>46142.77871527777</v>
+      </c>
+      <c r="R627" s="3">
+        <v>46142.77871527777</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Danissa</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>968164021</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>danissamanriquez38@gmail.com</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>Conchalí</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O628" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P628" s="3">
+        <v>46142.77914351852</v>
+      </c>
+      <c r="Q628" s="3">
+        <v>46142.81106481481</v>
+      </c>
+      <c r="R628" s="3">
+        <v>46142.81106481481</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Jose Gonzalez</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Roxana Arévalo</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Claudia Arévalo</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Agustina González</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>968503698</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>jm.gonzalez046@gmail.com</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O629" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P629" s="3">
+        <v>46142.78719907408</v>
+      </c>
+      <c r="Q629" s="3">
+        <v>46142.81898148148</v>
+      </c>
+      <c r="R629" s="3">
+        <v>46142.81898148148</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>estela</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>967583643</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>alejandragomez@gmial.com</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>maipu</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O630" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P630" s="3">
+        <v>46142.8016087963</v>
+      </c>
+      <c r="Q630" s="3">
+        <v>46142.82771990741</v>
+      </c>
+      <c r="R630" s="3">
+        <v>46142.82771990741</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Marisol</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Alberto</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Yoselin</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>920726862</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>nolodio@gmail.com</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O631" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P631" s="3">
+        <v>46142.81996527778</v>
+      </c>
+      <c r="Q631" s="3">
+        <v>46142.84710648148</v>
+      </c>
+      <c r="R631" s="3">
+        <v>46142.84710648148</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>965644737</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>Mauriciopalacioxx@gmail.com</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O632" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P632" s="3">
+        <v>46142.82792824075</v>
+      </c>
+      <c r="Q632" s="3">
+        <v>46142.86813657408</v>
+      </c>
+      <c r="R632" s="3">
+        <v>46142.86813657408</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Flor</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Alberto</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>56968498437</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>oyarzun.cristian.m@gmail.com</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>Lo prado</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O633" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P633" s="3">
+        <v>46142.82893518519</v>
+      </c>
+      <c r="Q633" s="3">
+        <v>46142.863125</v>
+      </c>
+      <c r="R633" s="3">
+        <v>46142.863125</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Constanza</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>934535857</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>javiii.sp88@gmail.com</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>0376-12</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O634" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P634" s="3">
+        <v>46142.83086805556</v>
+      </c>
+      <c r="Q634" s="3">
+        <v>46142.87097222223</v>
+      </c>
+      <c r="R634" s="3">
+        <v>46142.87097222223</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Verónica</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>982696981</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>veritolopez1966@gmail.com</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O635" s="2">
+        <v>46135</v>
+      </c>
+      <c r="P635" s="3">
+        <v>46142.86496527778</v>
+      </c>
+      <c r="Q635" s="3">
+        <v>46142.89046296296</v>
+      </c>
+      <c r="R635" s="3">
+        <v>46142.89046296296</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Eugenia</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Isabela</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>945385634</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>eugeniavelez1@gmail.com</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O636" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P636" s="3">
+        <v>46142.86988425926</v>
+      </c>
+      <c r="Q636" s="3">
+        <v>46142.90114583333</v>
+      </c>
+      <c r="R636" s="3">
+        <v>46142.90114583333</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Valeria-  javier-José Tomas- Amapola</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Jose tomas</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Amapola</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>56058087</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>valeriavalenzuelajerez@gmail.com</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O637" s="2">
+        <v>46143</v>
+      </c>
+      <c r="P637" s="3">
+        <v>46142.87113425926</v>
+      </c>
+      <c r="Q637" s="3">
+        <v>46142.93508101851</v>
+      </c>
+      <c r="R637" s="3">
+        <v>46142.93508101851</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Maylen</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Lardy</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>940612507</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>lardypailahual@gmail.com</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>Cerrillos</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O638" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P638" s="3">
+        <v>46142.88689814815</v>
+      </c>
+      <c r="Q638" s="3">
+        <v>46142.92021990741</v>
+      </c>
+      <c r="R638" s="3">
+        <v>46142.92021990741</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>21156205-6</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Emiliano</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>956545787</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>emilianosinfuenmtes@gmail.com</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O639" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P639" s="3">
+        <v>46142.90173611111</v>
+      </c>
+      <c r="Q639" s="3">
+        <v>46142.92631944444</v>
+      </c>
+      <c r="R639" s="3">
+        <v>46142.92630787037</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Damaris</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Mariano</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>944444056</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>damaris.gonzalez.g@gmail.con</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O640" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P640" s="3">
+        <v>46142.9178125</v>
+      </c>
+      <c r="Q640" s="3">
+        <v>46142.92873842592</v>
+      </c>
+      <c r="R640" s="3">
+        <v>46142.92873842592</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2115605-6</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Rocío</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Martina</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>950337522</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>rociopaz1@gmail.com</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O641" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P641" s="3">
+        <v>46142.92895833333</v>
+      </c>
+      <c r="Q641" s="3">
+        <v>46142.96302083333</v>
+      </c>
+      <c r="R641" s="3">
+        <v>46142.96302083333</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Tamara</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Hernan</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>chikititamia@gmail.com</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>Cerro navia</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>0376-13</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O642" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P642" s="3">
+        <v>46142.93076388889</v>
+      </c>
+      <c r="Q642" s="3">
+        <v>46142.96165509259</v>
+      </c>
+      <c r="R642" s="3">
+        <v>46142.96165509259</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Danilo</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>930692205</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>mariana1994.cr@gmail.com</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O643" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P643" s="3">
+        <v>46142.93890046296</v>
+      </c>
+      <c r="Q643" s="3">
+        <v>46142.96038194445</v>
+      </c>
+      <c r="R643" s="3">
+        <v>46142.96038194445</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Gaspar</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Leonardo</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>996725715</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>gloria.parada@gmail.com</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O644" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P644" s="3">
+        <v>46142.94168981482</v>
+      </c>
+      <c r="Q644" s="3">
+        <v>46142.97112268519</v>
+      </c>
+      <c r="R644" s="3">
+        <v>46142.97112268519</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>18467644-3</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>cristobal</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>956287848</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>cristobal.munoz.caceres@gmail.com</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>las condes</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>7644</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O645" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P645" s="3">
+        <v>46142.96340277778</v>
+      </c>
+      <c r="R645" s="3">
+        <v>46142.97157407408</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>950257224</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>bustamantepatricioharling@gmail.com</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>Quinta normal</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>0376-14</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O646" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P646" s="3">
+        <v>46142.98422453704</v>
+      </c>
+      <c r="Q646" s="3">
+        <v>46143.00820601852</v>
+      </c>
+      <c r="R646" s="3">
+        <v>46143.00820601852</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Steven</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Anuar</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Delu</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>María Angela</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>975626206</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>Renca</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>9270-4</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O647" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P647" s="3">
+        <v>46142.99442129629</v>
+      </c>
+      <c r="Q647" s="3">
+        <v>46143.02815972222</v>
+      </c>
+      <c r="R647" s="3">
+        <v>46143.02813657407</v>
       </c>
     </row>
   </sheetData>

--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R731"/>
+  <dimension ref="A1:R759"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="15" max="15" width="20.7109375" style="2" customWidth="1"/>
@@ -45529,8 +45529,11 @@
       <c r="P719" s="3">
         <v>46147.01715277778</v>
       </c>
+      <c r="Q719" s="3">
+        <v>46147.77201388888</v>
+      </c>
       <c r="R719" s="3">
-        <v>46147.76423611111</v>
+        <v>46147.77201388888</v>
       </c>
     </row>
     <row r="720">
@@ -45856,6 +45859,16 @@
           <t>191656237</t>
         </is>
       </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>barbara</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>gianfranco</t>
+        </is>
+      </c>
       <c r="I725" t="inlineStr">
         <is>
           <t>9999</t>
@@ -45864,6 +45877,16 @@
       <c r="J725" t="inlineStr">
         <is>
           <t>bfernandez@datodinamico.cl</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>recoleta</t>
         </is>
       </c>
       <c r="M725" t="inlineStr">
@@ -45883,7 +45906,7 @@
         <v>46147.7237037037</v>
       </c>
       <c r="R725" s="3">
-        <v>46147.76622685185</v>
+        <v>46148.64532407407</v>
       </c>
     </row>
     <row r="726">
@@ -45944,7 +45967,7 @@
         <v>46147.72542824074</v>
       </c>
       <c r="R726" s="3">
-        <v>46147.73065972222</v>
+        <v>46147.84631944445</v>
       </c>
     </row>
     <row r="727">
@@ -46206,8 +46229,11 @@
       <c r="P730" s="3">
         <v>46147.75293981482</v>
       </c>
+      <c r="Q730" s="3">
+        <v>46147.78539351852</v>
+      </c>
       <c r="R730" s="3">
-        <v>46147.76199074074</v>
+        <v>46147.78539351852</v>
       </c>
     </row>
     <row r="731">
@@ -46272,8 +46298,1725 @@
       <c r="P731" s="3">
         <v>46147.75423611111</v>
       </c>
+      <c r="Q731" s="3">
+        <v>46147.78268518519</v>
+      </c>
       <c r="R731" s="3">
-        <v>46147.76261574074</v>
+        <v>46147.78268518519</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>95729 7667</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>kathi@live.cl</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O732" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P732" s="3">
+        <v>46147.77251157408</v>
+      </c>
+      <c r="Q732" s="3">
+        <v>46147.79947916667</v>
+      </c>
+      <c r="R732" s="3">
+        <v>46147.79947916667</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>20568285-6</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Sara Alvear</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Diego Plaza</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Catalina Plaza</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Pedro Plaza</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>977339289</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>sarybb83@gmail.com</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O733" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P733" s="3">
+        <v>46147.77332175926</v>
+      </c>
+      <c r="Q733" s="3">
+        <v>46147.84125</v>
+      </c>
+      <c r="R733" s="3">
+        <v>46147.84125</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>213099035</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Bastian</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>949034499</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>camilita1603@gmail.com</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>Pudahuel</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O734" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P734" s="3">
+        <v>46147.79555555555</v>
+      </c>
+      <c r="Q734" s="3">
+        <v>46147.81766203704</v>
+      </c>
+      <c r="R734" s="3">
+        <v>46147.81766203704</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>202410367</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Sebastian Alund</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Fabiana Cantilo</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>933533329</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>sebastianlovayen@outlook.com</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>0367</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O735" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P735" s="3">
+        <v>46147.82731481481</v>
+      </c>
+      <c r="Q735" s="3">
+        <v>46147.99678240741</v>
+      </c>
+      <c r="R735" s="3">
+        <v>46147.99678240741</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>930872103</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>darlingrebolledo827@gmail.com</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>La cisterna</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>9270-3</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O736" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P736" s="3">
+        <v>46147.83100694444</v>
+      </c>
+      <c r="Q736" s="3">
+        <v>46147.84984953704</v>
+      </c>
+      <c r="R736" s="3">
+        <v>46147.84984953704</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Aylin</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>958716914</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>Aylinrojas337@gmail.com</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O737" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P737" s="3">
+        <v>46147.89228009259</v>
+      </c>
+      <c r="Q737" s="3">
+        <v>46147.94623842592</v>
+      </c>
+      <c r="R737" s="3">
+        <v>46147.94622685185</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Antonia</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>antosanchezas841@gmail.com</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O738" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P738" s="3">
+        <v>46147.94635416666</v>
+      </c>
+      <c r="R738" s="3">
+        <v>46147.95976851851</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>125228445</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>mmejias1973@yahoo.cl</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O739" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P739" s="3">
+        <v>46147.95002314815</v>
+      </c>
+      <c r="Q739" s="3">
+        <v>46148.15695601852</v>
+      </c>
+      <c r="R739" s="3">
+        <v>46148.15695601852</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>antosanchezas841@gmail.com</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O740" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P740" s="3">
+        <v>46147.98179398148</v>
+      </c>
+      <c r="R740" s="3">
+        <v>46147.98318287038</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>111111111111</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>111111111</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>11111111111</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>PRUEBA@PRUEBA.CL</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>11111</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>11111111111111</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O741" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P741" s="3">
+        <v>46147.98318287038</v>
+      </c>
+      <c r="R741" s="3">
+        <v>46147.98767361111</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Carina</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Maximiliano</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Fabricio</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>982130913</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>carina1616.1987@gmail.com</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>La pintana</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O742" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P742" s="3">
+        <v>46148.02159722222</v>
+      </c>
+      <c r="Q742" s="3">
+        <v>46148.05199074074</v>
+      </c>
+      <c r="R742" s="3">
+        <v>46148.05195601852</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>12789438-8</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Ana fariña</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>950887663</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>anafabi.faria.6@gmail.com</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>Ana fariña</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O743" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P743" s="3">
+        <v>46148.03469907407</v>
+      </c>
+      <c r="R743" s="3">
+        <v>46148.07763888889</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Antonia</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>antosanchezas841@gmail.com</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O744" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P744" s="3">
+        <v>46148.03700231481</v>
+      </c>
+      <c r="Q744" s="3">
+        <v>46148.04678240741</v>
+      </c>
+      <c r="R744" s="3">
+        <v>46148.04674768518</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Hirina</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>felipearturo@inacapmail.com</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O745" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P745" s="3">
+        <v>46148.04888888889</v>
+      </c>
+      <c r="Q745" s="3">
+        <v>46148.06162037037</v>
+      </c>
+      <c r="R745" s="3">
+        <v>46148.06158564815</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Jeanette</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Elias</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Dania</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>985093029</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>jeanette.olmedo77@gmail.com</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O746" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P746" s="3">
+        <v>46148.07048611112</v>
+      </c>
+      <c r="Q746" s="3">
+        <v>46148.10331018519</v>
+      </c>
+      <c r="R746" s="3">
+        <v>46148.10331018519</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Camila Gutiérrez</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Ángel Gutiérrez</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Sandra Faúndez</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Alejandra Gutiérrez</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>981782193</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>camilagutiwerezfaundez@gmail.com</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O747" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P747" s="3">
+        <v>46148.07258101852</v>
+      </c>
+      <c r="Q747" s="3">
+        <v>46148.09637731481</v>
+      </c>
+      <c r="R747" s="3">
+        <v>46148.09637731481</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Romina</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Amelia</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>995902817</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>romi.barbagelata@gmail.com</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O748" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P748" s="3">
+        <v>46148.09489583333</v>
+      </c>
+      <c r="Q748" s="3">
+        <v>46148.12075231482</v>
+      </c>
+      <c r="R748" s="3">
+        <v>46148.12075231482</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>978850325</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>alexanderbenavidesals@gmail.com</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>4290</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O749" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P749" s="3">
+        <v>46148.11864583333</v>
+      </c>
+      <c r="Q749" s="3">
+        <v>46148.13988425926</v>
+      </c>
+      <c r="R749" s="3">
+        <v>46148.13988425926</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Margarita</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Juan carlos</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Guadalupa</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>974476355</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>margaritaduranc16@gmail.com</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O750" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P750" s="3">
+        <v>46148.12877314815</v>
+      </c>
+      <c r="Q750" s="3">
+        <v>46148.15601851852</v>
+      </c>
+      <c r="R750" s="3">
+        <v>46148.15601851852</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Paulina</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Hector</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Noelia</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Belen</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>988562258</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>paulaza@live.cl</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O751" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P751" s="3">
+        <v>46148.12982638889</v>
+      </c>
+      <c r="Q751" s="3">
+        <v>46148.17927083334</v>
+      </c>
+      <c r="R751" s="3">
+        <v>46148.17927083334</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>10102181-5</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>998920888</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>fernanda.anai.mora@gmail.com</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O752" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P752" s="3">
+        <v>46148.13240740741</v>
+      </c>
+      <c r="R752" s="3">
+        <v>46148.14884259259</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>10102181-5</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Marjorie</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>anai</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>998920888</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>fernanda.anai.mora@gmail.com</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>lo prado</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O753" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P753" s="3">
+        <v>46148.14890046296</v>
+      </c>
+      <c r="Q753" s="3">
+        <v>46148.19263888889</v>
+      </c>
+      <c r="R753" s="3">
+        <v>46148.19263888889</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>17286752-9</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Hernan</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Matilde</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>964946167</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>euevelopez@gmail.com</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>HUECHURABA</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O754" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P754" s="3">
+        <v>46148.16171296296</v>
+      </c>
+      <c r="Q754" s="3">
+        <v>46148.19428240741</v>
+      </c>
+      <c r="R754" s="3">
+        <v>46148.19428240741</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>125228445</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Maite</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>mmejias1973@yahoo.cl</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O755" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P755" s="3">
+        <v>46148.20069444444</v>
+      </c>
+      <c r="Q755" s="3">
+        <v>46148.22878472222</v>
+      </c>
+      <c r="R755" s="3">
+        <v>46148.22878472222</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>125238445</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>978350819</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>mmejias1973@yahoo.cl</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O756" s="2">
+        <v>46147</v>
+      </c>
+      <c r="P756" s="3">
+        <v>46148.23722222222</v>
+      </c>
+      <c r="Q756" s="3">
+        <v>46148.25457175926</v>
+      </c>
+      <c r="R756" s="3">
+        <v>46148.25457175926</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Andrés</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>982353017</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>mariana.pasten.g@gmail.com</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O757" s="2">
+        <v>46148</v>
+      </c>
+      <c r="P757" s="3">
+        <v>46148.66172453704</v>
+      </c>
+      <c r="Q757" s="3">
+        <v>46148.67400462963</v>
+      </c>
+      <c r="R757" s="3">
+        <v>46148.67400462963</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2080647977</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>pedropablogato@gmail.com</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>pedropablogato@gmail.com</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>4797</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O758" s="2">
+        <v>46148</v>
+      </c>
+      <c r="P758" s="3">
+        <v>46148.71138888889</v>
+      </c>
+      <c r="R758" s="3">
+        <v>46148.71928240741</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>18.050.509-1</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Alvaro</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Apolonia</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>56966603557</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>alvarotorres.ps@gmail.com</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O759" s="2">
+        <v>46148</v>
+      </c>
+      <c r="P759" s="3">
+        <v>46148.73949074074</v>
+      </c>
+      <c r="Q759" s="3">
+        <v>46148.77854166667</v>
+      </c>
+      <c r="R759" s="3">
+        <v>46148.77854166667</v>
       </c>
     </row>
   </sheetData>

--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R759"/>
+  <dimension ref="A1:R767"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="15" max="15" width="20.7109375" style="2" customWidth="1"/>
@@ -45912,47 +45912,42 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>52636363-4</t>
+          <t>20241036-7</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Nicolas Soto</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Karen riffo</t>
-        </is>
-      </c>
-      <c r="D726" t="inlineStr">
-        <is>
-          <t>Trinidad</t>
+          <t>Emily Soto Pradenas</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>837364</t>
+          <t>965668134</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>prueba@hshshs.com</t>
+          <t>nicolas.soto.soto@outlook.com</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="M726" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="N726" t="inlineStr">
@@ -45964,51 +45959,64 @@
         <v>46147</v>
       </c>
       <c r="P726" s="3">
-        <v>46147.72542824074</v>
+        <v>46147.73053240741</v>
+      </c>
+      <c r="Q726" s="3">
+        <v>46147.76380787037</v>
       </c>
       <c r="R726" s="3">
-        <v>46147.84631944445</v>
+        <v>46147.76380787037</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>20241036-7</t>
+          <t>19172396-1</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Nicolas Soto</t>
+          <t>Franco</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Emily Soto Pradenas</t>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>965668134</t>
+          <t>56987737635</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>nicolas.soto.soto@outlook.com</t>
+          <t>fvenegas1512@gmail.com</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="M727" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>396</t>
         </is>
       </c>
       <c r="N727" t="inlineStr">
@@ -46017,52 +46025,52 @@
         </is>
       </c>
       <c r="O727" s="2">
-        <v>46147</v>
+        <v>45658</v>
       </c>
       <c r="P727" s="3">
-        <v>46147.73053240741</v>
+        <v>46147.73855324074</v>
       </c>
       <c r="Q727" s="3">
-        <v>46147.76380787037</v>
+        <v>46147.75910879629</v>
       </c>
       <c r="R727" s="3">
-        <v>46147.76380787037</v>
+        <v>46147.75910879629</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>19172396-1</t>
+          <t>175458975</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Franco</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Alejandra</t>
+          <t>Hector</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Anibal</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>56987737635</t>
+          <t>931124228</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>fvenegas1512@gmail.com</t>
+          <t>vergararojash@gmail.com</t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
@@ -46072,12 +46080,12 @@
       </c>
       <c r="L728" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Puente alto</t>
         </is>
       </c>
       <c r="M728" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>897</t>
         </is>
       </c>
       <c r="N728" t="inlineStr">
@@ -46086,136 +46094,136 @@
         </is>
       </c>
       <c r="O728" s="2">
-        <v>45658</v>
+        <v>45292</v>
       </c>
       <c r="P728" s="3">
-        <v>46147.73855324074</v>
+        <v>46147.74388888889</v>
       </c>
       <c r="Q728" s="3">
-        <v>46147.75910879629</v>
+        <v>46147.76350694444</v>
       </c>
       <c r="R728" s="3">
-        <v>46147.75910879629</v>
+        <v>46147.76350694444</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>175458975</t>
+          <t>160334290</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Guillermo</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Hector</t>
+          <t>Mabel</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Anibal</t>
+          <t>Patrcio</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>931124228</t>
+          <t>957469697</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>vergararojash@gmail.com</t>
+          <t>gmobenavides10@gmail.com</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L729" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="M729" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="N729" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O729" s="2">
-        <v>45292</v>
+        <v>46147</v>
       </c>
       <c r="P729" s="3">
-        <v>46147.74388888889</v>
+        <v>46147.75293981482</v>
       </c>
       <c r="Q729" s="3">
-        <v>46147.76350694444</v>
+        <v>46147.78539351852</v>
       </c>
       <c r="R729" s="3">
-        <v>46147.76350694444</v>
+        <v>46147.78539351852</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>160334290</t>
+          <t>213099035</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Guillermo</t>
+          <t>María Cecilia</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Mabel</t>
+          <t>Ignacio</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Patrcio</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>957469697</t>
+          <t>991780315</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>gmobenavides10@gmail.com</t>
+          <t>mceciliabarrientos@gmail.com</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L730" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>La reina</t>
         </is>
       </c>
       <c r="M730" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="N730" t="inlineStr">
@@ -46227,113 +46235,113 @@
         <v>46147</v>
       </c>
       <c r="P730" s="3">
-        <v>46147.75293981482</v>
+        <v>46147.75423611111</v>
       </c>
       <c r="Q730" s="3">
-        <v>46147.78539351852</v>
+        <v>46147.78268518519</v>
       </c>
       <c r="R730" s="3">
-        <v>46147.78539351852</v>
+        <v>46147.78268518519</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>213099035</t>
+          <t>175682163</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>María Cecilia</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Ignacio</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Emilia</t>
-        </is>
-      </c>
-      <c r="E731" t="inlineStr">
-        <is>
-          <t>Magdalena</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>991780315</t>
+          <t>95729 7667</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>mceciliabarrientos@gmail.com</t>
+          <t>kathi@live.cl</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L731" t="inlineStr">
         <is>
-          <t>La reina</t>
+          <t>Viña del mar</t>
         </is>
       </c>
       <c r="M731" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="N731" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O731" s="2">
         <v>46147</v>
       </c>
       <c r="P731" s="3">
-        <v>46147.75423611111</v>
+        <v>46147.77251157408</v>
       </c>
       <c r="Q731" s="3">
-        <v>46147.78268518519</v>
+        <v>46147.79947916667</v>
       </c>
       <c r="R731" s="3">
-        <v>46147.78268518519</v>
+        <v>46147.79947916667</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>175682163</t>
+          <t>20568285-6</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Sara Alvear</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Diego Plaza</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Catalina Plaza</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Pedro Plaza</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>95729 7667</t>
+          <t>977339289</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>kathi@live.cl</t>
+          <t>sarybb83@gmail.com</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
@@ -46343,12 +46351,12 @@
       </c>
       <c r="L732" t="inlineStr">
         <is>
-          <t>Viña del mar</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="M732" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="N732" t="inlineStr">
@@ -46360,226 +46368,221 @@
         <v>46147</v>
       </c>
       <c r="P732" s="3">
-        <v>46147.77251157408</v>
+        <v>46147.77332175926</v>
       </c>
       <c r="Q732" s="3">
-        <v>46147.79947916667</v>
+        <v>46147.84125</v>
       </c>
       <c r="R732" s="3">
-        <v>46147.79947916667</v>
+        <v>46147.84125</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>20568285-6</t>
+          <t>213099035</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Sara Alvear</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Diego Plaza</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Catalina Plaza</t>
+          <t>Bastian</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Pedro Plaza</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>977339289</t>
+          <t>949034499</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>sarybb83@gmail.com</t>
+          <t>camilita1603@gmail.com</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="M733" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="N733" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O733" s="2">
         <v>46147</v>
       </c>
       <c r="P733" s="3">
-        <v>46147.77332175926</v>
+        <v>46147.79555555555</v>
       </c>
       <c r="Q733" s="3">
-        <v>46147.84125</v>
+        <v>46147.81766203704</v>
       </c>
       <c r="R733" s="3">
-        <v>46147.84125</v>
+        <v>46147.81766203704</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>213099035</t>
+          <t>202410367</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Sebastian Alund</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Joel</t>
-        </is>
-      </c>
-      <c r="D734" t="inlineStr">
-        <is>
-          <t>Bastian</t>
-        </is>
-      </c>
-      <c r="E734" t="inlineStr">
-        <is>
-          <t>Lucas</t>
+          <t>Fabiana Cantilo</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>949034499</t>
+          <t>933533329</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>camilita1603@gmail.com</t>
+          <t>sebastianlovayen@outlook.com</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="M734" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="N734" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O734" s="2">
         <v>46147</v>
       </c>
       <c r="P734" s="3">
-        <v>46147.79555555555</v>
+        <v>46147.82731481481</v>
       </c>
       <c r="Q734" s="3">
-        <v>46147.81766203704</v>
+        <v>46147.99678240741</v>
       </c>
       <c r="R734" s="3">
-        <v>46147.81766203704</v>
+        <v>46147.99678240741</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>202410367</t>
+          <t>18959270-1</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Sebastian Alund</t>
+          <t>María</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Fabiana Cantilo</t>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Matias</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>933533329</t>
+          <t>930872103</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>sebastianlovayen@outlook.com</t>
+          <t>darlingrebolledo827@gmail.com</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L735" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>La cisterna</t>
         </is>
       </c>
       <c r="M735" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>9270-3</t>
         </is>
       </c>
       <c r="N735" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O735" s="2">
         <v>46147</v>
       </c>
       <c r="P735" s="3">
-        <v>46147.82731481481</v>
+        <v>46147.83100694444</v>
       </c>
       <c r="Q735" s="3">
-        <v>46147.99678240741</v>
+        <v>46147.84984953704</v>
       </c>
       <c r="R735" s="3">
-        <v>46147.99678240741</v>
+        <v>46147.84984953704</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>18959270-1</t>
+          <t>175682163</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>María</t>
+          <t>Aylin</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Patricio</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -46587,47 +46590,52 @@
           <t>Matias</t>
         </is>
       </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>930872103</t>
+          <t>958716914</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>darlingrebolledo827@gmail.com</t>
+          <t>Aylinrojas337@gmail.com</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L736" t="inlineStr">
         <is>
-          <t>La cisterna</t>
+          <t>Viña del mar</t>
         </is>
       </c>
       <c r="M736" t="inlineStr">
         <is>
-          <t>9270-3</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="N736" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O736" s="2">
         <v>46147</v>
       </c>
       <c r="P736" s="3">
-        <v>46147.83100694444</v>
+        <v>46147.89228009259</v>
       </c>
       <c r="Q736" s="3">
-        <v>46147.84984953704</v>
+        <v>46147.94623842592</v>
       </c>
       <c r="R736" s="3">
-        <v>46147.84984953704</v>
+        <v>46147.94622685185</v>
       </c>
     </row>
     <row r="737">
@@ -46638,32 +46646,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Aylin</t>
+          <t>Antonia</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Matias</t>
-        </is>
-      </c>
-      <c r="E737" t="inlineStr">
-        <is>
-          <t>Benjamin</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>958716914</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>Aylinrojas337@gmail.com</t>
+          <t>antosanchezas841@gmail.com</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
@@ -46673,7 +46676,7 @@
       </c>
       <c r="L737" t="inlineStr">
         <is>
-          <t>Viña del mar</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="M737" t="inlineStr">
@@ -46683,66 +46686,53 @@
       </c>
       <c r="N737" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O737" s="2">
         <v>46147</v>
       </c>
       <c r="P737" s="3">
-        <v>46147.89228009259</v>
-      </c>
-      <c r="Q737" s="3">
-        <v>46147.94623842592</v>
+        <v>46147.94635416666</v>
       </c>
       <c r="R737" s="3">
-        <v>46147.94622685185</v>
+        <v>46147.95976851851</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>175682163</t>
+          <t>125228445</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Antonia</t>
-        </is>
-      </c>
-      <c r="C738" t="inlineStr">
-        <is>
-          <t>Irma</t>
-        </is>
-      </c>
-      <c r="D738" t="inlineStr">
-        <is>
-          <t>Lucas</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>99999999</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>antosanchezas841@gmail.com</t>
+          <t>mmejias1973@yahoo.cl</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L738" t="inlineStr">
         <is>
-          <t>Valparaiso</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="M738" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>844</t>
         </is>
       </c>
       <c r="N738" t="inlineStr">
@@ -46754,21 +46744,19 @@
         <v>46147</v>
       </c>
       <c r="P738" s="3">
-        <v>46147.94635416666</v>
+        <v>46147.95002314815</v>
+      </c>
+      <c r="Q738" s="3">
+        <v>46148.15695601852</v>
       </c>
       <c r="R738" s="3">
-        <v>46147.95976851851</v>
+        <v>46148.15695601852</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>125228445</t>
-        </is>
-      </c>
-      <c r="B739" t="inlineStr">
-        <is>
-          <t>Jose</t>
+          <t>175682163</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -46778,22 +46766,12 @@
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>mmejias1973@yahoo.cl</t>
-        </is>
-      </c>
-      <c r="K739" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="L739" t="inlineStr">
-        <is>
-          <t>Talca</t>
+          <t>antosanchezas841@gmail.com</t>
         </is>
       </c>
       <c r="M739" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N739" t="inlineStr">
@@ -46805,34 +46783,61 @@
         <v>46147</v>
       </c>
       <c r="P739" s="3">
-        <v>46147.95002314815</v>
-      </c>
-      <c r="Q739" s="3">
-        <v>46148.15695601852</v>
+        <v>46147.98179398148</v>
       </c>
       <c r="R739" s="3">
-        <v>46148.15695601852</v>
+        <v>46147.98318287038</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>175682163</t>
+          <t>105318464</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Carina</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Maximiliano</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Fabricio</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>99999999</t>
+          <t>982130913</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>antosanchezas841@gmail.com</t>
+          <t>carina1616.1987@gmail.com</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>La pintana</t>
         </is>
       </c>
       <c r="M740" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="N740" t="inlineStr">
@@ -46844,51 +46849,49 @@
         <v>46147</v>
       </c>
       <c r="P740" s="3">
-        <v>46147.98179398148</v>
+        <v>46148.02159722222</v>
+      </c>
+      <c r="Q740" s="3">
+        <v>46148.05199074074</v>
       </c>
       <c r="R740" s="3">
-        <v>46147.98318287038</v>
+        <v>46148.05195601852</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>111111111111</t>
+          <t>12789438-8</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>111111111</t>
-        </is>
-      </c>
-      <c r="C741" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Ana fariña</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>11111111111</t>
+          <t>950887663</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>PRUEBA@PRUEBA.CL</t>
+          <t>anafabi.faria.6@gmail.com</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L741" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="M741" t="inlineStr">
         <is>
-          <t>11111111111111</t>
+          <t>Ana fariña</t>
         </is>
       </c>
       <c r="N741" t="inlineStr">
@@ -46900,61 +46903,56 @@
         <v>46147</v>
       </c>
       <c r="P741" s="3">
-        <v>46147.98318287038</v>
+        <v>46148.03469907407</v>
       </c>
       <c r="R741" s="3">
-        <v>46147.98767361111</v>
+        <v>46148.07763888889</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>105318464</t>
+          <t>175682163</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Carina</t>
+          <t>Antonia</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Maximiliano</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Felipe</t>
-        </is>
-      </c>
-      <c r="E742" t="inlineStr">
-        <is>
-          <t>Fabricio</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>982130913</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>carina1616.1987@gmail.com</t>
+          <t>antosanchezas841@gmail.com</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L742" t="inlineStr">
         <is>
-          <t>La pintana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="M742" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N742" t="inlineStr">
@@ -46966,95 +46964,113 @@
         <v>46147</v>
       </c>
       <c r="P742" s="3">
-        <v>46148.02159722222</v>
+        <v>46148.03700231481</v>
       </c>
       <c r="Q742" s="3">
-        <v>46148.05199074074</v>
+        <v>46148.04678240741</v>
       </c>
       <c r="R742" s="3">
-        <v>46148.05195601852</v>
+        <v>46148.04674768518</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>12789438-8</t>
+          <t>175682163</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Ana fariña</t>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Hirina</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>950887663</t>
+          <t>999999999</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>anafabi.faria.6@gmail.com</t>
+          <t>felipearturo@inacapmail.com</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L743" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="M743" t="inlineStr">
         <is>
-          <t>Ana fariña</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N743" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O743" s="2">
         <v>46147</v>
       </c>
       <c r="P743" s="3">
-        <v>46148.03469907407</v>
+        <v>46148.04888888889</v>
+      </c>
+      <c r="Q743" s="3">
+        <v>46148.06162037037</v>
       </c>
       <c r="R743" s="3">
-        <v>46148.07763888889</v>
+        <v>46148.06158564815</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>175682163</t>
+          <t>160334290</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Antonia</t>
+          <t>Jeanette</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Elias</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Dania</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>985093029</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>antosanchezas841@gmail.com</t>
+          <t>jeanette.olmedo77@gmail.com</t>
         </is>
       </c>
       <c r="K744" t="inlineStr">
@@ -47081,128 +47097,128 @@
         <v>46147</v>
       </c>
       <c r="P744" s="3">
-        <v>46148.03700231481</v>
+        <v>46148.07048611112</v>
       </c>
       <c r="Q744" s="3">
-        <v>46148.04678240741</v>
+        <v>46148.10331018519</v>
       </c>
       <c r="R744" s="3">
-        <v>46148.04674768518</v>
+        <v>46148.10331018519</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>175682163</t>
+          <t>13305368-9</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Felipe</t>
+          <t>Camila Gutiérrez</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Ángel Gutiérrez</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>Hirina</t>
+          <t>Sandra Faúndez</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Alejandra Gutiérrez</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>999999999</t>
+          <t>981782193</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>felipearturo@inacapmail.com</t>
+          <t>camilagutiwerezfaundez@gmail.com</t>
         </is>
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L745" t="inlineStr">
         <is>
-          <t>Valparaiso</t>
+          <t>Pencahue</t>
         </is>
       </c>
       <c r="M745" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N745" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O745" s="2">
         <v>46147</v>
       </c>
       <c r="P745" s="3">
-        <v>46148.04888888889</v>
+        <v>46148.07258101852</v>
       </c>
       <c r="Q745" s="3">
-        <v>46148.06162037037</v>
+        <v>46148.09637731481</v>
       </c>
       <c r="R745" s="3">
-        <v>46148.06158564815</v>
+        <v>46148.09637731481</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>160334290</t>
+          <t>105318464</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Jeanette</t>
+          <t>Romina</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Elias</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Dania</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>985093029</t>
+          <t>995902817</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>jeanette.olmedo77@gmail.com</t>
+          <t>romi.barbagelata@gmail.com</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L746" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="M746" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="N746" t="inlineStr">
@@ -47214,128 +47230,128 @@
         <v>46147</v>
       </c>
       <c r="P746" s="3">
-        <v>46148.07048611112</v>
+        <v>46148.09489583333</v>
       </c>
       <c r="Q746" s="3">
-        <v>46148.10331018519</v>
+        <v>46148.12075231482</v>
       </c>
       <c r="R746" s="3">
-        <v>46148.10331018519</v>
+        <v>46148.12075231482</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>160334290</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Camila Gutiérrez</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Ángel Gutiérrez</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Sandra Faúndez</t>
-        </is>
-      </c>
-      <c r="E747" t="inlineStr">
-        <is>
-          <t>Alejandra Gutiérrez</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>981782193</t>
+          <t>978850325</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>camilagutiwerezfaundez@gmail.com</t>
+          <t>alexanderbenavidesals@gmail.com</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L747" t="inlineStr">
         <is>
-          <t>Pencahue</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="M747" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="N747" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O747" s="2">
         <v>46147</v>
       </c>
       <c r="P747" s="3">
-        <v>46148.07258101852</v>
+        <v>46148.11864583333</v>
       </c>
       <c r="Q747" s="3">
-        <v>46148.09637731481</v>
+        <v>46148.13988425926</v>
       </c>
       <c r="R747" s="3">
-        <v>46148.09637731481</v>
+        <v>46148.13988425926</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>105318464</t>
+          <t>160334290</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Romina</t>
+          <t>Margarita</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Juan carlos</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Guadalupa</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>995902817</t>
+          <t>974476355</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>romi.barbagelata@gmail.com</t>
+          <t>margaritaduranc16@gmail.com</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L748" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>Viña del mar</t>
         </is>
       </c>
       <c r="M748" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N748" t="inlineStr">
@@ -47347,44 +47363,54 @@
         <v>46147</v>
       </c>
       <c r="P748" s="3">
-        <v>46148.09489583333</v>
+        <v>46148.12877314815</v>
       </c>
       <c r="Q748" s="3">
-        <v>46148.12075231482</v>
+        <v>46148.15601851852</v>
       </c>
       <c r="R748" s="3">
-        <v>46148.12075231482</v>
+        <v>46148.15601851852</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>160334290</t>
+          <t>175682163</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Hector</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Noelia</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Belen</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>978850325</t>
+          <t>988562258</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>alexanderbenavidesals@gmail.com</t>
+          <t>paulaza@live.cl</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
@@ -47394,12 +47420,12 @@
       </c>
       <c r="L749" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Viña del mar</t>
         </is>
       </c>
       <c r="M749" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N749" t="inlineStr">
@@ -47411,64 +47437,34 @@
         <v>46147</v>
       </c>
       <c r="P749" s="3">
-        <v>46148.11864583333</v>
+        <v>46148.12982638889</v>
       </c>
       <c r="Q749" s="3">
-        <v>46148.13988425926</v>
+        <v>46148.17927083334</v>
       </c>
       <c r="R749" s="3">
-        <v>46148.13988425926</v>
+        <v>46148.17927083334</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>160334290</t>
-        </is>
-      </c>
-      <c r="B750" t="inlineStr">
-        <is>
-          <t>Margarita</t>
-        </is>
-      </c>
-      <c r="C750" t="inlineStr">
-        <is>
-          <t>Juan carlos</t>
-        </is>
-      </c>
-      <c r="D750" t="inlineStr">
-        <is>
-          <t>Guadalupa</t>
-        </is>
-      </c>
-      <c r="E750" t="inlineStr">
-        <is>
-          <t>Benjamin</t>
+          <t>10102181-5</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>974476355</t>
+          <t>998920888</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>margaritaduranc16@gmail.com</t>
-        </is>
-      </c>
-      <c r="K750" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="L750" t="inlineStr">
-        <is>
-          <t>Viña del mar</t>
+          <t>fernanda.anai.mora@gmail.com</t>
         </is>
       </c>
       <c r="M750" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>181</t>
         </is>
       </c>
       <c r="N750" t="inlineStr">
@@ -47480,69 +47476,51 @@
         <v>46147</v>
       </c>
       <c r="P750" s="3">
-        <v>46148.12877314815</v>
-      </c>
-      <c r="Q750" s="3">
-        <v>46148.15601851852</v>
+        <v>46148.13240740741</v>
       </c>
       <c r="R750" s="3">
-        <v>46148.15601851852</v>
+        <v>46148.14884259259</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>175682163</t>
+          <t>10102181-5</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Marjorie</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Hector</t>
-        </is>
-      </c>
-      <c r="D751" t="inlineStr">
-        <is>
-          <t>Noelia</t>
-        </is>
-      </c>
-      <c r="E751" t="inlineStr">
-        <is>
-          <t>Fernando</t>
-        </is>
-      </c>
-      <c r="F751" t="inlineStr">
-        <is>
-          <t>Belen</t>
+          <t>anai</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>988562258</t>
+          <t>998920888</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>paulaza@live.cl</t>
+          <t>fernanda.anai.mora@gmail.com</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L751" t="inlineStr">
         <is>
-          <t>Viña del mar</t>
+          <t>lo prado</t>
         </is>
       </c>
       <c r="M751" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>181</t>
         </is>
       </c>
       <c r="N751" t="inlineStr">
@@ -47554,34 +47532,64 @@
         <v>46147</v>
       </c>
       <c r="P751" s="3">
-        <v>46148.12982638889</v>
+        <v>46148.14890046296</v>
       </c>
       <c r="Q751" s="3">
-        <v>46148.17927083334</v>
+        <v>46148.19263888889</v>
       </c>
       <c r="R751" s="3">
-        <v>46148.17927083334</v>
+        <v>46148.19263888889</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>10102181-5</t>
+          <t>17286752-9</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Hernan</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Matilde</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>998920888</t>
+          <t>964946167</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>fernanda.anai.mora@gmail.com</t>
+          <t>euevelopez@gmail.com</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>HUECHURABA</t>
         </is>
       </c>
       <c r="M752" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="N752" t="inlineStr">
@@ -47593,120 +47601,118 @@
         <v>46147</v>
       </c>
       <c r="P752" s="3">
-        <v>46148.13240740741</v>
+        <v>46148.16171296296</v>
+      </c>
+      <c r="Q752" s="3">
+        <v>46148.19428240741</v>
       </c>
       <c r="R752" s="3">
-        <v>46148.14884259259</v>
+        <v>46148.19428240741</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>10102181-5</t>
+          <t>125228445</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Marjorie</t>
+          <t>Rosa</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>anai</t>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Maite</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>998920888</t>
+          <t>99999999</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
         <is>
-          <t>fernanda.anai.mora@gmail.com</t>
+          <t>mmejias1973@yahoo.cl</t>
         </is>
       </c>
       <c r="K753" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L753" t="inlineStr">
         <is>
-          <t>lo prado</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="M753" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>844</t>
         </is>
       </c>
       <c r="N753" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O753" s="2">
         <v>46147</v>
       </c>
       <c r="P753" s="3">
-        <v>46148.14890046296</v>
+        <v>46148.20069444444</v>
       </c>
       <c r="Q753" s="3">
-        <v>46148.19263888889</v>
+        <v>46148.22878472222</v>
       </c>
       <c r="R753" s="3">
-        <v>46148.19263888889</v>
+        <v>46148.22878472222</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>17286752-9</t>
+          <t>125238445</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Hernan</t>
-        </is>
-      </c>
-      <c r="D754" t="inlineStr">
-        <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="E754" t="inlineStr">
-        <is>
-          <t>Matilde</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>964946167</t>
+          <t>978350819</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>euevelopez@gmail.com</t>
+          <t>mmejias1973@yahoo.cl</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L754" t="inlineStr">
         <is>
-          <t>HUECHURABA</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="M754" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>844</t>
         </is>
       </c>
       <c r="N754" t="inlineStr">
@@ -47718,59 +47724,64 @@
         <v>46147</v>
       </c>
       <c r="P754" s="3">
-        <v>46148.16171296296</v>
+        <v>46148.23722222222</v>
       </c>
       <c r="Q754" s="3">
-        <v>46148.19428240741</v>
+        <v>46148.25457175926</v>
       </c>
       <c r="R754" s="3">
-        <v>46148.19428240741</v>
+        <v>46148.25457175926</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>125228445</t>
+          <t>98784624</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Rosa</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Maite</t>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Andrés</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>99999999</t>
+          <t>982353017</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
         <is>
-          <t>mmejias1973@yahoo.cl</t>
+          <t>mariana.pasten.g@gmail.com</t>
         </is>
       </c>
       <c r="K755" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L755" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Puente alto</t>
         </is>
       </c>
       <c r="M755" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>624</t>
         </is>
       </c>
       <c r="N755" t="inlineStr">
@@ -47779,57 +47790,37 @@
         </is>
       </c>
       <c r="O755" s="2">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="P755" s="3">
-        <v>46148.20069444444</v>
+        <v>46148.66172453704</v>
       </c>
       <c r="Q755" s="3">
-        <v>46148.22878472222</v>
+        <v>46148.67400462963</v>
       </c>
       <c r="R755" s="3">
-        <v>46148.22878472222</v>
+        <v>46148.67400462963</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>125238445</t>
-        </is>
-      </c>
-      <c r="B756" t="inlineStr">
-        <is>
-          <t>Jose</t>
-        </is>
-      </c>
-      <c r="C756" t="inlineStr">
-        <is>
-          <t>Maria</t>
+          <t>2080647977</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>978350819</t>
+          <t>pedropablogato@gmail.com</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>mmejias1973@yahoo.cl</t>
-        </is>
-      </c>
-      <c r="K756" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="L756" t="inlineStr">
-        <is>
-          <t>Talca</t>
+          <t>pedropablogato@gmail.com</t>
         </is>
       </c>
       <c r="M756" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="N756" t="inlineStr">
@@ -47838,52 +47829,44 @@
         </is>
       </c>
       <c r="O756" s="2">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="P756" s="3">
-        <v>46148.23722222222</v>
-      </c>
-      <c r="Q756" s="3">
-        <v>46148.25457175926</v>
+        <v>46148.71138888889</v>
       </c>
       <c r="R756" s="3">
-        <v>46148.25457175926</v>
+        <v>46148.71928240741</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>98784624</t>
+          <t>18.050.509-1</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Alvaro</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Fernanda</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-      <c r="E757" t="inlineStr">
-        <is>
-          <t>Andrés</t>
+          <t>Apolonia</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>982353017</t>
+          <t>56966603557</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>mariana.pasten.g@gmail.com</t>
+          <t>alvarotorres.ps@gmail.com</t>
         </is>
       </c>
       <c r="K757" t="inlineStr">
@@ -47893,12 +47876,12 @@
       </c>
       <c r="L757" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="M757" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>091</t>
         </is>
       </c>
       <c r="N757" t="inlineStr">
@@ -47910,80 +47893,93 @@
         <v>46148</v>
       </c>
       <c r="P757" s="3">
-        <v>46148.66172453704</v>
+        <v>46148.73949074074</v>
       </c>
       <c r="Q757" s="3">
-        <v>46148.67400462963</v>
+        <v>46148.77854166667</v>
       </c>
       <c r="R757" s="3">
-        <v>46148.67400462963</v>
+        <v>46148.77854166667</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2080647977</t>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Hijo</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>pedropablogato@gmail.com</t>
+          <t>975272192</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>pedropablogato@gmail.com</t>
+          <t>gonzalezpaty.05@gmail.com</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="M758" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="N758" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O758" s="2">
         <v>46148</v>
       </c>
       <c r="P758" s="3">
-        <v>46148.71138888889</v>
+        <v>46148.89631944444</v>
+      </c>
+      <c r="Q758" s="3">
+        <v>46149.0878125</v>
       </c>
       <c r="R758" s="3">
-        <v>46148.71928240741</v>
+        <v>46149.0878125</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>18.050.509-1</t>
+          <t>184676443</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Alvaro</t>
-        </is>
-      </c>
-      <c r="C759" t="inlineStr">
-        <is>
-          <t>Fernanda</t>
-        </is>
-      </c>
-      <c r="D759" t="inlineStr">
-        <is>
-          <t>Apolonia</t>
+          <t>Waiker</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>56966603557</t>
+          <t>956287678</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>alvarotorres.ps@gmail.com</t>
+          <t>noresponde@gmail.com</t>
         </is>
       </c>
       <c r="K759" t="inlineStr">
@@ -47993,12 +47989,12 @@
       </c>
       <c r="L759" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Estación central</t>
         </is>
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="N759" t="inlineStr">
@@ -48010,13 +48006,519 @@
         <v>46148</v>
       </c>
       <c r="P759" s="3">
-        <v>46148.73949074074</v>
-      </c>
-      <c r="Q759" s="3">
-        <v>46148.77854166667</v>
+        <v>46148.90033564815</v>
       </c>
       <c r="R759" s="3">
-        <v>46148.77854166667</v>
+        <v>46148.91074074074</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>98784624</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>María Paz Henriquez.</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>971402041</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>Mariapaz.h@oscplus.cl</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O760" s="2">
+        <v>46148</v>
+      </c>
+      <c r="P760" s="3">
+        <v>46148.90809027778</v>
+      </c>
+      <c r="Q760" s="3">
+        <v>46148.924375</v>
+      </c>
+      <c r="R760" s="3">
+        <v>46148.924375</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Camila Tirapegui</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Juan Peña Canales</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Emily Rubio</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>992701643</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>camiilapaztirapeguiflores@gmail.com</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O761" s="2">
+        <v>46148</v>
+      </c>
+      <c r="P761" s="3">
+        <v>46148.91137731481</v>
+      </c>
+      <c r="Q761" s="3">
+        <v>46148.92965277778</v>
+      </c>
+      <c r="R761" s="3">
+        <v>46148.92965277778</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>20568285-6</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Diana Morales Vera</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Gabriel Poblete</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>dxmvera@gmail.com</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>dxmvera@gmail.com</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>valparaiso</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O762" s="2">
+        <v>46148</v>
+      </c>
+      <c r="P762" s="3">
+        <v>46148.93633101851</v>
+      </c>
+      <c r="Q762" s="3">
+        <v>46148.96303240741</v>
+      </c>
+      <c r="R762" s="3">
+        <v>46148.96303240741</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>20806479-7</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>56986147685</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>carolina.ore.mo@gmail.com</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>6479-01</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O763" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P763" s="3">
+        <v>46149.62575231482</v>
+      </c>
+      <c r="Q763" s="3">
+        <v>46149.67486111111</v>
+      </c>
+      <c r="R763" s="3">
+        <v>46149.67486111111</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>19172396-1</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>920269626</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>francoantoniorios@gmail.com</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O764" s="2">
+        <v>45566</v>
+      </c>
+      <c r="P764" s="3">
+        <v>46149.66836805556</v>
+      </c>
+      <c r="Q764" s="3">
+        <v>46149.68783564815</v>
+      </c>
+      <c r="R764" s="3">
+        <v>46149.68783564815</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>20806479-7</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Blkys</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Yanethe</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>56989629748</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>jjjsuarez@gmail.com</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>6479-02</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O765" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P765" s="3">
+        <v>46149.67758101852</v>
+      </c>
+      <c r="Q765" s="3">
+        <v>46149.73665509259</v>
+      </c>
+      <c r="R765" s="3">
+        <v>46149.73665509259</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Valentina Indo</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Maria Paz Hermandez</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>948553351</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>vale.indo20@gmail.com</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O766" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P766" s="3">
+        <v>46149.7152662037</v>
+      </c>
+      <c r="Q766" s="3">
+        <v>46149.73702546296</v>
+      </c>
+      <c r="R766" s="3">
+        <v>46149.73702546296</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Maricarmen</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Brandon Pino</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Karen Pino</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Melany medina</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>56952277293</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>brankar.1981@gmail.com</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O767" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P767" s="3">
+        <v>46149.78666666667</v>
+      </c>
+      <c r="R767" s="3">
+        <v>46149.80401620371</v>
       </c>
     </row>
   </sheetData>

--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R767"/>
+  <dimension ref="A1:R785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="15" max="15" width="20.7109375" style="2" customWidth="1"/>
@@ -48202,47 +48202,47 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>20806479-7</t>
+          <t>20568285-6</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Carolina</t>
+          <t>Luis vergara Castillo</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Carolina Muñoz Barrientos</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>Ema</t>
+          <t>Florencia Vergara Muñoz</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>56986147685</t>
+          <t>+56 9 7103 6642</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>carolina.ore.mo@gmail.com</t>
+          <t>lvergaracastillo28@gmail.com</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L763" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="M763" t="inlineStr">
         <is>
-          <t>6479-01</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="N763" t="inlineStr">
@@ -48254,34 +48254,44 @@
         <v>46149</v>
       </c>
       <c r="P763" s="3">
-        <v>46149.62575231482</v>
+        <v>46149.01924768518</v>
       </c>
       <c r="Q763" s="3">
-        <v>46149.67486111111</v>
+        <v>46149.88473379629</v>
       </c>
       <c r="R763" s="3">
-        <v>46149.67486111111</v>
+        <v>46149.88473379629</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>19172396-1</t>
+          <t>20806479-7</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Franco</t>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Ema</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>920269626</t>
+          <t>56986147685</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>francoantoniorios@gmail.com</t>
+          <t>carolina.ore.mo@gmail.com</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
@@ -48291,12 +48301,12 @@
       </c>
       <c r="L764" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="M764" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>6479-01</t>
         </is>
       </c>
       <c r="N764" t="inlineStr">
@@ -48305,57 +48315,37 @@
         </is>
       </c>
       <c r="O764" s="2">
-        <v>45566</v>
+        <v>46149</v>
       </c>
       <c r="P764" s="3">
-        <v>46149.66836805556</v>
+        <v>46149.62575231482</v>
       </c>
       <c r="Q764" s="3">
-        <v>46149.68783564815</v>
+        <v>46149.67486111111</v>
       </c>
       <c r="R764" s="3">
-        <v>46149.68783564815</v>
+        <v>46149.67486111111</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>20806479-7</t>
+          <t>19172396-1</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C765" t="inlineStr">
-        <is>
-          <t>Blkys</t>
-        </is>
-      </c>
-      <c r="D765" t="inlineStr">
-        <is>
-          <t>Yanethe</t>
-        </is>
-      </c>
-      <c r="E765" t="inlineStr">
-        <is>
-          <t>Miguel</t>
-        </is>
-      </c>
-      <c r="F765" t="inlineStr">
-        <is>
-          <t>Sofia</t>
+          <t>Franco</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>56989629748</t>
+          <t>920269626</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>jjjsuarez@gmail.com</t>
+          <t>francoantoniorios@gmail.com</t>
         </is>
       </c>
       <c r="K765" t="inlineStr">
@@ -48365,71 +48355,86 @@
       </c>
       <c r="L765" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="M765" t="inlineStr">
         <is>
-          <t>6479-02</t>
+          <t>396</t>
         </is>
       </c>
       <c r="N765" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O765" s="2">
-        <v>46149</v>
+        <v>45566</v>
       </c>
       <c r="P765" s="3">
-        <v>46149.67758101852</v>
+        <v>46149.66836805556</v>
       </c>
       <c r="Q765" s="3">
-        <v>46149.73665509259</v>
+        <v>46149.68783564815</v>
       </c>
       <c r="R765" s="3">
-        <v>46149.73665509259</v>
+        <v>46149.68783564815</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>20806479-7</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Valentina Indo</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Maria Paz Hermandez</t>
+          <t>Blkys</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Yanethe</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>948553351</t>
+          <t>56989629748</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>vale.indo20@gmail.com</t>
+          <t>jjjsuarez@gmail.com</t>
         </is>
       </c>
       <c r="K766" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L766" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="M766" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6479-02</t>
         </is>
       </c>
       <c r="N766" t="inlineStr">
@@ -48441,69 +48446,54 @@
         <v>46149</v>
       </c>
       <c r="P766" s="3">
-        <v>46149.7152662037</v>
+        <v>46149.67758101852</v>
       </c>
       <c r="Q766" s="3">
-        <v>46149.73702546296</v>
+        <v>46149.73665509259</v>
       </c>
       <c r="R766" s="3">
-        <v>46149.73702546296</v>
+        <v>46149.73665509259</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>13081719-k</t>
+          <t>13305368-9</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Maricarmen</t>
+          <t>Valentina Indo</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Brandon Pino</t>
-        </is>
-      </c>
-      <c r="D767" t="inlineStr">
-        <is>
-          <t>Karen Pino</t>
-        </is>
-      </c>
-      <c r="E767" t="inlineStr">
-        <is>
-          <t>Melany medina</t>
-        </is>
-      </c>
-      <c r="F767" t="inlineStr">
-        <is>
-          <t>Andres</t>
+          <t>Maria Paz Hermandez</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>56952277293</t>
+          <t>948553351</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>brankar.1981@gmail.com</t>
+          <t>vale.indo20@gmail.com</t>
         </is>
       </c>
       <c r="K767" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L767" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="M767" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N767" t="inlineStr">
@@ -48515,10 +48505,1167 @@
         <v>46149</v>
       </c>
       <c r="P767" s="3">
+        <v>46149.7152662037</v>
+      </c>
+      <c r="Q767" s="3">
+        <v>46149.73702546296</v>
+      </c>
+      <c r="R767" s="3">
+        <v>46149.73702546296</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Maricarmen</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Brandon Pino</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Karen Pino</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Melany medina</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>56952277293</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>brankar.1981@gmail.com</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O768" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P768" s="3">
         <v>46149.78666666667</v>
       </c>
-      <c r="R767" s="3">
-        <v>46149.80401620371</v>
+      <c r="Q768" s="3">
+        <v>46149.82563657407</v>
+      </c>
+      <c r="R768" s="3">
+        <v>46149.82563657407</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Julián</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Ana María</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>972088563</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>randresvalenzuelaj@gmail.com</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O769" s="2">
+        <v>46138</v>
+      </c>
+      <c r="P769" s="3">
+        <v>46149.81055555555</v>
+      </c>
+      <c r="Q769" s="3">
+        <v>46149.87510416667</v>
+      </c>
+      <c r="R769" s="3">
+        <v>46149.87510416667</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>13081719-K</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Rosario</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Jasmin</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Msrcelo</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>926428130</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>quirozvillarroelr@gmail.com</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>Correlativo 33</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O770" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P770" s="3">
+        <v>46149.85027777778</v>
+      </c>
+      <c r="Q770" s="3">
+        <v>46149.88844907407</v>
+      </c>
+      <c r="R770" s="3">
+        <v>46149.88844907407</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>18050509-1</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Gracia</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>56974040835</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>DAVID.VALDIVIA.R@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O771" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P771" s="3">
+        <v>46149.90491898148</v>
+      </c>
+      <c r="Q771" s="3">
+        <v>46149.94763888889</v>
+      </c>
+      <c r="R771" s="3">
+        <v>46149.94763888889</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Roberto Fuentes</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>999332932</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>gisela.godoy020388@gmail.com</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O772" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P772" s="3">
+        <v>46149.97364583334</v>
+      </c>
+      <c r="Q772" s="3">
+        <v>46150.00019675925</v>
+      </c>
+      <c r="R772" s="3">
+        <v>46150.00019675925</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Rayen / Thomas / Catherine / Josefina</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Josefina</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Catherine</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>947184058</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>rayensantos@gmail.com</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>CORRELATIVO 34</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O773" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P773" s="3">
+        <v>46149.97879629629</v>
+      </c>
+      <c r="Q773" s="3">
+        <v>46150.02318287037</v>
+      </c>
+      <c r="R773" s="3">
+        <v>46150.02314814815</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Tomas rozas</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Agustín solano</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>935123019</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>geramiifabiola@gmail.com</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O774" s="2">
+        <v>44958</v>
+      </c>
+      <c r="P774" s="3">
+        <v>46150.03915509259</v>
+      </c>
+      <c r="Q774" s="3">
+        <v>46150.09788194444</v>
+      </c>
+      <c r="R774" s="3">
+        <v>46150.09788194444</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Verónica</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>961244665</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>vegitomaster@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>Ventanas</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>4290</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O775" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P775" s="3">
+        <v>46150.04923611111</v>
+      </c>
+      <c r="Q775" s="3">
+        <v>46150.08106481482</v>
+      </c>
+      <c r="R775" s="3">
+        <v>46150.08104166666</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Yadira</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>949815493</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>yari.figueroa2010@gmail.com</t>
+        </is>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>Valparaixo</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="N776" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O776" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P776" s="3">
+        <v>46150.06782407407</v>
+      </c>
+      <c r="Q776" s="3">
+        <v>46150.11704861111</v>
+      </c>
+      <c r="R776" s="3">
+        <v>46150.11704861111</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>160334290</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Verónica</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Berta</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>959866246</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>cosita22-@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>4290</t>
+        </is>
+      </c>
+      <c r="N777" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O777" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P777" s="3">
+        <v>46150.07528935185</v>
+      </c>
+      <c r="Q777" s="3">
+        <v>46150.09877314814</v>
+      </c>
+      <c r="R777" s="3">
+        <v>46150.09877314814</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Geramy navarro</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Tomas rozas</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>934837199</t>
+        </is>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>fabiola.gonzale.villar@gmail.com</t>
+        </is>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N778" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O778" s="2">
+        <v>43563</v>
+      </c>
+      <c r="P778" s="3">
+        <v>46150.10210648148</v>
+      </c>
+      <c r="Q778" s="3">
+        <v>46150.15333333334</v>
+      </c>
+      <c r="R778" s="3">
+        <v>46150.15333333334</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>105033206</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Katerine</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>951987113</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>katerine.farias1@iclaud.com</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O779" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P779" s="3">
+        <v>46150.12767361111</v>
+      </c>
+      <c r="Q779" s="3">
+        <v>46150.18925925926</v>
+      </c>
+      <c r="R779" s="3">
+        <v>46150.18925925926</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>13081719k</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Carla</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Julieta</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>996546036</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>carlaarandacorrea@gmail.com</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>Sabtiago</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N780" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O780" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P780" s="3">
+        <v>46150.58122685185</v>
+      </c>
+      <c r="Q780" s="3">
+        <v>46150.60709490741</v>
+      </c>
+      <c r="R780" s="3">
+        <v>46150.60709490741</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Claudia Hermosilla</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Amanda Diaz Hermosilla</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Alfonsina Díaz Hermosilla</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>97967352</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>cvalhermosilla@gmail.com</t>
+        </is>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N781" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O781" s="2">
+        <v>46149</v>
+      </c>
+      <c r="P781" s="3">
+        <v>46150.69798611111</v>
+      </c>
+      <c r="Q781" s="3">
+        <v>46150.72464120371</v>
+      </c>
+      <c r="R781" s="3">
+        <v>46150.72464120371</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>18.050.509-1</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Angelo</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Rayen</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Emilio</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>56966206968</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>barbra.faun@gmail.com</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="N782" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O782" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P782" s="3">
+        <v>46150.71868055555</v>
+      </c>
+      <c r="Q782" s="3">
+        <v>46150.76734953704</v>
+      </c>
+      <c r="R782" s="3">
+        <v>46150.76734953704</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Ide</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Yohanna</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>935225921</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>idearriagada@gmail.com</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>TALXA</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="N783" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O783" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P783" s="3">
+        <v>46150.72909722223</v>
+      </c>
+      <c r="Q783" s="3">
+        <v>46150.75146990741</v>
+      </c>
+      <c r="R783" s="3">
+        <v>46150.75146990741</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Belen</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>989033752</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>bele.castro.p@gmail.com</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>Concon</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N784" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O784" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P784" s="3">
+        <v>46150.74744212963</v>
+      </c>
+      <c r="Q784" s="3">
+        <v>46150.76724537037</v>
+      </c>
+      <c r="R784" s="3">
+        <v>46150.76724537037</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Luciano</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Elisa</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>977687764</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>daniela.sf.k@gmail.com</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>Quilpue</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N785" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O785" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P785" s="3">
+        <v>46150.76731481482</v>
+      </c>
+      <c r="R785" s="3">
+        <v>46150.76993055556</v>
       </c>
     </row>
   </sheetData>

--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R785"/>
+  <dimension ref="A1:R806"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="15" max="15" width="20.7109375" style="2" customWidth="1"/>
@@ -46906,7 +46906,7 @@
         <v>46148.03469907407</v>
       </c>
       <c r="R741" s="3">
-        <v>46148.07763888889</v>
+        <v>46152.82055555555</v>
       </c>
     </row>
     <row r="742">
@@ -47905,96 +47905,116 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>105033206</t>
+          <t>205094288</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Cristian</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Hijo</t>
+          <t>Cristian ortiz</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Ofelia dia</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Deyanira ortiz</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Cristian leon</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>975272192</t>
+          <t>966927178</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>gonzalezpaty.05@gmail.com</t>
+          <t>carmendiaz.andrade@gmail.com</t>
         </is>
       </c>
       <c r="K758" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L758" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Curico</t>
         </is>
       </c>
       <c r="M758" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>Labofam</t>
         </is>
       </c>
       <c r="N758" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O758" s="2">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="P758" s="3">
-        <v>46148.89631944444</v>
+        <v>46148.82622685185</v>
       </c>
       <c r="Q758" s="3">
-        <v>46149.0878125</v>
+        <v>46153.16072916667</v>
       </c>
       <c r="R758" s="3">
-        <v>46149.0878125</v>
+        <v>46153.16072916667</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>184676443</t>
+          <t>105033206</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Waiker</t>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Hijo</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>956287678</t>
+          <t>975272192</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>noresponde@gmail.com</t>
+          <t>gonzalezpaty.05@gmail.com</t>
         </is>
       </c>
       <c r="K759" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L759" t="inlineStr">
         <is>
-          <t>Estación central</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="N759" t="inlineStr">
@@ -48006,41 +48026,34 @@
         <v>46148</v>
       </c>
       <c r="P759" s="3">
-        <v>46148.90033564815</v>
+        <v>46148.89631944444</v>
+      </c>
+      <c r="Q759" s="3">
+        <v>46149.0878125</v>
       </c>
       <c r="R759" s="3">
-        <v>46148.91074074074</v>
+        <v>46149.0878125</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>98784624</t>
+          <t>184676443</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>María Paz Henriquez.</t>
-        </is>
-      </c>
-      <c r="C760" t="inlineStr">
-        <is>
-          <t>Felipe</t>
-        </is>
-      </c>
-      <c r="D760" t="inlineStr">
-        <is>
-          <t>Isidora</t>
+          <t>Waiker</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>971402041</t>
+          <t>956287678</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>Mariapaz.h@oscplus.cl</t>
+          <t>noresponde@gmail.com</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
@@ -48050,12 +48063,12 @@
       </c>
       <c r="L760" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Estación central</t>
         </is>
       </c>
       <c r="M760" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="N760" t="inlineStr">
@@ -48067,136 +48080,138 @@
         <v>46148</v>
       </c>
       <c r="P760" s="3">
-        <v>46148.90809027778</v>
-      </c>
-      <c r="Q760" s="3">
-        <v>46148.924375</v>
+        <v>46148.90033564815</v>
       </c>
       <c r="R760" s="3">
-        <v>46148.924375</v>
+        <v>46148.91074074074</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>98784624</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Camila Tirapegui</t>
+          <t>María Paz Henriquez.</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Juan Peña Canales</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>Emily Rubio</t>
+          <t>Isidora</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>992701643</t>
+          <t>971402041</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>camiilapaztirapeguiflores@gmail.com</t>
+          <t>Mariapaz.h@oscplus.cl</t>
         </is>
       </c>
       <c r="K761" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L761" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="M761" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>624</t>
         </is>
       </c>
       <c r="N761" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O761" s="2">
         <v>46148</v>
       </c>
       <c r="P761" s="3">
-        <v>46148.91137731481</v>
+        <v>46148.90809027778</v>
       </c>
       <c r="Q761" s="3">
-        <v>46148.92965277778</v>
+        <v>46148.924375</v>
       </c>
       <c r="R761" s="3">
-        <v>46148.92965277778</v>
+        <v>46148.924375</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>20568285-6</t>
+          <t>13305368-9</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Diana Morales Vera</t>
+          <t>Camila Tirapegui</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Gabriel Poblete</t>
+          <t>Juan Peña Canales</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Emily Rubio</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>dxmvera@gmail.com</t>
+          <t>992701643</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>dxmvera@gmail.com</t>
+          <t>camiilapaztirapeguiflores@gmail.com</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L762" t="inlineStr">
         <is>
-          <t>valparaiso</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="M762" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N762" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O762" s="2">
         <v>46148</v>
       </c>
       <c r="P762" s="3">
-        <v>46148.93633101851</v>
+        <v>46148.91137731481</v>
       </c>
       <c r="Q762" s="3">
-        <v>46148.96303240741</v>
+        <v>46148.92965277778</v>
       </c>
       <c r="R762" s="3">
-        <v>46148.96303240741</v>
+        <v>46148.92965277778</v>
       </c>
     </row>
     <row r="763">
@@ -48207,27 +48222,22 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Luis vergara Castillo</t>
+          <t>Diana Morales Vera</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Carolina Muñoz Barrientos</t>
-        </is>
-      </c>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>Florencia Vergara Muñoz</t>
+          <t>Gabriel Poblete</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>+56 9 7103 6642</t>
+          <t>dxmvera@gmail.com</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>lvergaracastillo28@gmail.com</t>
+          <t>dxmvera@gmail.com</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
@@ -48237,7 +48247,7 @@
       </c>
       <c r="L763" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>valparaiso</t>
         </is>
       </c>
       <c r="M763" t="inlineStr">
@@ -48251,62 +48261,62 @@
         </is>
       </c>
       <c r="O763" s="2">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="P763" s="3">
-        <v>46149.01924768518</v>
+        <v>46148.93633101851</v>
       </c>
       <c r="Q763" s="3">
-        <v>46149.88473379629</v>
+        <v>46148.96303240741</v>
       </c>
       <c r="R763" s="3">
-        <v>46149.88473379629</v>
+        <v>46148.96303240741</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>20806479-7</t>
+          <t>20568285-6</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Carolina</t>
+          <t>Luis vergara Castillo</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Carolina Muñoz Barrientos</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>Ema</t>
+          <t>Florencia Vergara Muñoz</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>56986147685</t>
+          <t>+56 9 7103 6642</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>carolina.ore.mo@gmail.com</t>
+          <t>lvergaracastillo28@gmail.com</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L764" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="M764" t="inlineStr">
         <is>
-          <t>6479-01</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="N764" t="inlineStr">
@@ -48318,34 +48328,44 @@
         <v>46149</v>
       </c>
       <c r="P764" s="3">
-        <v>46149.62575231482</v>
+        <v>46149.01924768518</v>
       </c>
       <c r="Q764" s="3">
-        <v>46149.67486111111</v>
+        <v>46149.88473379629</v>
       </c>
       <c r="R764" s="3">
-        <v>46149.67486111111</v>
+        <v>46149.88473379629</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>19172396-1</t>
+          <t>20806479-7</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Franco</t>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Ema</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>920269626</t>
+          <t>56986147685</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>francoantoniorios@gmail.com</t>
+          <t>carolina.ore.mo@gmail.com</t>
         </is>
       </c>
       <c r="K765" t="inlineStr">
@@ -48355,12 +48375,12 @@
       </c>
       <c r="L765" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="M765" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>6479-01</t>
         </is>
       </c>
       <c r="N765" t="inlineStr">
@@ -48369,57 +48389,37 @@
         </is>
       </c>
       <c r="O765" s="2">
-        <v>45566</v>
+        <v>46149</v>
       </c>
       <c r="P765" s="3">
-        <v>46149.66836805556</v>
+        <v>46149.62575231482</v>
       </c>
       <c r="Q765" s="3">
-        <v>46149.68783564815</v>
+        <v>46149.67486111111</v>
       </c>
       <c r="R765" s="3">
-        <v>46149.68783564815</v>
+        <v>46149.67486111111</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>20806479-7</t>
+          <t>19172396-1</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="C766" t="inlineStr">
-        <is>
-          <t>Blkys</t>
-        </is>
-      </c>
-      <c r="D766" t="inlineStr">
-        <is>
-          <t>Yanethe</t>
-        </is>
-      </c>
-      <c r="E766" t="inlineStr">
-        <is>
-          <t>Miguel</t>
-        </is>
-      </c>
-      <c r="F766" t="inlineStr">
-        <is>
-          <t>Sofia</t>
+          <t>Franco</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>56989629748</t>
+          <t>920269626</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>jjjsuarez@gmail.com</t>
+          <t>francoantoniorios@gmail.com</t>
         </is>
       </c>
       <c r="K766" t="inlineStr">
@@ -48429,71 +48429,86 @@
       </c>
       <c r="L766" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="M766" t="inlineStr">
         <is>
-          <t>6479-02</t>
+          <t>396</t>
         </is>
       </c>
       <c r="N766" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O766" s="2">
-        <v>46149</v>
+        <v>45566</v>
       </c>
       <c r="P766" s="3">
-        <v>46149.67758101852</v>
+        <v>46149.66836805556</v>
       </c>
       <c r="Q766" s="3">
-        <v>46149.73665509259</v>
+        <v>46149.68783564815</v>
       </c>
       <c r="R766" s="3">
-        <v>46149.73665509259</v>
+        <v>46149.68783564815</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>20806479-7</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Valentina Indo</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Maria Paz Hermandez</t>
+          <t>Blkys</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Yanethe</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>948553351</t>
+          <t>56989629748</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>vale.indo20@gmail.com</t>
+          <t>jjjsuarez@gmail.com</t>
         </is>
       </c>
       <c r="K767" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L767" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="M767" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6479-02</t>
         </is>
       </c>
       <c r="N767" t="inlineStr">
@@ -48505,69 +48520,54 @@
         <v>46149</v>
       </c>
       <c r="P767" s="3">
-        <v>46149.7152662037</v>
+        <v>46149.67758101852</v>
       </c>
       <c r="Q767" s="3">
-        <v>46149.73702546296</v>
+        <v>46149.73665509259</v>
       </c>
       <c r="R767" s="3">
-        <v>46149.73702546296</v>
+        <v>46149.73665509259</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>13081719-k</t>
+          <t>13305368-9</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Maricarmen</t>
+          <t>Valentina Indo</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Brandon Pino</t>
-        </is>
-      </c>
-      <c r="D768" t="inlineStr">
-        <is>
-          <t>Karen Pino</t>
-        </is>
-      </c>
-      <c r="E768" t="inlineStr">
-        <is>
-          <t>Melany medina</t>
-        </is>
-      </c>
-      <c r="F768" t="inlineStr">
-        <is>
-          <t>Andres</t>
+          <t>Maria Paz Hermandez</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>56952277293</t>
+          <t>948553351</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>brankar.1981@gmail.com</t>
+          <t>vale.indo20@gmail.com</t>
         </is>
       </c>
       <c r="K768" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L768" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="M768" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N768" t="inlineStr">
@@ -48579,39 +48579,54 @@
         <v>46149</v>
       </c>
       <c r="P768" s="3">
-        <v>46149.78666666667</v>
+        <v>46149.7152662037</v>
       </c>
       <c r="Q768" s="3">
-        <v>46149.82563657407</v>
+        <v>46149.73702546296</v>
       </c>
       <c r="R768" s="3">
-        <v>46149.82563657407</v>
+        <v>46149.73702546296</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>13081719k</t>
+          <t>13081719-k</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Julián</t>
+          <t>Maricarmen</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Ana María</t>
+          <t>Brandon Pino</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Karen Pino</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Melany medina</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Andres</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
         <is>
-          <t>972088563</t>
+          <t>56952277293</t>
         </is>
       </c>
       <c r="J769" t="inlineStr">
         <is>
-          <t>randresvalenzuelaj@gmail.com</t>
+          <t>brankar.1981@gmail.com</t>
         </is>
       </c>
       <c r="K769" t="inlineStr">
@@ -48621,66 +48636,56 @@
       </c>
       <c r="L769" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="M769" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N769" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O769" s="2">
-        <v>46138</v>
+        <v>46149</v>
       </c>
       <c r="P769" s="3">
-        <v>46149.81055555555</v>
+        <v>46149.78666666667</v>
       </c>
       <c r="Q769" s="3">
-        <v>46149.87510416667</v>
+        <v>46149.82563657407</v>
       </c>
       <c r="R769" s="3">
-        <v>46149.87510416667</v>
+        <v>46149.82563657407</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>13081719-K</t>
+          <t>13081719k</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Rosario</t>
+          <t>Julián</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Jasmin</t>
-        </is>
-      </c>
-      <c r="D770" t="inlineStr">
-        <is>
-          <t>Gabriel</t>
-        </is>
-      </c>
-      <c r="E770" t="inlineStr">
-        <is>
-          <t>Msrcelo</t>
+          <t>Ana María</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
         <is>
-          <t>926428130</t>
+          <t>972088563</t>
         </is>
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>quirozvillarroelr@gmail.com</t>
+          <t>randresvalenzuelaj@gmail.com</t>
         </is>
       </c>
       <c r="K770" t="inlineStr">
@@ -48690,12 +48695,12 @@
       </c>
       <c r="L770" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="M770" t="inlineStr">
         <is>
-          <t>Correlativo 33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N770" t="inlineStr">
@@ -48704,42 +48709,52 @@
         </is>
       </c>
       <c r="O770" s="2">
-        <v>46149</v>
+        <v>46138</v>
       </c>
       <c r="P770" s="3">
-        <v>46149.85027777778</v>
+        <v>46149.81055555555</v>
       </c>
       <c r="Q770" s="3">
-        <v>46149.88844907407</v>
+        <v>46149.87510416667</v>
       </c>
       <c r="R770" s="3">
-        <v>46149.88844907407</v>
+        <v>46149.87510416667</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>18050509-1</t>
+          <t>13081719-K</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Rosario</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Gracia</t>
+          <t>Jasmin</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Msrcelo</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
         <is>
-          <t>56974040835</t>
+          <t>926428130</t>
         </is>
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>DAVID.VALDIVIA.R@GMAIL.COM</t>
+          <t>quirozvillarroelr@gmail.com</t>
         </is>
       </c>
       <c r="K771" t="inlineStr">
@@ -48749,51 +48764,56 @@
       </c>
       <c r="L771" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="M771" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>Correlativo 33</t>
         </is>
       </c>
       <c r="N771" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O771" s="2">
         <v>46149</v>
       </c>
       <c r="P771" s="3">
-        <v>46149.90491898148</v>
+        <v>46149.85027777778</v>
       </c>
       <c r="Q771" s="3">
-        <v>46149.94763888889</v>
+        <v>46149.88844907407</v>
       </c>
       <c r="R771" s="3">
-        <v>46149.94763888889</v>
+        <v>46149.88844907407</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>13081719k</t>
+          <t>18050509-1</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Roberto Fuentes</t>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Gracia</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
         <is>
-          <t>999332932</t>
+          <t>56974040835</t>
         </is>
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>gisela.godoy020388@gmail.com</t>
+          <t>DAVID.VALDIVIA.R@GMAIL.COM</t>
         </is>
       </c>
       <c r="K772" t="inlineStr">
@@ -48803,66 +48823,51 @@
       </c>
       <c r="L772" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="M772" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>091</t>
         </is>
       </c>
       <c r="N772" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O772" s="2">
         <v>46149</v>
       </c>
       <c r="P772" s="3">
-        <v>46149.97364583334</v>
+        <v>46149.90491898148</v>
       </c>
       <c r="Q772" s="3">
-        <v>46150.00019675925</v>
+        <v>46149.94763888889</v>
       </c>
       <c r="R772" s="3">
-        <v>46150.00019675925</v>
+        <v>46149.94763888889</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>13081719-k</t>
+          <t>13081719k</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Rayen / Thomas / Catherine / Josefina</t>
-        </is>
-      </c>
-      <c r="C773" t="inlineStr">
-        <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="D773" t="inlineStr">
-        <is>
-          <t>Josefina</t>
-        </is>
-      </c>
-      <c r="E773" t="inlineStr">
-        <is>
-          <t>Catherine</t>
+          <t>Roberto Fuentes</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>947184058</t>
+          <t>999332932</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>rayensantos@gmail.com</t>
+          <t>gisela.godoy020388@gmail.com</t>
         </is>
       </c>
       <c r="K773" t="inlineStr">
@@ -48872,56 +48877,66 @@
       </c>
       <c r="L773" t="inlineStr">
         <is>
-          <t>La florida</t>
+          <t>Puente alto</t>
         </is>
       </c>
       <c r="M773" t="inlineStr">
         <is>
-          <t>CORRELATIVO 34</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N773" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O773" s="2">
         <v>46149</v>
       </c>
       <c r="P773" s="3">
-        <v>46149.97879629629</v>
+        <v>46149.97364583334</v>
       </c>
       <c r="Q773" s="3">
-        <v>46150.02318287037</v>
+        <v>46150.00019675925</v>
       </c>
       <c r="R773" s="3">
-        <v>46150.02314814815</v>
+        <v>46150.00019675925</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>13081719k</t>
+          <t>13081719-k</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Tomas rozas</t>
+          <t>Rayen / Thomas / Catherine / Josefina</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Agustín solano</t>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Josefina</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>935123019</t>
+          <t>947184058</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>geramiifabiola@gmail.com</t>
+          <t>rayensantos@gmail.com</t>
         </is>
       </c>
       <c r="K774" t="inlineStr">
@@ -48931,120 +48946,120 @@
       </c>
       <c r="L774" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>La florida</t>
         </is>
       </c>
       <c r="M774" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>CORRELATIVO 34</t>
         </is>
       </c>
       <c r="N774" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O774" s="2">
-        <v>44958</v>
+        <v>46149</v>
       </c>
       <c r="P774" s="3">
-        <v>46150.03915509259</v>
+        <v>46149.97879629629</v>
       </c>
       <c r="Q774" s="3">
-        <v>46150.09788194444</v>
+        <v>46150.02318287037</v>
       </c>
       <c r="R774" s="3">
-        <v>46150.09788194444</v>
+        <v>46150.02314814815</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>160334290</t>
+          <t>13081719k</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Alejandro</t>
+          <t>Tomas rozas</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Verónica</t>
-        </is>
-      </c>
-      <c r="D775" t="inlineStr">
-        <is>
-          <t>Benjamin</t>
+          <t>Agustín solano</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>961244665</t>
+          <t>935123019</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
         <is>
-          <t>vegitomaster@hotmail.com</t>
+          <t>geramiifabiola@gmail.com</t>
         </is>
       </c>
       <c r="K775" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L775" t="inlineStr">
         <is>
-          <t>Ventanas</t>
+          <t>Puente alto</t>
         </is>
       </c>
       <c r="M775" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>36</t>
         </is>
       </c>
       <c r="N775" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O775" s="2">
-        <v>46149</v>
+        <v>44958</v>
       </c>
       <c r="P775" s="3">
-        <v>46150.04923611111</v>
+        <v>46150.03915509259</v>
       </c>
       <c r="Q775" s="3">
-        <v>46150.08106481482</v>
+        <v>46150.09788194444</v>
       </c>
       <c r="R775" s="3">
-        <v>46150.08104166666</v>
+        <v>46150.09788194444</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>105033206</t>
+          <t>160334290</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Yadira</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Scarlet</t>
+          <t>Verónica</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>949815493</t>
+          <t>961244665</t>
         </is>
       </c>
       <c r="J776" t="inlineStr">
         <is>
-          <t>yari.figueroa2010@gmail.com</t>
+          <t>vegitomaster@hotmail.com</t>
         </is>
       </c>
       <c r="K776" t="inlineStr">
@@ -49054,71 +49069,56 @@
       </c>
       <c r="L776" t="inlineStr">
         <is>
-          <t>Valparaixo</t>
+          <t>Ventanas</t>
         </is>
       </c>
       <c r="M776" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="N776" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O776" s="2">
         <v>46149</v>
       </c>
       <c r="P776" s="3">
-        <v>46150.06782407407</v>
+        <v>46150.04923611111</v>
       </c>
       <c r="Q776" s="3">
-        <v>46150.11704861111</v>
+        <v>46150.08106481482</v>
       </c>
       <c r="R776" s="3">
-        <v>46150.11704861111</v>
+        <v>46150.08104166666</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>160334290</t>
+          <t>105033206</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Verónica</t>
+          <t>Yadira</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Patricio</t>
-        </is>
-      </c>
-      <c r="D777" t="inlineStr">
-        <is>
-          <t>Francisca</t>
-        </is>
-      </c>
-      <c r="E777" t="inlineStr">
-        <is>
-          <t>Claudia</t>
-        </is>
-      </c>
-      <c r="F777" t="inlineStr">
-        <is>
-          <t>Berta</t>
+          <t>Scarlet</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
         <is>
-          <t>959866246</t>
+          <t>949815493</t>
         </is>
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>cosita22-@hotmail.com</t>
+          <t>yari.figueroa2010@gmail.com</t>
         </is>
       </c>
       <c r="K777" t="inlineStr">
@@ -49128,130 +49128,145 @@
       </c>
       <c r="L777" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Valparaixo</t>
         </is>
       </c>
       <c r="M777" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="N777" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O777" s="2">
         <v>46149</v>
       </c>
       <c r="P777" s="3">
-        <v>46150.07528935185</v>
+        <v>46150.06782407407</v>
       </c>
       <c r="Q777" s="3">
-        <v>46150.09877314814</v>
+        <v>46150.11704861111</v>
       </c>
       <c r="R777" s="3">
-        <v>46150.09877314814</v>
+        <v>46150.11704861111</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>13081719k</t>
+          <t>160334290</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>Geramy navarro</t>
+          <t>Verónica</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Tomas rozas</t>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Berta</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>934837199</t>
+          <t>959866246</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>fabiola.gonzale.villar@gmail.com</t>
+          <t>cosita22-@hotmail.com</t>
         </is>
       </c>
       <c r="K778" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L778" t="inlineStr">
         <is>
-          <t>Puente alto</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="M778" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="N778" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O778" s="2">
-        <v>43563</v>
+        <v>46149</v>
       </c>
       <c r="P778" s="3">
-        <v>46150.10210648148</v>
+        <v>46150.07528935185</v>
       </c>
       <c r="Q778" s="3">
-        <v>46150.15333333334</v>
+        <v>46150.09877314814</v>
       </c>
       <c r="R778" s="3">
-        <v>46150.15333333334</v>
+        <v>46150.09877314814</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>105033206</t>
+          <t>13081719k</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Katerine</t>
+          <t>Geramy navarro</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Tomas rozas</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
         <is>
-          <t>951987113</t>
+          <t>934837199</t>
         </is>
       </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>katerine.farias1@iclaud.com</t>
+          <t>fabiola.gonzale.villar@gmail.com</t>
         </is>
       </c>
       <c r="K779" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L779" t="inlineStr">
         <is>
-          <t>Valparaiso</t>
+          <t>Puente alto</t>
         </is>
       </c>
       <c r="M779" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>37</t>
         </is>
       </c>
       <c r="N779" t="inlineStr">
@@ -49260,67 +49275,57 @@
         </is>
       </c>
       <c r="O779" s="2">
-        <v>46149</v>
+        <v>43563</v>
       </c>
       <c r="P779" s="3">
-        <v>46150.12767361111</v>
+        <v>46150.10210648148</v>
       </c>
       <c r="Q779" s="3">
-        <v>46150.18925925926</v>
+        <v>46150.15333333334</v>
       </c>
       <c r="R779" s="3">
-        <v>46150.18925925926</v>
+        <v>46150.15333333334</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>13081719k</t>
+          <t>105033206</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Katerine</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Patricio</t>
-        </is>
-      </c>
-      <c r="D780" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="E780" t="inlineStr">
-        <is>
-          <t>Julieta</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
         <is>
-          <t>996546036</t>
+          <t>951987113</t>
         </is>
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>carlaarandacorrea@gmail.com</t>
+          <t>katerine.farias1@iclaud.com</t>
         </is>
       </c>
       <c r="K780" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L780" t="inlineStr">
         <is>
-          <t>Sabtiago</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="M780" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="N780" t="inlineStr">
@@ -49332,128 +49337,123 @@
         <v>46149</v>
       </c>
       <c r="P780" s="3">
-        <v>46150.58122685185</v>
+        <v>46150.12767361111</v>
       </c>
       <c r="Q780" s="3">
-        <v>46150.60709490741</v>
+        <v>46150.18925925926</v>
       </c>
       <c r="R780" s="3">
-        <v>46150.60709490741</v>
+        <v>46150.18925925926</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>13305368-9</t>
+          <t>29568285-6</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Claudia Hermosilla</t>
+          <t>Tania Romero Carrasco</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Amanda Diaz Hermosilla</t>
-        </is>
-      </c>
-      <c r="D781" t="inlineStr">
-        <is>
-          <t>Alfonsina Díaz Hermosilla</t>
+          <t>Tobías Bascuñan Romero</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t>97967352</t>
+          <t>957419812</t>
         </is>
       </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>cvalhermosilla@gmail.com</t>
+          <t>Ta.romero.c@gmail.com</t>
         </is>
       </c>
       <c r="K781" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L781" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="M781" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="N781" t="inlineStr">
         <is>
-          <t>Empresa sin sello 40 horas</t>
+          <t>Empresa con sello 40 horas</t>
         </is>
       </c>
       <c r="O781" s="2">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="P781" s="3">
-        <v>46150.69798611111</v>
+        <v>46150.27762731482</v>
       </c>
       <c r="Q781" s="3">
-        <v>46150.72464120371</v>
+        <v>46151.24962962963</v>
       </c>
       <c r="R781" s="3">
-        <v>46150.72464120371</v>
+        <v>46151.24962962963</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>18.050.509-1</t>
+          <t>13081719k</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Rayen</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>Emilio</t>
+          <t>Julieta</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t>56966206968</t>
+          <t>996546036</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>barbra.faun@gmail.com</t>
+          <t>carlaarandacorrea@gmail.com</t>
         </is>
       </c>
       <c r="K782" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L782" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Sabtiago</t>
         </is>
       </c>
       <c r="M782" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>32</t>
         </is>
       </c>
       <c r="N782" t="inlineStr">
@@ -49462,42 +49462,47 @@
         </is>
       </c>
       <c r="O782" s="2">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="P782" s="3">
-        <v>46150.71868055555</v>
+        <v>46150.58122685185</v>
       </c>
       <c r="Q782" s="3">
-        <v>46150.76734953704</v>
+        <v>46150.60709490741</v>
       </c>
       <c r="R782" s="3">
-        <v>46150.76734953704</v>
+        <v>46150.60709490741</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>125897401</t>
+          <t>13305368-9</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Ide</t>
+          <t>Claudia Hermosilla</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Yohanna</t>
+          <t>Amanda Diaz Hermosilla</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Alfonsina Díaz Hermosilla</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>935225921</t>
+          <t>97967352</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>idearriagada@gmail.com</t>
+          <t>cvalhermosilla@gmail.com</t>
         </is>
       </c>
       <c r="K783" t="inlineStr">
@@ -49507,12 +49512,12 @@
       </c>
       <c r="L783" t="inlineStr">
         <is>
-          <t>TALXA</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="M783" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N783" t="inlineStr">
@@ -49521,62 +49526,67 @@
         </is>
       </c>
       <c r="O783" s="2">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="P783" s="3">
-        <v>46150.72909722223</v>
+        <v>46150.69798611111</v>
       </c>
       <c r="Q783" s="3">
-        <v>46150.75146990741</v>
+        <v>46150.72464120371</v>
       </c>
       <c r="R783" s="3">
-        <v>46150.75146990741</v>
+        <v>46150.72464120371</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>175682163</t>
+          <t>18.050.509-1</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Belen</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Rayen</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Emilio</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>989033752</t>
+          <t>56966206968</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>bele.castro.p@gmail.com</t>
+          <t>barbra.faun@gmail.com</t>
         </is>
       </c>
       <c r="K784" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L784" t="inlineStr">
         <is>
-          <t>Concon</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="M784" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>091</t>
         </is>
       </c>
       <c r="N784" t="inlineStr">
@@ -49588,84 +49598,1395 @@
         <v>46150</v>
       </c>
       <c r="P784" s="3">
-        <v>46150.74744212963</v>
+        <v>46150.71868055555</v>
       </c>
       <c r="Q784" s="3">
-        <v>46150.76724537037</v>
+        <v>46150.76734953704</v>
       </c>
       <c r="R784" s="3">
-        <v>46150.76724537037</v>
+        <v>46150.76734953704</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>175682163</t>
+          <t>125897401</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Daniela</t>
+          <t>Ide</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Rosa</t>
-        </is>
-      </c>
-      <c r="D785" t="inlineStr">
-        <is>
-          <t>Matias</t>
-        </is>
-      </c>
-      <c r="E785" t="inlineStr">
-        <is>
-          <t>Luciano</t>
-        </is>
-      </c>
-      <c r="F785" t="inlineStr">
-        <is>
-          <t>Elisa</t>
+          <t>Yohanna</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>977687764</t>
+          <t>935225921</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>daniela.sf.k@gmail.com</t>
+          <t>idearriagada@gmail.com</t>
         </is>
       </c>
       <c r="K785" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L785" t="inlineStr">
         <is>
-          <t>Quilpue</t>
+          <t>TALXA</t>
         </is>
       </c>
       <c r="M785" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="N785" t="inlineStr">
         <is>
-          <t>Empresa con sello 40 horas</t>
+          <t>Empresa sin sello 40 horas</t>
         </is>
       </c>
       <c r="O785" s="2">
         <v>46150</v>
       </c>
       <c r="P785" s="3">
+        <v>46150.72909722223</v>
+      </c>
+      <c r="Q785" s="3">
+        <v>46150.75146990741</v>
+      </c>
+      <c r="R785" s="3">
+        <v>46150.75146990741</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Belen</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>989033752</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>bele.castro.p@gmail.com</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>Concon</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N786" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O786" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P786" s="3">
+        <v>46150.74744212963</v>
+      </c>
+      <c r="Q786" s="3">
+        <v>46150.76724537037</v>
+      </c>
+      <c r="R786" s="3">
+        <v>46150.76724537037</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Luciano</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Elisa</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>977687764</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>daniela.sf.k@gmail.com</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>Quilpue</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O787" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P787" s="3">
         <v>46150.76731481482</v>
       </c>
-      <c r="R785" s="3">
-        <v>46150.76993055556</v>
+      <c r="Q787" s="3">
+        <v>46150.77721064815</v>
+      </c>
+      <c r="R787" s="3">
+        <v>46150.77721064815</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Nathaly salinas</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>933017123</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>bravonathaly594@gmail.com</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>Pte alto</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N788" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O788" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P788" s="3">
+        <v>46150.77685185186</v>
+      </c>
+      <c r="Q788" s="3">
+        <v>46150.80439814815</v>
+      </c>
+      <c r="R788" s="3">
+        <v>46150.80439814815</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>983712962</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>josepepeguerra@gmail.com</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N789" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O789" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P789" s="3">
+        <v>46150.77736111111</v>
+      </c>
+      <c r="Q789" s="3">
+        <v>46150.7925925926</v>
+      </c>
+      <c r="R789" s="3">
+        <v>46150.7925925926</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Matilde</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Isidora</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>9999999999</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>srodriguezi@inacap.cl</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O790" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P790" s="3">
+        <v>46150.79291666667</v>
+      </c>
+      <c r="Q790" s="3">
+        <v>46150.80523148148</v>
+      </c>
+      <c r="R790" s="3">
+        <v>46150.80523148148</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Malono</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>nicolas.gutierrez3@gmail.com</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N791" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O791" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P791" s="3">
+        <v>46150.81090277778</v>
+      </c>
+      <c r="Q791" s="3">
+        <v>46150.81938657408</v>
+      </c>
+      <c r="R791" s="3">
+        <v>46150.81938657408</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Baltazar</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>983712962</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>valentinacortes6@gmail.com</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O792" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P792" s="3">
+        <v>46150.85070601852</v>
+      </c>
+      <c r="Q792" s="3">
+        <v>46150.91142361111</v>
+      </c>
+      <c r="R792" s="3">
+        <v>46150.91142361111</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>175682163</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>976574742</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>felipe.ortiz.moreno@gmail.com</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>Viña del mar</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N793" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O793" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P793" s="3">
+        <v>46150.91185185185</v>
+      </c>
+      <c r="Q793" s="3">
+        <v>46150.9279050926</v>
+      </c>
+      <c r="R793" s="3">
+        <v>46150.9279050926</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Juana</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>976784364</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>noloda@gmail.com</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>9270-14</t>
+        </is>
+      </c>
+      <c r="N794" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O794" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P794" s="3">
+        <v>46151.02030092593</v>
+      </c>
+      <c r="Q794" s="3">
+        <v>46151.0521875</v>
+      </c>
+      <c r="R794" s="3">
+        <v>46151.05215277777</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>200730720</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>ejemplo</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>999999999999999999</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>an.pvaezh@gmail.com</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>valpraiso</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>encuesta de ejemplo</t>
+        </is>
+      </c>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O795" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P795" s="3">
+        <v>46151.03435185185</v>
+      </c>
+      <c r="Q795" s="3">
+        <v>46151.06518518519</v>
+      </c>
+      <c r="R795" s="3">
+        <v>46151.06515046296</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Cristian.</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Nicol</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>967067925</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>patricia.cardenas2178@gmail.com</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>9270-13</t>
+        </is>
+      </c>
+      <c r="N796" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O796" s="2">
+        <v>46151</v>
+      </c>
+      <c r="P796" s="3">
+        <v>46151.67547453704</v>
+      </c>
+      <c r="Q796" s="3">
+        <v>46151.70488425926</v>
+      </c>
+      <c r="R796" s="3">
+        <v>46151.70487268519</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Sebastián</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>988497131</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>elmo6067@gmail.com</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>Ñunoa</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>9270-15</t>
+        </is>
+      </c>
+      <c r="N797" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O797" s="2">
+        <v>46151</v>
+      </c>
+      <c r="P797" s="3">
+        <v>46151.80619212963</v>
+      </c>
+      <c r="Q797" s="3">
+        <v>46151.83134259259</v>
+      </c>
+      <c r="R797" s="3">
+        <v>46151.83134259259</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>20568285-6</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Karla Bahamondes</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Emily Moreno Bahamondes</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>56993317805</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>Karla.araus.bahamondes@gmail.com</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="N798" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O798" s="2">
+        <v>46150</v>
+      </c>
+      <c r="P798" s="3">
+        <v>46151.85035879629</v>
+      </c>
+      <c r="Q798" s="3">
+        <v>46151.89292824074</v>
+      </c>
+      <c r="R798" s="3">
+        <v>46151.89292824074</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Doris</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Berta</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Milton</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>989744344</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>Jacqueline98riveras@gmail.com</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>9270-15</t>
+        </is>
+      </c>
+      <c r="N799" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O799" s="2">
+        <v>46151</v>
+      </c>
+      <c r="P799" s="3">
+        <v>46151.86383101852</v>
+      </c>
+      <c r="Q799" s="3">
+        <v>46151.88270833333</v>
+      </c>
+      <c r="R799" s="3">
+        <v>46151.88270833333</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>189592701</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>991332795</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>vengasj10@gmail.com</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>Estacion central</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>9270-14</t>
+        </is>
+      </c>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O800" s="2">
+        <v>46151</v>
+      </c>
+      <c r="P800" s="3">
+        <v>46151.94351851851</v>
+      </c>
+      <c r="Q800" s="3">
+        <v>46151.96341435185</v>
+      </c>
+      <c r="R800" s="3">
+        <v>46151.96341435185</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Marcela</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>9 7570 7338</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>borgesmanuel615@gmail.com</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="N801" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O801" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P801" s="3">
+        <v>46153.69306712963</v>
+      </c>
+      <c r="Q801" s="3">
+        <v>46153.71498842593</v>
+      </c>
+      <c r="R801" s="3">
+        <v>46153.71498842593</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>155458975</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>942174867</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>valdebenitoogaldeoscaramdres@gmail.com</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O802" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P802" s="3">
+        <v>46153.75862268519</v>
+      </c>
+      <c r="Q802" s="3">
+        <v>46153.77246527778</v>
+      </c>
+      <c r="R802" s="3">
+        <v>46153.77246527778</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>204670528</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>constanza</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>odette</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>marcelo</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>catalina</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>belen</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>56991276542</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>constanzaulloa50@gmail.com</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>maule</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O803" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P803" s="3">
+        <v>46153.83768518519</v>
+      </c>
+      <c r="Q803" s="3">
+        <v>46153.85694444444</v>
+      </c>
+      <c r="R803" s="3">
+        <v>46153.85694444444</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>17442373-3</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>María Teresa</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Camilo</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>56984971541</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N804" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O804" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P804" s="3">
+        <v>46153.84171296297</v>
+      </c>
+      <c r="R804" s="3">
+        <v>46153.85741898148</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>155458975</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Patricio</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Trinidad</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>936211043</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>paredespinonespatricioantonio@gmail.com</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>Pirque</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="N805" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O805" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P805" s="3">
+        <v>46153.86465277777</v>
+      </c>
+      <c r="Q805" s="3">
+        <v>46153.87699074074</v>
+      </c>
+      <c r="R805" s="3">
+        <v>46153.87699074074</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>jose carrasco</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>amalia</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>56932847759</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>josemiguelcarrascothomas@gmail.com</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>la florida</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N806" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O806" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P806" s="3">
+        <v>46153.88606481481</v>
+      </c>
+      <c r="R806" s="3">
+        <v>46153.90050925926</v>
       </c>
     </row>
   </sheetData>

--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R806"/>
+  <dimension ref="A1:R822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="15" max="15" width="20.7109375" style="2" customWidth="1"/>
@@ -50877,27 +50877,27 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>155458975</t>
+          <t>19636993-7</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Patricio</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Trinidad</t>
+          <t>Fernanda</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
         <is>
-          <t>936211043</t>
+          <t>936443180</t>
         </is>
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>paredespinonespatricioantonio@gmail.com</t>
+          <t>manuel.borquez.farfan@gmail.com</t>
         </is>
       </c>
       <c r="K805" t="inlineStr">
@@ -50907,12 +50907,12 @@
       </c>
       <c r="L805" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>993</t>
         </is>
       </c>
       <c r="N805" t="inlineStr">
@@ -50924,39 +50924,39 @@
         <v>46153</v>
       </c>
       <c r="P805" s="3">
-        <v>46153.86465277777</v>
+        <v>46153.85958333334</v>
       </c>
       <c r="Q805" s="3">
-        <v>46153.87699074074</v>
+        <v>46154.10374999999</v>
       </c>
       <c r="R805" s="3">
-        <v>46153.87699074074</v>
+        <v>46154.10372685186</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>202372376</t>
+          <t>155458975</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>jose carrasco</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>amalia</t>
+          <t>Trinidad</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
         <is>
-          <t>56932847759</t>
+          <t>936211043</t>
         </is>
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>josemiguelcarrascothomas@gmail.com</t>
+          <t>paredespinonespatricioantonio@gmail.com</t>
         </is>
       </c>
       <c r="K806" t="inlineStr">
@@ -50966,12 +50966,12 @@
       </c>
       <c r="L806" t="inlineStr">
         <is>
-          <t>la florida</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="M806" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>897</t>
         </is>
       </c>
       <c r="N806" t="inlineStr">
@@ -50983,10 +50983,1007 @@
         <v>46153</v>
       </c>
       <c r="P806" s="3">
+        <v>46153.86465277777</v>
+      </c>
+      <c r="Q806" s="3">
+        <v>46153.87699074074</v>
+      </c>
+      <c r="R806" s="3">
+        <v>46153.87699074074</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>jose carrasco</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>amalia</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>56932847759</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>josemiguelcarrascothomas@gmail.com</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>la florida</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O807" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P807" s="3">
         <v>46153.88606481481</v>
       </c>
-      <c r="R806" s="3">
-        <v>46153.90050925926</v>
+      <c r="Q807" s="3">
+        <v>46153.91876157407</v>
+      </c>
+      <c r="R807" s="3">
+        <v>46153.91876157407</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>125228445</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>mmejias1973@yahoo.cl</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="N808" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O808" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P808" s="3">
+        <v>46153.95605324074</v>
+      </c>
+      <c r="Q808" s="3">
+        <v>46153.97439814814</v>
+      </c>
+      <c r="R808" s="3">
+        <v>46153.97439814814</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>19870558-6</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>977686171</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>cespedes.moller@gmail.com</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>ddd</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O809" s="2">
+        <v>46152</v>
+      </c>
+      <c r="P809" s="3">
+        <v>46153.98493055555</v>
+      </c>
+      <c r="R809" s="3">
+        <v>46154.03331018519</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>954908498</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>marco.correa@gmail.com</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="N810" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O810" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P810" s="3">
+        <v>46153.98953703704</v>
+      </c>
+      <c r="Q810" s="3">
+        <v>46154.01131944444</v>
+      </c>
+      <c r="R810" s="3">
+        <v>46154.01131944444</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>12522844-5</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Solange</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Hija 1</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Hijo 2</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>978467998</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>valearre27@gmail.com</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="N811" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O811" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P811" s="3">
+        <v>46154.00579861111</v>
+      </c>
+      <c r="Q811" s="3">
+        <v>46154.04957175926</v>
+      </c>
+      <c r="R811" s="3">
+        <v>46154.04953703703</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Mariela</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>984580906</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>edu.vito.ibacache@gmail.com</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O812" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P812" s="3">
+        <v>46154.02667824074</v>
+      </c>
+      <c r="Q812" s="3">
+        <v>46154.0522800926</v>
+      </c>
+      <c r="R812" s="3">
+        <v>46154.05225694444</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>204886369</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>joker persona 1</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>joker persona 2</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>56991412118</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>chavezolivaresd@gmail.com</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>chiguayork</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>204886369</t>
+        </is>
+      </c>
+      <c r="N813" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O813" s="2">
+        <v>44927</v>
+      </c>
+      <c r="P813" s="3">
+        <v>46154.0275462963</v>
+      </c>
+      <c r="R813" s="3">
+        <v>46154.10268518519</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Fabricio</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Macarena</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>956067197</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>fabricio.valenzuela2015@gmail.com</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O814" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P814" s="3">
+        <v>46154.06445601852</v>
+      </c>
+      <c r="Q814" s="3">
+        <v>46154.08399305555</v>
+      </c>
+      <c r="R814" s="3">
+        <v>46154.08396990741</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Paola</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Marcela</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>969407732</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>paolaguirrecerda@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="N815" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O815" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P815" s="3">
+        <v>46154.09425925926</v>
+      </c>
+      <c r="Q815" s="3">
+        <v>46154.11127314815</v>
+      </c>
+      <c r="R815" s="3">
+        <v>46154.11127314815</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Gonzalo</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Gladys</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>981827322</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>gonzalo.parra008@gmail.com</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="N816" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O816" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P816" s="3">
+        <v>46154.1200462963</v>
+      </c>
+      <c r="Q816" s="3">
+        <v>46154.18040509259</v>
+      </c>
+      <c r="R816" s="3">
+        <v>46154.18040509259</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>17442373-3</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>sofia</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>ignacio</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>benjamin</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>984657548</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>curicó</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N817" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O817" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P817" s="3">
+        <v>46154.1296412037</v>
+      </c>
+      <c r="Q817" s="3">
+        <v>46154.16207175926</v>
+      </c>
+      <c r="R817" s="3">
+        <v>46154.16207175926</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Maximo</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>967008474</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>katherineayala.39@gmail.com</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O818" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P818" s="3">
+        <v>46154.64964120371</v>
+      </c>
+      <c r="Q818" s="3">
+        <v>46154.67545138889</v>
+      </c>
+      <c r="R818" s="3">
+        <v>46154.67545138889</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>20432176-0</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>jo@d.cl</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O819" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P819" s="3">
+        <v>46154.66483796296</v>
+      </c>
+      <c r="R819" s="3">
+        <v>46154.67299768519</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>191656237</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>barbara</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>gianfranco</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>bfernandez@datodinamico.cl</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>recoleta</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O820" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P820" s="3">
+        <v>46154.6821412037</v>
+      </c>
+      <c r="R820" s="3">
+        <v>46154.72288194444</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Claudio</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Marisol</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>978713734</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>claudio.gonzalez@gmail.com</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O821" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P821" s="3">
+        <v>46154.69850694445</v>
+      </c>
+      <c r="Q821" s="3">
+        <v>46154.72174768518</v>
+      </c>
+      <c r="R821" s="3">
+        <v>46154.72174768518</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Corina morales</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Nicol</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>990950822</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>cori.amor2000@gmail.com</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O822" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P822" s="3">
+        <v>46154.72982638889</v>
+      </c>
+      <c r="R822" s="3">
+        <v>46154.73311342593</v>
       </c>
     </row>
   </sheetData>

--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R822"/>
+  <dimension ref="A1:R856"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="15" max="15" width="20.7109375" style="2" customWidth="1"/>
@@ -46906,7 +46906,7 @@
         <v>46148.03469907407</v>
       </c>
       <c r="R741" s="3">
-        <v>46152.82055555555</v>
+        <v>46155.76674768519</v>
       </c>
     </row>
     <row r="742">
@@ -51797,7 +51797,7 @@
         <v>46154.66483796296</v>
       </c>
       <c r="R819" s="3">
-        <v>46154.67299768519</v>
+        <v>46154.73608796296</v>
       </c>
     </row>
     <row r="820">
@@ -51928,47 +51928,42 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>12680885-2</t>
+          <t>174423733</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Corina morales</t>
+          <t>paulina</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>Mercedes</t>
-        </is>
-      </c>
-      <c r="D822" t="inlineStr">
-        <is>
-          <t>Nicol</t>
+          <t>pablo</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
         <is>
-          <t>990950822</t>
+          <t>9 59307085</t>
         </is>
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>cori.amor2000@gmail.com</t>
+          <t>polyta7@hotmail.com</t>
         </is>
       </c>
       <c r="K822" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L822" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>maipu</t>
         </is>
       </c>
       <c r="M822" t="inlineStr">
         <is>
-          <t>0885</t>
+          <t>823</t>
         </is>
       </c>
       <c r="N822" t="inlineStr">
@@ -51980,10 +51975,2003 @@
         <v>46154</v>
       </c>
       <c r="P822" s="3">
+        <v>46154.72644675926</v>
+      </c>
+      <c r="Q822" s="3">
+        <v>46154.93195601852</v>
+      </c>
+      <c r="R822" s="3">
+        <v>46154.93195601852</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Corina morales</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Nicol</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>990950822</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>cori.amor2000@gmail.com</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O823" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P823" s="3">
         <v>46154.72982638889</v>
       </c>
-      <c r="R822" s="3">
-        <v>46154.73311342593</v>
+      <c r="Q823" s="3">
+        <v>46154.75060185185</v>
+      </c>
+      <c r="R823" s="3">
+        <v>46154.75060185185</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>174423733</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Ericka martinez</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Lucas Hurtado</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>9 4988 3849</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>eckamar19@gmail.com</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>Curico</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O824" s="2">
+        <v>46082</v>
+      </c>
+      <c r="P824" s="3">
+        <v>46154.73454861112</v>
+      </c>
+      <c r="Q824" s="3">
+        <v>46154.7777662037</v>
+      </c>
+      <c r="R824" s="3">
+        <v>46154.7777662037</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>19529428-3</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>999999</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>correo@noda.cl</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>9428-1</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O825" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P825" s="3">
+        <v>46154.73810185185</v>
+      </c>
+      <c r="R825" s="3">
+        <v>46154.73981481481</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>12680885-2</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Gerardo</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Daniella</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Damian</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Darling</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>957112382</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>gerardomunozalvear@gmail.com</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>0885</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O826" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P826" s="3">
+        <v>46154.81519675926</v>
+      </c>
+      <c r="Q826" s="3">
+        <v>46154.83581018518</v>
+      </c>
+      <c r="R826" s="3">
+        <v>46154.83581018518</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>19870558</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>milagro</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>9903171737</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>rf_guzman@abbott.com</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>Quilpue</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>05581</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O827" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P827" s="3">
+        <v>46154.82553240741</v>
+      </c>
+      <c r="Q827" s="3">
+        <v>46155.6754050926</v>
+      </c>
+      <c r="R827" s="3">
+        <v>46155.6754050926</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>20429244-2</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>999999</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>anoda@gmail.com</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>9244-1</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O828" s="2">
+        <v>46156</v>
+      </c>
+      <c r="P828" s="3">
+        <v>46154.84509259259</v>
+      </c>
+      <c r="R828" s="3">
+        <v>46154.89787037037</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>180914803</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Clara</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>964264038</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>valentinabasaurebarra@gmail.com</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>1480-1</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O829" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P829" s="3">
+        <v>46154.8494212963</v>
+      </c>
+      <c r="Q829" s="3">
+        <v>46154.86608796296</v>
+      </c>
+      <c r="R829" s="3">
+        <v>46154.86608796296</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Armin</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Pamela</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>María Cristina</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>998281656</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>affkairos@gmail.com</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>Lo prado</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>9270-16</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O830" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P830" s="3">
+        <v>46154.87670138889</v>
+      </c>
+      <c r="Q830" s="3">
+        <v>46154.91215277778</v>
+      </c>
+      <c r="R830" s="3">
+        <v>46154.91215277778</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Fabián Basoalto</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Victoria Magaña</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Florencia Basoalto</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Trinidad Basoalto</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>998874228</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>fabian.basoalto@gmail.com</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O831" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P831" s="3">
+        <v>46154.89166666666</v>
+      </c>
+      <c r="Q831" s="3">
+        <v>46154.92760416667</v>
+      </c>
+      <c r="R831" s="3">
+        <v>46154.92760416667</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>20550416-8</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>rosa</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>luis</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>pedro</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>951502657</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>javisanchez.he@gmail.com</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>lo espejo</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>0416 - 1</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O832" s="2">
+        <v>46153</v>
+      </c>
+      <c r="P832" s="3">
+        <v>46154.91236111111</v>
+      </c>
+      <c r="R832" s="3">
+        <v>46154.92133101852</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>13.081.719-K</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Andres navarro</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Tomas navarro</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>984696113</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>bedection@gmail.com</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O833" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P833" s="3">
+        <v>46154.91456018519</v>
+      </c>
+      <c r="Q833" s="3">
+        <v>46154.94804398148</v>
+      </c>
+      <c r="R833" s="3">
+        <v>46154.94804398148</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>13081719-k</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Romina</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Renato</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>990571366</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>romamelie@gmail.com</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>Puente alto</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O834" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P834" s="3">
+        <v>46154.92605324074</v>
+      </c>
+      <c r="Q834" s="3">
+        <v>46154.95211805556</v>
+      </c>
+      <c r="R834" s="3">
+        <v>46154.95211805556</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>946886343</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>marttaeliana@gmail.com</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O835" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P835" s="3">
+        <v>46154.93003472222</v>
+      </c>
+      <c r="R835" s="3">
+        <v>46154.93233796296</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>19656237</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>barbara</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>gianfranco</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>bfernandez@datodinamico.cl</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>recoleta</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>623-A1</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O836" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P836" s="3">
+        <v>46154.93743055555</v>
+      </c>
+      <c r="R836" s="3">
+        <v>46155.7380324074</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>19113309-9</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>56933760848</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>maurireznov@gmail.com</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>3309-1</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O837" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P837" s="3">
+        <v>46154.93800925926</v>
+      </c>
+      <c r="R837" s="3">
+        <v>46154.94436342592</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>20486959-6</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Tamara Arias</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Claudio Saa</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Celeste</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>56997126026</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>tamaraarias@gmail.com</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>Chillan</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>76016305-8</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O838" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P838" s="3">
+        <v>46154.9822337963</v>
+      </c>
+      <c r="Q838" s="3">
+        <v>46155.06440972222</v>
+      </c>
+      <c r="R838" s="3">
+        <v>46155.06440972222</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>204321760</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Rosa Bernarda</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Sergio Anibal Letelier Sánchez</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Sebastián Andrés Quezada Sánchez</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>987040461</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>sewastian6@gmail.com</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O839" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P839" s="3">
+        <v>46155.00253472223</v>
+      </c>
+      <c r="Q839" s="3">
+        <v>46155.05016203703</v>
+      </c>
+      <c r="R839" s="3">
+        <v>46155.05013888889</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>174423733</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>tomas</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>984971540</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>notiene@gmail.com</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>talca</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O840" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P840" s="3">
+        <v>46155.01337962963</v>
+      </c>
+      <c r="R840" s="3">
+        <v>46155.01971064815</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>22495119-1</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Josefina</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>9 83320209</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>Urrutiajosefina3@gmail.com</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O841" s="2">
+        <v>46297</v>
+      </c>
+      <c r="P841" s="3">
+        <v>46155.02158564815</v>
+      </c>
+      <c r="Q841" s="3">
+        <v>46155.02950231481</v>
+      </c>
+      <c r="R841" s="3">
+        <v>46155.02947916667</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>174423733</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>alfredo</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>joseph</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>996827748</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>anonimo.44177@gmail.com</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>estacion central</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O842" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P842" s="3">
+        <v>46155.02347222222</v>
+      </c>
+      <c r="Q842" s="3">
+        <v>46155.04913194444</v>
+      </c>
+      <c r="R842" s="3">
+        <v>46155.04910879629</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>19912765-9</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Gudio</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>gus.salinas.var@gmail.com</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>765-1</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O843" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P843" s="3">
+        <v>46155.03611111111</v>
+      </c>
+      <c r="R843" s="3">
+        <v>46155.1019212963</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>125897401</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Martta</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Juana Maria opazo</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>946886343</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>marttaeliana@gmail.com</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O844" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P844" s="3">
+        <v>46155.05408564815</v>
+      </c>
+      <c r="Q844" s="3">
+        <v>46155.07151620371</v>
+      </c>
+      <c r="R844" s="3">
+        <v>46155.07150462962</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>18091480-3</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>José Luis Baquedano Agüero</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Valentina Alejandra Basaure Barra</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Suyai Fernanda Baquedano Basaure</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>931128596</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>joseluisbaquedano1990@gmail.com</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>1480-1</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O845" s="2">
+        <v>46154</v>
+      </c>
+      <c r="P845" s="3">
+        <v>46155.09763888889</v>
+      </c>
+      <c r="R845" s="3">
+        <v>46155.13680555555</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>199127659</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>gus.salinas.var@gmail.com</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>765-A1</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O846" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P846" s="3">
+        <v>46155.6484375</v>
+      </c>
+      <c r="R846" s="3">
+        <v>46155.65204861111</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>13305368-9</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>María Jesús Benavides</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Cristián Deik</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>María Jesús Deik Benavides</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Lucas Deik Benavides</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Mateo Deik Benavides</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>968486356</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>mjesusbenavides@gmail.com</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O847" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P847" s="3">
+        <v>46155.67881944445</v>
+      </c>
+      <c r="Q847" s="3">
+        <v>46155.70708333333</v>
+      </c>
+      <c r="R847" s="3">
+        <v>46155.70708333333</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>19912765-9</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Tomás Parra</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>942445367</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>gus.salinas.vargas@gmail.com</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>775-A1</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O848" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P848" s="3">
+        <v>46155.68326388889</v>
+      </c>
+      <c r="Q848" s="3">
+        <v>46155.75493055556</v>
+      </c>
+      <c r="R848" s="3">
+        <v>46155.75491898148</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>20432176-0</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Patricio  Vega</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Maricel Henríquez</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Brayan Vega</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Lucero Vega</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>950288790</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>pvega@scuola.cl</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>Peñalolen</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O849" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P849" s="3">
+        <v>46155.6999537037</v>
+      </c>
+      <c r="Q849" s="3">
+        <v>46155.74170138889</v>
+      </c>
+      <c r="R849" s="3">
+        <v>46155.74170138889</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>17442373-3</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>984009195</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>marite.cont@gmail.com</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O850" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P850" s="3">
+        <v>46155.7006712963</v>
+      </c>
+      <c r="R850" s="3">
+        <v>46155.70195601851</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>17442373-3</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>984009195</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>marite.cont@gmail.com</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>Curico</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O851" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P851" s="3">
+        <v>46155.70197916667</v>
+      </c>
+      <c r="Q851" s="3">
+        <v>46155.74965277778</v>
+      </c>
+      <c r="R851" s="3">
+        <v>46155.74965277778</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>marcelo alvarado</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>patricia</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>noah alvarado</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>56999649208</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>maac79@gmail.com</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>puente alto</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O852" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P852" s="3">
+        <v>46155.70721064815</v>
+      </c>
+      <c r="Q852" s="3">
+        <v>46155.72563657408</v>
+      </c>
+      <c r="R852" s="3">
+        <v>46155.72563657408</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>jairo ulloa</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>karla winter</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>iker ulloa</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>34132619</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>jairoulloa00@gmail.com</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>la florida</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O853" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P853" s="3">
+        <v>46155.72572916667</v>
+      </c>
+      <c r="Q853" s="3">
+        <v>46155.74384259259</v>
+      </c>
+      <c r="R853" s="3">
+        <v>46155.74384259259</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>125228445</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>964783223</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>luzsanchezs@gmail.com</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O854" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P854" s="3">
+        <v>46155.74077546297</v>
+      </c>
+      <c r="Q854" s="3">
+        <v>46155.776875</v>
+      </c>
+      <c r="R854" s="3">
+        <v>46155.776875</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>elizabeth yefe</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>camilo</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>mia ovando</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>56989136099</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>elizabeth00@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>cisterna</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O855" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P855" s="3">
+        <v>46155.74596064815</v>
+      </c>
+      <c r="Q855" s="3">
+        <v>46155.75579861111</v>
+      </c>
+      <c r="R855" s="3">
+        <v>46155.75579861111</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>odette alvarez</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>alejandro cofre</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>hector cofre</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>karla cofre</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>56983026769</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>palvares99@gmail.com</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>puente alto</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O856" s="2">
+        <v>46155</v>
+      </c>
+      <c r="P856" s="3">
+        <v>46155.77892361111</v>
+      </c>
+      <c r="R856" s="3">
+        <v>46155.78762731481</v>
       </c>
     </row>
   </sheetData>

--- a/output/clio.xlsx
+++ b/output/clio.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1275"/>
+  <dimension ref="A1:R1352"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="16" max="16" width="20.7109375" style="2" customWidth="1"/>
@@ -57674,7 +57674,7 @@
       </c>
       <c r="R837" t="inlineStr">
         <is>
-          <t>2026-05-13 17:42:46</t>
+          <t>2026-05-19 16:24:10</t>
         </is>
       </c>
     </row>
@@ -63044,7 +63044,7 @@
       </c>
       <c r="R918" t="inlineStr">
         <is>
-          <t>2026-05-18 17:48:16</t>
+          <t>2026-05-18 20:34:50</t>
         </is>
       </c>
     </row>
@@ -87767,9 +87767,5219 @@
       <c r="P1275" s="2">
         <v>46160.90010416666</v>
       </c>
+      <c r="Q1275" t="inlineStr">
+        <is>
+          <t>2026-05-18 18:36:28</t>
+        </is>
+      </c>
       <c r="R1275" t="inlineStr">
         <is>
-          <t>2026-05-18 17:46:16</t>
+          <t>2026-05-18 18:36:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>13955210-5</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fernando </t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Josefa</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Maite</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>96552365</t>
+        </is>
+      </c>
+      <c r="J1276" t="inlineStr">
+        <is>
+          <t>Fernandosalgadomartinesteban@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1276" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santiago </t>
+        </is>
+      </c>
+      <c r="M1276" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1276" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1276" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P1276" s="2">
+        <v>46160.91861111111</v>
+      </c>
+      <c r="Q1276" t="inlineStr">
+        <is>
+          <t>2026-05-18 18:41:17</t>
+        </is>
+      </c>
+      <c r="R1276" t="inlineStr">
+        <is>
+          <t>2026-05-18 18:41:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Gabriela</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carmencita </t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Eliana</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Jacinta</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>68172797658</t>
+        </is>
+      </c>
+      <c r="J1277" t="inlineStr">
+        <is>
+          <t>facundoreugonzal@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1277" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1277" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1277" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1277" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1277" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1277" s="2">
+        <v>46160.93809027778</v>
+      </c>
+      <c r="Q1277" t="inlineStr">
+        <is>
+          <t>2026-05-18 18:46:26</t>
+        </is>
+      </c>
+      <c r="R1277" t="inlineStr">
+        <is>
+          <t>2026-05-18 18:46:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Raquel</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Nilsa</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="J1278" t="inlineStr">
+        <is>
+          <t>alfonsoeliasriiico@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1278" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1278" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1278" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1278" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1278" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1278" s="2">
+        <v>46160.93880787037</v>
+      </c>
+      <c r="Q1278" t="inlineStr">
+        <is>
+          <t>2026-05-18 18:49:04</t>
+        </is>
+      </c>
+      <c r="R1278" t="inlineStr">
+        <is>
+          <t>2026-05-18 18:49:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>135654590</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Miguel </t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>pamela</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>isabel</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>962265266</t>
+        </is>
+      </c>
+      <c r="J1279" t="inlineStr">
+        <is>
+          <t>migue.construccion2@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1279" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pudahuel </t>
+        </is>
+      </c>
+      <c r="M1279" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1279" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1279" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1279" s="2">
+        <v>46160.94622685185</v>
+      </c>
+      <c r="Q1279" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:13:18</t>
+        </is>
+      </c>
+      <c r="R1279" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:13:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>13955210-5</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amaro </t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matías </t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>942850337</t>
+        </is>
+      </c>
+      <c r="J1280" t="inlineStr">
+        <is>
+          <t>amarovargas23@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1280" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maipú </t>
+        </is>
+      </c>
+      <c r="M1280" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1280" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1280" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P1280" s="2">
+        <v>46160.94853009259</v>
+      </c>
+      <c r="Q1280" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:11:10</t>
+        </is>
+      </c>
+      <c r="R1280" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:11:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Tania</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Josefa</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Anais</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>9897522578</t>
+        </is>
+      </c>
+      <c r="J1281" t="inlineStr">
+        <is>
+          <t>vaniacpntrerasras@gmail.con</t>
+        </is>
+      </c>
+      <c r="K1281" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1281" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1281" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1281" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1281" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1281" s="2">
+        <v>46160.94958333333</v>
+      </c>
+      <c r="Q1281" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:04:07</t>
+        </is>
+      </c>
+      <c r="R1281" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:04:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222191440 </t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lucas </t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joselyn </t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>957577757</t>
+        </is>
+      </c>
+      <c r="J1282" t="inlineStr">
+        <is>
+          <t>lucasfierro@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1282" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Florida </t>
+        </is>
+      </c>
+      <c r="M1282" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="N1282" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1282" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1282" s="2">
+        <v>46160.95028935185</v>
+      </c>
+      <c r="Q1282" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:06:53</t>
+        </is>
+      </c>
+      <c r="R1282" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:06:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Gaston</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Erna</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Nnacy</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="J1283" t="inlineStr">
+        <is>
+          <t>isaaacrabdduosjesus@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1283" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1283" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1283" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1283" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1283" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1283" s="2">
+        <v>46160.95114583333</v>
+      </c>
+      <c r="Q1283" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:03:36</t>
+        </is>
+      </c>
+      <c r="R1283" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:03:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>139552105</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juan </t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elizabeth </t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Benjaminy</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renato </t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>957457720</t>
+        </is>
+      </c>
+      <c r="J1284" t="inlineStr">
+        <is>
+          <t>noloentrega@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1284" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1284" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="M1284" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1284" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1284" t="inlineStr">
+        <is>
+          <t>1979-03-15</t>
+        </is>
+      </c>
+      <c r="P1284" s="2">
+        <v>46160.95434027778</v>
+      </c>
+      <c r="Q1284" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:57:37</t>
+        </is>
+      </c>
+      <c r="R1284" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:57:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>13955210-5</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facundo </t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Maite</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ignacia </t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>937019851</t>
+        </is>
+      </c>
+      <c r="J1285" t="inlineStr">
+        <is>
+          <t>facundosalazar@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1285" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La florida </t>
+        </is>
+      </c>
+      <c r="M1285" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1285" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1285" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P1285" s="2">
+        <v>46160.968125</v>
+      </c>
+      <c r="Q1285" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:31:39</t>
+        </is>
+      </c>
+      <c r="R1285" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:31:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>139552105</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Benjamín. </t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tomás </t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>933557474</t>
+        </is>
+      </c>
+      <c r="J1286" t="inlineStr">
+        <is>
+          <t>jenniferchochito@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1286" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1286" t="inlineStr">
+        <is>
+          <t>Estación central</t>
+        </is>
+      </c>
+      <c r="M1286" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1286" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1286" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="P1286" s="2">
+        <v>46160.97193287036</v>
+      </c>
+      <c r="Q1286" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:00:05</t>
+        </is>
+      </c>
+      <c r="R1286" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>135654590</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>bastian</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>ignacia oyarce</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">francisco Ignacio </t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>957867485</t>
+        </is>
+      </c>
+      <c r="J1287" t="inlineStr">
+        <is>
+          <t>bastisilva@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1287" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la florida </t>
+        </is>
+      </c>
+      <c r="M1287" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1287" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1287" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1287" s="2">
+        <v>46160.97776620371</v>
+      </c>
+      <c r="Q1287" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:02:29</t>
+        </is>
+      </c>
+      <c r="R1287" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:02:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>12549041-7</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Angelica</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">David </t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Camila </t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>964377649</t>
+        </is>
+      </c>
+      <c r="J1288" t="inlineStr">
+        <is>
+          <t>angelicarrosario@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1288" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maipú </t>
+        </is>
+      </c>
+      <c r="M1288" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1288" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1288" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1288" s="2">
+        <v>46160.99722222222</v>
+      </c>
+      <c r="Q1288" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:40:45</t>
+        </is>
+      </c>
+      <c r="R1288" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:40:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>127289433</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>925463815</t>
+        </is>
+      </c>
+      <c r="J1289" t="inlineStr">
+        <is>
+          <t>lorena3436.8@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1289" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1289" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="M1289" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1289" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1289" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1289" s="2">
+        <v>46161.00548611111</v>
+      </c>
+      <c r="Q1289" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:36:16</t>
+        </is>
+      </c>
+      <c r="R1289" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:36:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>139552105</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Brenda</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joaquín </t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Alberto</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>975181812</t>
+        </is>
+      </c>
+      <c r="J1290" t="inlineStr">
+        <is>
+          <t>belizaba@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1290" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1290" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="M1290" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="N1290" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1290" t="inlineStr">
+        <is>
+          <t>1980-03-15</t>
+        </is>
+      </c>
+      <c r="P1290" s="2">
+        <v>46161.00943287037</v>
+      </c>
+      <c r="R1290" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:21:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>139552105</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brenda </t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alberto </t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>975181812</t>
+        </is>
+      </c>
+      <c r="J1291" t="inlineStr">
+        <is>
+          <t>bellizaba@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1291" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maipu </t>
+        </is>
+      </c>
+      <c r="M1291" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1291" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1291" t="inlineStr">
+        <is>
+          <t>1980-02-15</t>
+        </is>
+      </c>
+      <c r="P1291" s="2">
+        <v>46161.01486111111</v>
+      </c>
+      <c r="Q1291" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:47:14</t>
+        </is>
+      </c>
+      <c r="R1291" t="inlineStr">
+        <is>
+          <t>2026-05-18 20:47:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222191440 </t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martina </t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Francisco </t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>965756722</t>
+        </is>
+      </c>
+      <c r="J1292" t="inlineStr">
+        <is>
+          <t>martinazamorano@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1292" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Florida </t>
+        </is>
+      </c>
+      <c r="M1292" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="N1292" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1292" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1292" s="2">
+        <v>46161.03439814815</v>
+      </c>
+      <c r="Q1292" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:38:36</t>
+        </is>
+      </c>
+      <c r="R1292" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:38:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>139552105</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nielsen </t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Angela </t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>976019435</t>
+        </is>
+      </c>
+      <c r="J1293" t="inlineStr">
+        <is>
+          <t>noloindica@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1293" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1293" t="inlineStr">
+        <is>
+          <t>Maipi</t>
+        </is>
+      </c>
+      <c r="M1293" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1293" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1293" t="inlineStr">
+        <is>
+          <t>1975-09-06</t>
+        </is>
+      </c>
+      <c r="P1293" s="2">
+        <v>46161.03983796296</v>
+      </c>
+      <c r="Q1293" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:30:31</t>
+        </is>
+      </c>
+      <c r="R1293" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:30:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>175458975</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Marce</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>+56 9 3389 0456</t>
+        </is>
+      </c>
+      <c r="J1294" t="inlineStr">
+        <is>
+          <t>Pilar82rivera@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1294" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1294" t="inlineStr">
+        <is>
+          <t>Santiago centro</t>
+        </is>
+      </c>
+      <c r="M1294" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="N1294" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1294" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1294" s="2">
+        <v>46161.04333333333</v>
+      </c>
+      <c r="Q1294" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:30:50</t>
+        </is>
+      </c>
+      <c r="R1294" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:30:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>12549041-7</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Javier </t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rodrigo </t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>949883883</t>
+        </is>
+      </c>
+      <c r="J1295" t="inlineStr">
+        <is>
+          <t>maria_quintana@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1295" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La florida </t>
+        </is>
+      </c>
+      <c r="M1295" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1295" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1295" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1295" s="2">
+        <v>46161.04358796297</v>
+      </c>
+      <c r="Q1295" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:51:29</t>
+        </is>
+      </c>
+      <c r="R1295" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:51:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2222</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>8531</t>
+        </is>
+      </c>
+      <c r="J1296" t="inlineStr">
+        <is>
+          <t>benjamin.sifri@gmail.com</t>
+        </is>
+      </c>
+      <c r="M1296" t="inlineStr">
+        <is>
+          <t>2222</t>
+        </is>
+      </c>
+      <c r="N1296" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1296" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1296" s="2">
+        <v>46161.05618055556</v>
+      </c>
+      <c r="R1296" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:22:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Hernan</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Juliana</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>989010134</t>
+        </is>
+      </c>
+      <c r="J1297" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1297" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1297" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1297" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1297" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1297" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1297" s="2">
+        <v>46161.06046296297</v>
+      </c>
+      <c r="Q1297" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:45:07</t>
+        </is>
+      </c>
+      <c r="R1297" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:45:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>139552105</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juan Pablo </t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Karen </t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lucas </t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>958462666</t>
+        </is>
+      </c>
+      <c r="J1298" t="inlineStr">
+        <is>
+          <t>noloindica@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1298" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maipu </t>
+        </is>
+      </c>
+      <c r="M1298" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1298" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1298" t="inlineStr">
+        <is>
+          <t>1980-09-06</t>
+        </is>
+      </c>
+      <c r="P1298" s="2">
+        <v>46161.06644675926</v>
+      </c>
+      <c r="Q1298" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:10:10</t>
+        </is>
+      </c>
+      <c r="R1298" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>paola</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>estefania</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>diego</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>945329854</t>
+        </is>
+      </c>
+      <c r="J1299" t="inlineStr">
+        <is>
+          <t>pandreadiez43@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1299" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1299" t="inlineStr">
+        <is>
+          <t>san joaquin</t>
+        </is>
+      </c>
+      <c r="M1299" t="inlineStr">
+        <is>
+          <t>9270-24</t>
+        </is>
+      </c>
+      <c r="N1299" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1299" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1299" s="2">
+        <v>46161.06834490741</v>
+      </c>
+      <c r="Q1299" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:12:44</t>
+        </is>
+      </c>
+      <c r="R1299" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:12:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222191440 </t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tomas </t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Almendra </t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>977577270</t>
+        </is>
+      </c>
+      <c r="J1300" t="inlineStr">
+        <is>
+          <t>tomasnavia@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1300" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Florida </t>
+        </is>
+      </c>
+      <c r="M1300" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="N1300" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1300" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1300" s="2">
+        <v>46161.07251157408</v>
+      </c>
+      <c r="Q1300" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:52:14</t>
+        </is>
+      </c>
+      <c r="R1300" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:52:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>12549041-7</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eduardo </t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sofia </t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>982446289</t>
+        </is>
+      </c>
+      <c r="J1301" t="inlineStr">
+        <is>
+          <t>edurmerinohimojosa@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1301" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1301" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="M1301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1301" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1301" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1301" s="2">
+        <v>46161.08008101852</v>
+      </c>
+      <c r="Q1301" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:40:31</t>
+        </is>
+      </c>
+      <c r="R1301" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:40:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>937829621</t>
+        </is>
+      </c>
+      <c r="J1302" t="inlineStr">
+        <is>
+          <t>andres.farias@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1302" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1302" t="inlineStr">
+        <is>
+          <t>San miguel</t>
+        </is>
+      </c>
+      <c r="M1302" t="inlineStr">
+        <is>
+          <t>0376-22</t>
+        </is>
+      </c>
+      <c r="N1302" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1302" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1302" s="2">
+        <v>46161.08030092593</v>
+      </c>
+      <c r="R1302" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:36:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>13565459-0</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>felipe</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>soledad</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>santino</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>942578153</t>
+        </is>
+      </c>
+      <c r="J1303" t="inlineStr">
+        <is>
+          <t>felipe.gon04@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K1303" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1303" t="inlineStr">
+        <is>
+          <t>maipu</t>
+        </is>
+      </c>
+      <c r="M1303" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1303" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1303" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1303" s="2">
+        <v>46161.08195601852</v>
+      </c>
+      <c r="Q1303" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:32:23</t>
+        </is>
+      </c>
+      <c r="R1303" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:32:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222191440 </t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diego </t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Josefa </t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matías </t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>967576475</t>
+        </is>
+      </c>
+      <c r="J1304" t="inlineStr">
+        <is>
+          <t>diegoiturra@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1304" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Florida </t>
+        </is>
+      </c>
+      <c r="M1304" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="N1304" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1304" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1304" s="2">
+        <v>46161.08453703704</v>
+      </c>
+      <c r="Q1304" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:20:15</t>
+        </is>
+      </c>
+      <c r="R1304" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:20:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>119889332</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raul </t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>976718826</t>
+        </is>
+      </c>
+      <c r="J1305" t="inlineStr">
+        <is>
+          <t>raulzairr8@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1305" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1305" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="M1305" t="inlineStr">
+        <is>
+          <t>9332</t>
+        </is>
+      </c>
+      <c r="N1305" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1305" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1305" s="2">
+        <v>46161.09180555555</v>
+      </c>
+      <c r="Q1305" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:00:29</t>
+        </is>
+      </c>
+      <c r="R1305" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>186762762</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cecilia </t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carlos </t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>984596036</t>
+        </is>
+      </c>
+      <c r="J1306" t="inlineStr">
+        <is>
+          <t>nubleencuestas@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1306" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pudahuel </t>
+        </is>
+      </c>
+      <c r="M1306" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N1306" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1306" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1306" s="2">
+        <v>46161.09395833334</v>
+      </c>
+      <c r="Q1306" t="inlineStr">
+        <is>
+          <t>2026-05-19 03:03:47</t>
+        </is>
+      </c>
+      <c r="R1306" t="inlineStr">
+        <is>
+          <t>2026-05-19 03:03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>139552105</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Osvaldo </t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Nayadet</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>921882696</t>
+        </is>
+      </c>
+      <c r="J1307" t="inlineStr">
+        <is>
+          <t>noloindca@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1307" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maipu </t>
+        </is>
+      </c>
+      <c r="M1307" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1307" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1307" t="inlineStr">
+        <is>
+          <t>1975-03-15</t>
+        </is>
+      </c>
+      <c r="P1307" s="2">
+        <v>46161.09936342592</v>
+      </c>
+      <c r="Q1307" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:48:29</t>
+        </is>
+      </c>
+      <c r="R1307" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:48:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>jorge</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>fernanda</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>melissa</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>994401289</t>
+        </is>
+      </c>
+      <c r="J1308" t="inlineStr">
+        <is>
+          <t>jorgeolivav@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1308" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1308" t="inlineStr">
+        <is>
+          <t>san joaquin</t>
+        </is>
+      </c>
+      <c r="M1308" t="inlineStr">
+        <is>
+          <t>9270-24</t>
+        </is>
+      </c>
+      <c r="N1308" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1308" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1308" s="2">
+        <v>46161.10119212963</v>
+      </c>
+      <c r="Q1308" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:03:42</t>
+        </is>
+      </c>
+      <c r="R1308" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:03:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222191440 </t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alvaro </t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florencia </t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>976578767</t>
+        </is>
+      </c>
+      <c r="J1309" t="inlineStr">
+        <is>
+          <t>alvarorojas@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1309" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Florida </t>
+        </is>
+      </c>
+      <c r="M1309" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="N1309" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1309" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1309" s="2">
+        <v>46161.10600694444</v>
+      </c>
+      <c r="Q1309" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:43:49</t>
+        </is>
+      </c>
+      <c r="R1309" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:43:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>12549041-7</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tomás </t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Silvia </t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>985133474</t>
+        </is>
+      </c>
+      <c r="J1310" t="inlineStr">
+        <is>
+          <t>maria_sepulveda49@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1310" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1310" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="M1310" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1310" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1310" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1310" s="2">
+        <v>46161.11608796296</v>
+      </c>
+      <c r="Q1310" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:30:06</t>
+        </is>
+      </c>
+      <c r="R1310" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:30:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>17250376-4</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>937829621</t>
+        </is>
+      </c>
+      <c r="J1311" t="inlineStr">
+        <is>
+          <t>andres.farias@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1311" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1311" t="inlineStr">
+        <is>
+          <t>San miguel</t>
+        </is>
+      </c>
+      <c r="M1311" t="inlineStr">
+        <is>
+          <t>0376-22</t>
+        </is>
+      </c>
+      <c r="N1311" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1311" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1311" s="2">
+        <v>46161.11648148148</v>
+      </c>
+      <c r="Q1311" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:10:21</t>
+        </is>
+      </c>
+      <c r="R1311" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:10:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222191440 </t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vicente </t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marisol </t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>937576487</t>
+        </is>
+      </c>
+      <c r="J1312" t="inlineStr">
+        <is>
+          <t>vicentepalma@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1312" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Florida </t>
+        </is>
+      </c>
+      <c r="M1312" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="N1312" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1312" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1312" s="2">
+        <v>46161.12142361111</v>
+      </c>
+      <c r="Q1312" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:10:03</t>
+        </is>
+      </c>
+      <c r="R1312" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>139552105</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Romina</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Julián </t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Agustin</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>937214551</t>
+        </is>
+      </c>
+      <c r="J1313" t="inlineStr">
+        <is>
+          <t>romina1520.tobe@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1313" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1313" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="M1313" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1313" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1313" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="P1313" s="2">
+        <v>46161.13026620371</v>
+      </c>
+      <c r="Q1313" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:07:41</t>
+        </is>
+      </c>
+      <c r="R1313" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:07:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Guillermina</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Tatiana</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>92763527919</t>
+        </is>
+      </c>
+      <c r="J1314" t="inlineStr">
+        <is>
+          <t>sergiopollolomcdilan@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1314" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1314" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1314" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1314" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1314" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1314" s="2">
+        <v>46161.13479166667</v>
+      </c>
+      <c r="Q1314" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:38:10</t>
+        </is>
+      </c>
+      <c r="R1314" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:38:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222191440 </t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maximiliano </t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antonia </t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>976728464</t>
+        </is>
+      </c>
+      <c r="J1315" t="inlineStr">
+        <is>
+          <t>maximilianocid@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1315" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Florida </t>
+        </is>
+      </c>
+      <c r="M1315" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="N1315" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1315" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1315" s="2">
+        <v>46161.13721064814</v>
+      </c>
+      <c r="Q1315" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:38:35</t>
+        </is>
+      </c>
+      <c r="R1315" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:38:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>18959270-1</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andres </t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>antonio</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>berta</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>955194247</t>
+        </is>
+      </c>
+      <c r="J1316" t="inlineStr">
+        <is>
+          <t>andres.farias@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1316" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1316" t="inlineStr">
+        <is>
+          <t>la cisterna</t>
+        </is>
+      </c>
+      <c r="M1316" t="inlineStr">
+        <is>
+          <t>9270-24</t>
+        </is>
+      </c>
+      <c r="N1316" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1316" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1316" s="2">
+        <v>46161.14310185185</v>
+      </c>
+      <c r="Q1316" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:58:22</t>
+        </is>
+      </c>
+      <c r="R1316" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:58:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>19636993-7</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Gimena</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>935580741</t>
+        </is>
+      </c>
+      <c r="J1317" t="inlineStr">
+        <is>
+          <t>gimena.villamizar@wom.cl</t>
+        </is>
+      </c>
+      <c r="K1317" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1317" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="M1317" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="N1317" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1317" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1317" s="2">
+        <v>46161.14559027778</v>
+      </c>
+      <c r="Q1317" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:47:29</t>
+        </is>
+      </c>
+      <c r="R1317" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>11988933-2</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>alexis zapata</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>9 7799 7207</t>
+        </is>
+      </c>
+      <c r="J1318" t="inlineStr">
+        <is>
+          <t>zm92.alexis@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1318" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1318" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="M1318" t="inlineStr">
+        <is>
+          <t>9332</t>
+        </is>
+      </c>
+      <c r="N1318" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1318" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1318" s="2">
+        <v>46161.1606712963</v>
+      </c>
+      <c r="Q1318" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:39:30</t>
+        </is>
+      </c>
+      <c r="R1318" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:39:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222191440 </t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gaspar </t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amanda </t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>947578467</t>
+        </is>
+      </c>
+      <c r="J1319" t="inlineStr">
+        <is>
+          <t>gasparmunoz@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1319" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Florida </t>
+        </is>
+      </c>
+      <c r="M1319" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="N1319" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1319" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1319" s="2">
+        <v>46161.16707175926</v>
+      </c>
+      <c r="Q1319" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:45:05</t>
+        </is>
+      </c>
+      <c r="R1319" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>12549041-7</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pamela </t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sebastián </t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isabel </t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcelo </t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Milan </t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>959019812</t>
+        </is>
+      </c>
+      <c r="J1320" t="inlineStr">
+        <is>
+          <t>pamelarodri24@gmail.cl</t>
+        </is>
+      </c>
+      <c r="K1320" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Puente alto </t>
+        </is>
+      </c>
+      <c r="M1320" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1320" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1320" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1320" s="2">
+        <v>46161.17104166667</v>
+      </c>
+      <c r="Q1320" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:42:53</t>
+        </is>
+      </c>
+      <c r="R1320" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:42:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98784624 </t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Génesis </t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Agustin</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>946452680</t>
+        </is>
+      </c>
+      <c r="J1321" t="inlineStr">
+        <is>
+          <t>gns.pvz14@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1321" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Puente Alto </t>
+        </is>
+      </c>
+      <c r="M1321" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="N1321" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1321" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1321" s="2">
+        <v>46161.17322916667</v>
+      </c>
+      <c r="R1321" t="inlineStr">
+        <is>
+          <t>2026-05-19 03:11:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Saul</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Gerald</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Romina</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>Solange</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>981716781</t>
+        </is>
+      </c>
+      <c r="J1322" t="inlineStr">
+        <is>
+          <t>raulithotuchiquito@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1322" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1322" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1322" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1322" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1322" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1322" s="2">
+        <v>46161.17381944445</v>
+      </c>
+      <c r="Q1322" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:31:11</t>
+        </is>
+      </c>
+      <c r="R1322" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:31:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Sofhia</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Damian</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Amaro</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>958062314</t>
+        </is>
+      </c>
+      <c r="J1323" t="inlineStr">
+        <is>
+          <t>sofhiacsm@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1323" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1323" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1323" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1323" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1323" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1323" s="2">
+        <v>46161.18861111111</v>
+      </c>
+      <c r="Q1323" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:49:29</t>
+        </is>
+      </c>
+      <c r="R1323" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:49:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>119889332</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>raul</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>9 2728 8415</t>
+        </is>
+      </c>
+      <c r="J1324" t="inlineStr">
+        <is>
+          <t>raulzankerot@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1324" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1324" t="inlineStr">
+        <is>
+          <t>santiago</t>
+        </is>
+      </c>
+      <c r="M1324" t="inlineStr">
+        <is>
+          <t>9332</t>
+        </is>
+      </c>
+      <c r="N1324" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1324" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P1324" s="2">
+        <v>46161.1971875</v>
+      </c>
+      <c r="Q1324" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:39:45</t>
+        </is>
+      </c>
+      <c r="R1324" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:39:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>19994102-k</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>marcela</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Raul</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>990572059</t>
+        </is>
+      </c>
+      <c r="J1325" t="inlineStr">
+        <is>
+          <t>ricardo.alvarezespina98@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1325" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1325" t="inlineStr">
+        <is>
+          <t>recoleta</t>
+        </is>
+      </c>
+      <c r="M1325" t="inlineStr">
+        <is>
+          <t>4102-1</t>
+        </is>
+      </c>
+      <c r="N1325" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1325" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1325" s="2">
+        <v>46161.19868055556</v>
+      </c>
+      <c r="Q1325" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:13:59</t>
+        </is>
+      </c>
+      <c r="R1325" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:13:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>12549041-7</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcelo </t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cristóbal </t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>993026956</t>
+        </is>
+      </c>
+      <c r="J1326" t="inlineStr">
+        <is>
+          <t>l_sanhueza20@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1326" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peñalolén </t>
+        </is>
+      </c>
+      <c r="M1326" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1326" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1326" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1326" s="2">
+        <v>46161.20591435186</v>
+      </c>
+      <c r="Q1326" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:44:43</t>
+        </is>
+      </c>
+      <c r="R1326" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:44:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19313240-5 </t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Karla</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ismael </t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Danian </t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>947558479</t>
+        </is>
+      </c>
+      <c r="J1327" t="inlineStr">
+        <is>
+          <t>karlajavier@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K1327" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renca </t>
+        </is>
+      </c>
+      <c r="M1327" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N1327" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1327" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1327" s="2">
+        <v>46161.21724537037</v>
+      </c>
+      <c r="Q1327" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:37:29</t>
+        </is>
+      </c>
+      <c r="R1327" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:37:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>119889332</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Karol</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Hija</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>977769712</t>
+        </is>
+      </c>
+      <c r="J1328" t="inlineStr">
+        <is>
+          <t>karol.grandon@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1328" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1328" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="M1328" t="inlineStr">
+        <is>
+          <t>9332</t>
+        </is>
+      </c>
+      <c r="N1328" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1328" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1328" s="2">
+        <v>46161.23034722223</v>
+      </c>
+      <c r="Q1328" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:09:27</t>
+        </is>
+      </c>
+      <c r="R1328" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:09:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Ignacio</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Javiera</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="J1329" t="inlineStr">
+        <is>
+          <t>gabrielyaelflor@gamil.com</t>
+        </is>
+      </c>
+      <c r="K1329" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1329" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1329" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1329" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1329" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1329" s="2">
+        <v>46161.23391203704</v>
+      </c>
+      <c r="Q1329" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:51:06</t>
+        </is>
+      </c>
+      <c r="R1329" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Yael</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Syndy</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>987678909</t>
+        </is>
+      </c>
+      <c r="J1330" t="inlineStr">
+        <is>
+          <t>ec9852150@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1330" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1330" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1330" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1330" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1330" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1330" s="2">
+        <v>46161.23402777778</v>
+      </c>
+      <c r="Q1330" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:50:19</t>
+        </is>
+      </c>
+      <c r="R1330" t="inlineStr">
+        <is>
+          <t>2026-05-19 01:50:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19313240-5 </t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Johanna</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daniela </t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>998483667</t>
+        </is>
+      </c>
+      <c r="J1331" t="inlineStr">
+        <is>
+          <t>johannaam@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1331" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lo prado </t>
+        </is>
+      </c>
+      <c r="M1331" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N1331" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1331" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1331" s="2">
+        <v>46161.23657407408</v>
+      </c>
+      <c r="Q1331" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:00:27</t>
+        </is>
+      </c>
+      <c r="R1331" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:00:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>139552105</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jessica </t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joaquín </t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>945116367</t>
+        </is>
+      </c>
+      <c r="J1332" t="inlineStr">
+        <is>
+          <t>jessiluri@hitmail.com</t>
+        </is>
+      </c>
+      <c r="K1332" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1332" t="inlineStr">
+        <is>
+          <t>Las condes</t>
+        </is>
+      </c>
+      <c r="M1332" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1332" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1332" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="P1332" s="2">
+        <v>46161.23815972223</v>
+      </c>
+      <c r="Q1332" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:13:03</t>
+        </is>
+      </c>
+      <c r="R1332" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:13:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222191440 </t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ángel </t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maira </t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>973496754</t>
+        </is>
+      </c>
+      <c r="J1333" t="inlineStr">
+        <is>
+          <t>cristobalescobar@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1333" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Florida </t>
+        </is>
+      </c>
+      <c r="M1333" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="N1333" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1333" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1333" s="2">
+        <v>46161.25340277777</v>
+      </c>
+      <c r="Q1333" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:13:44</t>
+        </is>
+      </c>
+      <c r="R1333" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:13:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>139552105</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Christopher </t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>942638820</t>
+        </is>
+      </c>
+      <c r="J1334" t="inlineStr">
+        <is>
+          <t>christopherquintana118@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1334" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Bernardo </t>
+        </is>
+      </c>
+      <c r="M1334" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="N1334" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1334" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="P1334" s="2">
+        <v>46161.26107638889</v>
+      </c>
+      <c r="Q1334" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:37:13</t>
+        </is>
+      </c>
+      <c r="R1334" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>20064128-0</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Alejandro Pozo</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Benjamin Pozo</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>+56946559683</t>
+        </is>
+      </c>
+      <c r="J1335" t="inlineStr">
+        <is>
+          <t>a.pozo.documentos@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1335" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1335" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="M1335" t="inlineStr">
+        <is>
+          <t>D1-KDM INDUSTRIAL S.A</t>
+        </is>
+      </c>
+      <c r="N1335" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1335" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1335" s="2">
+        <v>46161.28138888889</v>
+      </c>
+      <c r="Q1335" t="inlineStr">
+        <is>
+          <t>2026-05-19 03:58:34</t>
+        </is>
+      </c>
+      <c r="R1335" t="inlineStr">
+        <is>
+          <t>2026-05-19 03:58:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>166042194</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Rochard</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Marito</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>973683619</t>
+        </is>
+      </c>
+      <c r="J1336" t="inlineStr">
+        <is>
+          <t>notengo@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1336" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1336" t="inlineStr">
+        <is>
+          <t>La florida</t>
+        </is>
+      </c>
+      <c r="M1336" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N1336" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1336" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1336" s="2">
+        <v>46161.28302083333</v>
+      </c>
+      <c r="Q1336" t="inlineStr">
+        <is>
+          <t>2026-05-19 03:03:52</t>
+        </is>
+      </c>
+      <c r="R1336" t="inlineStr">
+        <is>
+          <t>2026-05-19 03:03:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>186762762</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>964464823</t>
+        </is>
+      </c>
+      <c r="J1337" t="inlineStr">
+        <is>
+          <t>yesseniamoraga45@gmail.com</t>
+        </is>
+      </c>
+      <c r="M1337" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N1337" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1337" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1337" s="2">
+        <v>46161.29451388889</v>
+      </c>
+      <c r="R1337" t="inlineStr">
+        <is>
+          <t>2026-05-19 03:20:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>19172396-1</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elizabeth </t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Noemi</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bastian </t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>954500683</t>
+        </is>
+      </c>
+      <c r="J1338" t="inlineStr">
+        <is>
+          <t>guissellaa.19@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1338" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1338" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M1338" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="N1338" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1338" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="P1338" s="2">
+        <v>46161.30756944444</v>
+      </c>
+      <c r="Q1338" t="inlineStr">
+        <is>
+          <t>2026-05-19 03:53:06</t>
+        </is>
+      </c>
+      <c r="R1338" t="inlineStr">
+        <is>
+          <t>2026-05-19 03:53:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>125228445</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Esposo</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Hijo</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>954352933</t>
+        </is>
+      </c>
+      <c r="J1339" t="inlineStr">
+        <is>
+          <t>mcarmenzuniga80@gmail.comi</t>
+        </is>
+      </c>
+      <c r="K1339" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santiago </t>
+        </is>
+      </c>
+      <c r="M1339" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="N1339" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1339" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1339" s="2">
+        <v>46161.32173611112</v>
+      </c>
+      <c r="Q1339" t="inlineStr">
+        <is>
+          <t>2026-05-19 04:16:08</t>
+        </is>
+      </c>
+      <c r="R1339" t="inlineStr">
+        <is>
+          <t>2026-05-19 04:16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>191723961</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roberto </t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>+56 9 3591 6111</t>
+        </is>
+      </c>
+      <c r="J1340" t="inlineStr">
+        <is>
+          <t>robertocoradaandres@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1340" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1340" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M1340" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="N1340" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1340" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="P1340" s="2">
+        <v>46161.33212962963</v>
+      </c>
+      <c r="Q1340" t="inlineStr">
+        <is>
+          <t>2026-05-19 04:32:05</t>
+        </is>
+      </c>
+      <c r="R1340" t="inlineStr">
+        <is>
+          <t>2026-05-19 04:32:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>20064128-0</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Ana Zenteno</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Bárbara Zenteno</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>Consuelo Vergara</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>+56981204344</t>
+        </is>
+      </c>
+      <c r="J1341" t="inlineStr">
+        <is>
+          <t>an4plis@outlook.com</t>
+        </is>
+      </c>
+      <c r="K1341" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1341" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="M1341" t="inlineStr">
+        <is>
+          <t>A2-Clínica UC</t>
+        </is>
+      </c>
+      <c r="N1341" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1341" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1341" s="2">
+        <v>46161.3629050926</v>
+      </c>
+      <c r="R1341" t="inlineStr">
+        <is>
+          <t>2026-05-19 04:47:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>20064128-0</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Bárbara Oyarce Navarro</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Christian Pefaur Villavicencio</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Noah Pefaur Oyarce</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>+56966903897</t>
+        </is>
+      </c>
+      <c r="J1342" t="inlineStr">
+        <is>
+          <t>boyarcenavarro@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1342" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1342" t="inlineStr">
+        <is>
+          <t>Maipu</t>
+        </is>
+      </c>
+      <c r="M1342" t="inlineStr">
+        <is>
+          <t>E-pilotes terratest s.a.</t>
+        </is>
+      </c>
+      <c r="N1342" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1342" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P1342" s="2">
+        <v>46161.36310185185</v>
+      </c>
+      <c r="Q1342" t="inlineStr">
+        <is>
+          <t>2026-05-19 05:18:18</t>
+        </is>
+      </c>
+      <c r="R1342" t="inlineStr">
+        <is>
+          <t>2026-05-19 05:18:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>ignacio subitbre</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>katalina sean</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>camila subiatbre</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>56997658824</t>
+        </is>
+      </c>
+      <c r="J1343" t="inlineStr">
+        <is>
+          <t>Isubiabre9@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1343" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L1343" t="inlineStr">
+        <is>
+          <t>valparaiso</t>
+        </is>
+      </c>
+      <c r="M1343" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N1343" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1343" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P1343" s="2">
+        <v>46161.84292824075</v>
+      </c>
+      <c r="Q1343" t="inlineStr">
+        <is>
+          <t>2026-05-19 16:43:52</t>
+        </is>
+      </c>
+      <c r="R1343" t="inlineStr">
+        <is>
+          <t>2026-05-19 16:43:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>20467052</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARLA SAAVEDRA </t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Benjamin SAAVEDRA </t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>56966954540</t>
+        </is>
+      </c>
+      <c r="J1344" t="inlineStr">
+        <is>
+          <t>Carla.cea009@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1344" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1344" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="M1344" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N1344" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1344" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P1344" s="2">
+        <v>46161.84465277778</v>
+      </c>
+      <c r="Q1344" t="inlineStr">
+        <is>
+          <t>2026-05-19 16:40:46</t>
+        </is>
+      </c>
+      <c r="R1344" t="inlineStr">
+        <is>
+          <t>2026-05-19 16:40:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>13565459-0</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>fresia</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>melissa</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>rocio</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>966765462</t>
+        </is>
+      </c>
+      <c r="J1345" t="inlineStr">
+        <is>
+          <t>fresiapita@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1345" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1345" t="inlineStr">
+        <is>
+          <t>las condes</t>
+        </is>
+      </c>
+      <c r="M1345" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1345" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1345" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P1345" s="2">
+        <v>46161.85194444444</v>
+      </c>
+      <c r="Q1345" t="inlineStr">
+        <is>
+          <t>2026-05-19 16:54:20</t>
+        </is>
+      </c>
+      <c r="R1345" t="inlineStr">
+        <is>
+          <t>2026-05-19 16:54:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>17.026.006-6</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Karen Larenas</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>camila larenas</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>942621922</t>
+        </is>
+      </c>
+      <c r="J1346" t="inlineStr">
+        <is>
+          <t>karenlarenastapia@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1346" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1346" t="inlineStr">
+        <is>
+          <t>la florida</t>
+        </is>
+      </c>
+      <c r="M1346" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 0066F1</t>
+        </is>
+      </c>
+      <c r="N1346" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1346" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="P1346" s="2">
+        <v>46161.8563425926</v>
+      </c>
+      <c r="R1346" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:34:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>200730720</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Diego Tabilo Jopia</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Makarena Riquelme Cisternas</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>Rosa Cisternas Chacana</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>Sol Aburto Riquelme</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>Alfonso Tabilo Riquelme</t>
+        </is>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>965583375</t>
+        </is>
+      </c>
+      <c r="J1347" t="inlineStr">
+        <is>
+          <t>mk.rcisternas@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1347" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L1347" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="M1347" t="inlineStr">
+        <is>
+          <t>072</t>
+        </is>
+      </c>
+      <c r="N1347" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1347" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P1347" s="2">
+        <v>46161.85708333334</v>
+      </c>
+      <c r="R1347" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:36:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>20467052</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>ELIA ACUM COLPIANTE</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Hector Henrrique</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Maria Ignacia Henrrique</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>56972763348</t>
+        </is>
+      </c>
+      <c r="J1348" t="inlineStr">
+        <is>
+          <t>sr.accolpiant00@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1348" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1348" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="M1348" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N1348" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1348" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P1348" s="2">
+        <v>46161.86263888889</v>
+      </c>
+      <c r="Q1348" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:14:03</t>
+        </is>
+      </c>
+      <c r="R1348" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:14:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>202372376</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>juan ortis</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>karin altamirano</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>56942909914</t>
+        </is>
+      </c>
+      <c r="J1349" t="inlineStr">
+        <is>
+          <t>Ignaciofuenteso81@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1349" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L1349" t="inlineStr">
+        <is>
+          <t>valparaiso</t>
+        </is>
+      </c>
+      <c r="M1349" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N1349" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1349" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P1349" s="2">
+        <v>46161.87202546296</v>
+      </c>
+      <c r="Q1349" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:14:28</t>
+        </is>
+      </c>
+      <c r="R1349" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:14:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>125228445</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Lucianne</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Esposo</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Bebe</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>972008989</t>
+        </is>
+      </c>
+      <c r="J1350" t="inlineStr">
+        <is>
+          <t>luciannezepherin@gmsil.com</t>
+        </is>
+      </c>
+      <c r="K1350" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santiago </t>
+        </is>
+      </c>
+      <c r="M1350" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="N1350" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1350" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P1350" s="2">
+        <v>46161.87375</v>
+      </c>
+      <c r="Q1350" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:31:37</t>
+        </is>
+      </c>
+      <c r="R1350" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:31:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>20467052</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>ELENA ISABEL GONZALEZ</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Gustabo Sandobal</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>56955673714</t>
+        </is>
+      </c>
+      <c r="J1351" t="inlineStr">
+        <is>
+          <t>elena.ig009@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1351" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1351" t="inlineStr">
+        <is>
+          <t>Macul</t>
+        </is>
+      </c>
+      <c r="M1351" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="N1351" t="inlineStr">
+        <is>
+          <t>Empresa con sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1351" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P1351" s="2">
+        <v>46161.88608796296</v>
+      </c>
+      <c r="Q1351" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:46:47</t>
+        </is>
+      </c>
+      <c r="R1351" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:46:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>13565459-0</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deyna </t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>agustina</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>jasmin</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>979706717</t>
+        </is>
+      </c>
+      <c r="J1352" t="inlineStr">
+        <is>
+          <t>deynarivasb@gmail.com</t>
+        </is>
+      </c>
+      <c r="K1352" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L1352" t="inlineStr">
+        <is>
+          <t>pudahuel</t>
+        </is>
+      </c>
+      <c r="M1352" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N1352" t="inlineStr">
+        <is>
+          <t>Empresa sin sello 40 horas</t>
+        </is>
+      </c>
+      <c r="O1352" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P1352" s="2">
+        <v>46161.88822916667</v>
+      </c>
+      <c r="Q1352" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:50:36</t>
+        </is>
+      </c>
+      <c r="R1352" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:50:36</t>
         </is>
       </c>
     </row>
